--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -9,9 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="요약" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="단가표" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="CPU 할인 효과" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="프로젝트별 구성" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="마진 계산" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="단가표" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="CPU 할인 효과" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="프로젝트별 구성" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="132">
   <si>
     <r>
       <rPr>
@@ -1267,6 +1268,716 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">타겟 프라이스 → 우리 마진</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란 칸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 프라이스 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객에게 파는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 가격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 금액을 넣으면 마진이 바로 계산됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) TSU DC24V </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">칸에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">450,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마진 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 프라이스 − 매입가     마진율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마진 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 프라이스 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매가 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">전원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 수량
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매입가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 프라이스
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마진
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">마진율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 매출</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 마진</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← 마진이 마이너스면 빨간색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC220V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 프로젝트 전부</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">납품 방식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 매입</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC24V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 납품</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC220V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 납품 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC24V)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 연간 합계는 해당 납품 방식의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 칸을 모두 입력해야 나옵니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로젝트별 마진은 위 표에서 바로 확인하세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 매입가는 현재 할인율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(CPU 0.45 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확장 모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.40) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 부품은 매입가에 포함되어 있지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1376,9 +2087,6 @@
     <t xml:space="preserve">모델</t>
   </si>
   <si>
-    <t xml:space="preserve">전원</t>
-  </si>
-  <si>
     <t xml:space="preserve">설명</t>
   </si>
   <si>
@@ -2251,51 +2959,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 수량
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">연간 절감</t>
   </si>
   <si>
@@ -2771,9 +3434,6 @@
       </rPr>
       <t xml:space="preserve">대 가격</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">AC220V</t>
   </si>
   <si>
     <r>
@@ -3616,12 +4276,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3829,10 +4490,32 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -3854,14 +4537,6 @@
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1F3864"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
@@ -3925,7 +4600,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -3945,6 +4620,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF808080"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3987,7 +4677,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4084,12 +4774,80 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -4100,7 +4858,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4108,7 +4866,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4116,39 +4874,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4160,15 +4906,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="33" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4181,6 +4927,17 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -4198,7 +4955,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
@@ -4230,7 +4987,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -4424,7 +5181,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -4690,8 +5447,20 @@
       <c r="F20" s="23"/>
       <c r="G20" s="23"/>
     </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="str">
+        <f aca="false">"⑧ 연간 마진 (DC24V 납품): "&amp;IF(ISNUMBER('마진 계산'!E17),TEXT('마진 계산'!E17,"#,##0")&amp;"원  (마진율 "&amp;TEXT('마진 계산'!F17,"0.0%")&amp;")","타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
+        <v>⑧ 연간 마진 (DC24V 납품): 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A15:G15"/>
@@ -4700,6 +5469,7 @@
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4712,6 +5482,406 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <f aca="false">요약!C6</f>
+        <v>200</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F9</f>
+        <v>392850</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="10" t="str">
+        <f aca="false">IF(E6="","",E6-D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="29" t="str">
+        <f aca="false">IF(OR(E6="",E6=0),"",F6/E6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f aca="false">IF(E6="","",C6*E6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="10" t="str">
+        <f aca="false">IF(E6="","",C6*F6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <f aca="false">요약!C6</f>
+        <v>200</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <f aca="false">'프로젝트별 구성'!F11</f>
+        <v>384750</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36" t="str">
+        <f aca="false">IF(E7="","",E7-D7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="37" t="str">
+        <f aca="false">IF(OR(E7="",E7=0),"",F7/E7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="34" t="str">
+        <f aca="false">IF(E7="","",C7*E7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="36" t="str">
+        <f aca="false">IF(E7="","",C7*F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <f aca="false">요약!C7</f>
+        <v>300</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F19</f>
+        <v>417600</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="10" t="str">
+        <f aca="false">IF(E8="","",E8-D8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="str">
+        <f aca="false">IF(OR(E8="",E8=0),"",F8/E8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f aca="false">IF(E8="","",C8*E8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="10" t="str">
+        <f aca="false">IF(E8="","",C8*F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <f aca="false">요약!C7</f>
+        <v>300</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <f aca="false">'프로젝트별 구성'!F21</f>
+        <v>406350</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36" t="str">
+        <f aca="false">IF(E9="","",E9-D9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="37" t="str">
+        <f aca="false">IF(OR(E9="",E9=0),"",F9/E9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="34" t="str">
+        <f aca="false">IF(E9="","",C9*E9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="36" t="str">
+        <f aca="false">IF(E9="","",C9*F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <f aca="false">요약!C8</f>
+        <v>50</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F30</f>
+        <v>531250</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="10" t="str">
+        <f aca="false">IF(E10="","",E10-D10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="29" t="str">
+        <f aca="false">IF(OR(E10="",E10=0),"",F10/E10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f aca="false">IF(E10="","",C10*E10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="10" t="str">
+        <f aca="false">IF(E10="","",C10*F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <f aca="false">요약!C8</f>
+        <v>50</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <f aca="false">'프로젝트별 구성'!F33</f>
+        <v>523150</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="36" t="str">
+        <f aca="false">IF(E11="","",E11-D11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="37" t="str">
+        <f aca="false">IF(OR(E11="",E11=0),"",F11/E11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="34" t="str">
+        <f aca="false">IF(E11="","",C11*E11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="36" t="str">
+        <f aca="false">IF(E11="","",C11*F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <f aca="false">요약!C9</f>
+        <v>100</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F44</f>
+        <v>1449500</v>
+      </c>
+      <c r="E12" s="28"/>
+      <c r="F12" s="10" t="str">
+        <f aca="false">IF(E12="","",E12-D12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="29" t="str">
+        <f aca="false">IF(OR(E12="",E12=0),"",F12/E12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f aca="false">IF(E12="","",C12*E12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="10" t="str">
+        <f aca="false">IF(E12="","",C12*F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="9" t="n">
+        <f aca="false">C6*D6+C8*D8+C10*D10+C12*D12</f>
+        <v>375362500</v>
+      </c>
+      <c r="D17" s="9" t="str">
+        <f aca="false">IF((E6="")+(E8="")+(E10="")+(E12="")&gt;0,"타겟 "&amp;((E6="")+(E8="")+(E10="")+(E12=""))&amp;"건 미입력",H6+H8+H10+H12)</f>
+        <v>타겟 4건 미입력</v>
+      </c>
+      <c r="E17" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(D17),D17-C17,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(D17),E17/D17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="39"/>
+      <c r="C18" s="9" t="n">
+        <f aca="false">C7*D7+C9*D9+C11*D11+C12*D12</f>
+        <v>369962500</v>
+      </c>
+      <c r="D18" s="9" t="str">
+        <f aca="false">IF((E7="")+(E9="")+(E11="")+(E12="")&gt;0,"타겟 "&amp;((E7="")+(E9="")+(E11="")+(E12=""))&amp;"건 미입력",H7+H9+H11+H12)</f>
+        <v>타겟 4건 미입력</v>
+      </c>
+      <c r="E18" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(D18),D18-C18,"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(D18),E18/D18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F6:I12">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(F6),F6&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:F18">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(E17),E17&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -4729,55 +5899,55 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>29</v>
+      <c r="A1" s="25" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>40</v>
+      <c r="B5" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>60</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>886000</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="45" t="n">
         <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -4786,22 +5956,22 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>42</v>
+      <c r="B6" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>62</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>873000</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="45" t="n">
         <v>0.45</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -4810,22 +5980,22 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>45</v>
+      <c r="B7" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>65</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>855000</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="45" t="n">
         <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -4834,22 +6004,22 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>47</v>
+      <c r="B8" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>67</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>928000</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="45" t="n">
         <v>0.45</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -4858,22 +6028,22 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>49</v>
+      <c r="B9" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>69</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>903000</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="45" t="n">
         <v>0.45</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -4882,22 +6052,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>52</v>
+      <c r="B10" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>72</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>228000</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -4906,22 +6076,22 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>54</v>
+      <c r="B11" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>74</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>202000</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -4930,22 +6100,22 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>56</v>
+      <c r="B12" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>76</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -4954,22 +6124,22 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>58</v>
+      <c r="B13" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -4978,22 +6148,22 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>60</v>
+      <c r="B14" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>80</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>213000</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -5002,22 +6172,22 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>62</v>
+      <c r="B15" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>82</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>161000</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -5026,22 +6196,22 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>64</v>
+      <c r="B16" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>84</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -5050,22 +6220,22 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>66</v>
+      <c r="B17" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>86</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
@@ -5074,22 +6244,22 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>68</v>
+      <c r="B18" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>88</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>311000</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -5098,22 +6268,22 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>70</v>
+      <c r="B19" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>90</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>284000</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -5122,22 +6292,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>72</v>
+      <c r="D20" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>331000</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -5146,22 +6316,22 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>74</v>
+      <c r="B21" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>94</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>346000</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -5170,22 +6340,22 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>76</v>
+      <c r="B22" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>96</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>351000</v>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="G22" s="10" t="n">
@@ -5204,7 +6374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -5223,61 +6393,61 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
-        <v>77</v>
+      <c r="A1" s="47" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="32" t="n">
+      <c r="A3" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="49" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="32" t="n">
+      <c r="A4" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="49" t="n">
         <v>0.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>39</v>
+      <c r="A7" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -5291,11 +6461,11 @@
         <f aca="false">ROUND(C7*$B$4,0)</f>
         <v>349200</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="50" t="n">
         <f aca="false">D7-E7</f>
         <v>43650</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="27" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -5303,16 +6473,16 @@
         <f aca="false">F7*G7</f>
         <v>10912500</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>87</v>
+      <c r="I7" s="51" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>39</v>
+      <c r="A8" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -5326,11 +6496,11 @@
         <f aca="false">ROUND(C8*$B$4,0)</f>
         <v>371200</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="50" t="n">
         <f aca="false">D8-E8</f>
         <v>46400</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="27" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -5338,16 +6508,16 @@
         <f aca="false">F8*G8</f>
         <v>13920000</v>
       </c>
-      <c r="I8" s="35" t="s">
-        <v>88</v>
+      <c r="I8" s="51" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>39</v>
+      <c r="A9" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -5361,11 +6531,11 @@
         <f aca="false">ROUND(C9*$B$4,0)</f>
         <v>354400</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="50" t="n">
         <f aca="false">D9-E9</f>
         <v>44300</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="27" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
@@ -5373,16 +6543,16 @@
         <f aca="false">F9*G9</f>
         <v>4430000</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="51" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>44</v>
+      <c r="A10" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -5396,11 +6566,11 @@
         <f aca="false">ROUND(C10*$B$4,0)</f>
         <v>342000</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="50" t="n">
         <f aca="false">D10-E10</f>
         <v>42750</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="27" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -5408,16 +6578,16 @@
         <f aca="false">F10*G10</f>
         <v>10687500</v>
       </c>
-      <c r="I10" s="35" t="s">
-        <v>89</v>
+      <c r="I10" s="51" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>44</v>
+      <c r="A11" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -5431,11 +6601,11 @@
         <f aca="false">ROUND(C11*$B$4,0)</f>
         <v>361200</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="50" t="n">
         <f aca="false">D11-E11</f>
         <v>45150</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="27" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -5443,43 +6613,43 @@
         <f aca="false">F11*G11</f>
         <v>13545000</v>
       </c>
-      <c r="I11" s="35" t="s">
-        <v>90</v>
+      <c r="I11" s="51" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
+      <c r="A13" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
       <c r="H13" s="16" t="n">
         <f aca="false">H7+H8+H9</f>
         <v>29262500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
+      <c r="A14" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
       <c r="H14" s="16" t="n">
         <f aca="false">H9+H10+H11</f>
         <v>28662500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>93</v>
+      <c r="A16" s="42" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5497,7 +6667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -5513,81 +6683,81 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>94</v>
+      <c r="A1" s="25" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="39" t="s">
+      <c r="A5" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="A6" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="41" t="str">
+      <c r="A8" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="55" t="str">
         <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="9" t="n">
@@ -5600,30 +6770,30 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43" t="n">
+      <c r="A9" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="57" t="n">
         <f aca="false">SUM(F8:F8)</f>
         <v>392850</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="41" t="str">
+      <c r="A10" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="55" t="str">
         <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
@@ -5636,94 +6806,94 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="43" t="n">
+      <c r="A11" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="57" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>384750</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
+      <c r="A12" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="39" t="s">
+      <c r="A15" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="A16" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="41" t="str">
+      <c r="A18" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="55" t="str">
         <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="9" t="n">
@@ -5736,30 +6906,30 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="43" t="n">
+      <c r="A19" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="57" t="n">
         <f aca="false">SUM(F18:F18)</f>
         <v>417600</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="41" t="str">
+      <c r="A20" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="55" t="str">
         <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="9" t="n">
@@ -5772,94 +6942,94 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="43" t="n">
+      <c r="A21" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="57" t="n">
         <f aca="false">SUM(F20:F20)</f>
         <v>406350</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
+      <c r="A22" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="39" t="s">
+      <c r="A25" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="A26" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="41" t="str">
+      <c r="A28" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="55" t="str">
         <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="9" t="n">
@@ -5872,15 +7042,15 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="41" t="str">
+      <c r="A29" s="26"/>
+      <c r="B29" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="55" t="str">
         <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="9" t="n">
@@ -5893,30 +7063,30 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43" t="n">
+      <c r="A30" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="57" t="n">
         <f aca="false">SUM(F28:F29)</f>
         <v>531250</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="41" t="str">
+      <c r="A31" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="55" t="str">
         <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="9" t="n">
@@ -5929,15 +7099,15 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="41" t="str">
+      <c r="A32" s="26"/>
+      <c r="B32" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="55" t="str">
         <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="9" t="n">
@@ -5950,94 +7120,94 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="43" t="n">
+      <c r="A33" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="57" t="n">
         <f aca="false">SUM(F31:F32)</f>
         <v>523150</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
+      <c r="A34" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="39" t="s">
+      <c r="A37" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="A38" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="41" t="str">
+      <c r="A40" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="55" t="str">
         <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU + 이더넷 (입력 14 / 출력 10)</v>
       </c>
-      <c r="D40" s="25" t="n">
+      <c r="D40" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="9" t="n">
@@ -6050,15 +7220,15 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="41" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="55" t="str">
         <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="D41" s="26" t="n">
         <v>6</v>
       </c>
       <c r="E41" s="9" t="n">
@@ -6071,15 +7241,15 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25"/>
-      <c r="B42" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="41" t="str">
+      <c r="A42" s="26"/>
+      <c r="B42" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="55" t="str">
         <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>릴레이 출력 16점</v>
       </c>
-      <c r="D42" s="25" t="n">
+      <c r="D42" s="26" t="n">
         <v>4</v>
       </c>
       <c r="E42" s="9" t="n">
@@ -6092,15 +7262,15 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25"/>
-      <c r="B43" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="41" t="str">
+      <c r="A43" s="26"/>
+      <c r="B43" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="55" t="str">
         <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>아날로그 출력 4CH</v>
       </c>
-      <c r="D43" s="25" t="n">
+      <c r="D43" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="9" t="n">
@@ -6113,27 +7283,27 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="43" t="n">
+      <c r="A44" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="57" t="n">
         <f aca="false">SUM(F40:F43)</f>
         <v>1449500</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
+      <c r="A45" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="256">
   <si>
     <r>
       <rPr>
@@ -596,6 +596,932 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가격 비교 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs RFQ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">충족 구성  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금액 차이의 핵심</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)  /  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제공 점수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RFQ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 가격</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 차이
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 금액
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 차이
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제안</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241CE40T + TM3DI16×2 + TM3DI8 + TM3DQ16T + TM3DQ8T + TM3AQ2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40 (TR) / AO 2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">✕ 미충족</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정안
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정본 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PPT)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241CE24T + TM3DI16×6 + TM3DQ16R×4 + TM3AQ4
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64 / AO 4 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현행 점수 그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○ 충족</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최소안</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241CE24T + TM3DI16×5 + TM3DQ16R×3 + TM3DQ8R + TM3AQ4
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">94 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">56 / AO 4 (RFQ ±10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">허용 활용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△ Techross
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 세 경우 모두 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM3XTRA1 + TM3XREC1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 가격표에 없어 미포함 — 견적 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최소안은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFQ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통사항 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 '10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정도 차이 허용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">102 → 94, -8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 것으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동의 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CE40T </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추정가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU TM241CE40T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 단가표에 없음 → 추정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(C40T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 13,000) × 0.45</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">핵심 정리</t>
   </si>
   <si>
@@ -641,227 +1567,6 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">③ MCC: Schneider </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제안은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFQ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조건 미달 → 재견적 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.  (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 출력이어야 하는데 트랜지스터로 제안</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">38</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2CH </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부족</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위 표의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MCC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가격은 조건을 맞춘 구성 기준입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1425,9 +2130,6 @@
     <t xml:space="preserve">No.</t>
   </si>
   <si>
-    <t xml:space="preserve">구분</t>
-  </si>
-  <si>
     <t xml:space="preserve">검토 항목</t>
   </si>
   <si>
@@ -8566,9 +9268,6 @@
       </rPr>
       <t xml:space="preserve">12 + TR 4)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
   </si>
   <si>
     <r>
@@ -8967,13 +9666,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="\+#,##0;\-#,##0;\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="57">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9136,7 +9836,15 @@
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFC00000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -9144,6 +9852,93 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF375623"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF7F6000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF7F6000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF595959"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF595959"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF1F3864"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -9188,14 +9983,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="맑은 고딕"/>
@@ -9212,31 +9999,10 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FF375623"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF7F6000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -9245,12 +10011,6 @@
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -9278,14 +10038,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF7F6000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="WenQuanYi Zen Hei"/>
@@ -9296,14 +10048,6 @@
       <color rgb="FFC00000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1F3864"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -9361,14 +10105,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -9455,7 +10199,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="91">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9532,15 +10276,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="36" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9548,7 +10348,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9556,32 +10360,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -9592,39 +10384,39 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9632,7 +10424,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9640,7 +10432,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9652,7 +10444,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9684,11 +10476,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9700,7 +10492,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9708,11 +10500,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9720,7 +10512,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9736,23 +10528,23 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="46" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9764,11 +10556,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10035,7 +10827,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -10218,125 +11010,258 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="str">
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <f aca="false">$D$19+2*VLOOKUP("TM3DI16",단가표!$B$5:$G$22,6,FALSE())+VLOOKUP("TM3DI8",단가표!$B$5:$G$22,6,FALSE())+VLOOKUP("TM3DQ16T",단가표!$B$5:$G$22,6,FALSE())+VLOOKUP("TM3DQ8T",단가표!$B$5:$G$22,6,FALSE())+VLOOKUP("TM3AQ2",단가표!$B$5:$G$22,6,FALSE())</f>
+        <v>983050</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <f aca="false">D15*$C$9</f>
+        <v>98305000</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <f aca="false">'프로젝트별 구성'!F44</f>
+        <v>1449500</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <f aca="false">D16-$D$15</f>
+        <v>466450</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <f aca="false">D16*$C$9</f>
+        <v>144950000</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <f aca="false">F16-$F$15</f>
+        <v>46645000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="25" t="n">
+        <f aca="false">VLOOKUP("TM241CE24T",단가표!$B$5:$G$22,6,FALSE())+5*VLOOKUP("TM3DI16",단가표!$B$5:$G$22,6,FALSE())+3*VLOOKUP("TM3DQ16R",단가표!$B$5:$G$22,6,FALSE())+VLOOKUP("TM3DQ8R",단가표!$B$5:$G$22,6,FALSE())+VLOOKUP("TM3AQ4",단가표!$B$5:$G$22,6,FALSE())</f>
+        <v>1331900</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <f aca="false">D17-$D$15</f>
+        <v>348850</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <f aca="false">D17*$C$9</f>
+        <v>133190000</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <f aca="false">F17-$F$15</f>
+        <v>34885000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31" t="n">
+        <v>423450</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="str">
         <f aca="false">"① 연간 구매금액: DC24V 기준 약 "&amp;TEXT(F10/100000000,"0.00")&amp;"억 원,  AC220V 기준 약 "&amp;TEXT(G10/100000000,"0.00")&amp;"억 원"</f>
         <v>① 연간 구매금액: DC24V 기준 약 3.75억 원,  AC220V 기준 약 3.70억 원</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-    </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="str">
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="35" t="str">
+        <f aca="false">"③ MCC: Schneider 제안은 RFQ 미충족(TR 출력, 점수 부족). 제대로 구성하면 1대 "&amp;TEXT(D16,"#,##0")&amp;"원 — Schneider 제안보다 1대 "&amp;TEXT(E16,"#,##0")&amp;"원, 연 "&amp;TEXT(G16,"#,##0")&amp;"원 더 듭니다. (위 MCC 가격 비교 참고)"</f>
+        <v>③ MCC: Schneider 제안은 RFQ 미충족(TR 출력, 점수 부족). 제대로 구성하면 1대 1,449,500원 — Schneider 제안보다 1대 466,450원, 연 46,645,000원 더 듭니다. (위 MCC 가격 비교 참고)</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="38" t="str">
         <f aca="false">"⑧ 연간 마진 (DC24V 납품): "&amp;IF(ISNUMBER('마진 계산'!E17),TEXT('마진 계산'!E17,"#,##0")&amp;"원  (마진율 "&amp;TEXT('마진 계산'!F17,"0.0%")&amp;")","타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
         <v>⑧ 연간 마진 (DC24V 납품): 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="str">
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="39" t="str">
         <f aca="false">"⑨ Schneider 제안 검토: 반드시 수정 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"✕")&amp;"건, 보완 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"△")&amp;"건  → 'Schneider 제안 검토' 시트"</f>
         <v>⑨ Schneider 제안 검토: 반드시 수정 4건, 보완 6건  → 'Schneider 제안 검토' 시트</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10366,607 +11291,607 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
-        <v>29</v>
+      <c r="A1" s="40" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="30" t="str">
+      <c r="A3" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="43" t="str">
         <f aca="false">"✕ "&amp;COUNTIF(F7:F24,"✕")&amp;"건   △ "&amp;COUNTIF(F7:F24,"△")&amp;"건   ○ "&amp;COUNTIF(F7:F24,"○")&amp;"건"</f>
         <v>✕ 4건   △ 6건   ○ 8건</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>43</v>
+      <c r="B7" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>62</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>46</v>
+        <v>63</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>48</v>
+      <c r="B8" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>67</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>50</v>
+        <v>68</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="n">
+      <c r="A9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>52</v>
+      <c r="B9" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>71</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>54</v>
+        <v>72</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="n">
+      <c r="A10" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>55</v>
+      <c r="B10" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>74</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>59</v>
+        <v>75</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="n">
+      <c r="A11" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>63</v>
+      <c r="C11" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="n">
+      <c r="A12" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="33" t="s">
+      <c r="B12" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>67</v>
+      <c r="G12" s="46" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="n">
+      <c r="A13" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>68</v>
+      <c r="B13" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>87</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>72</v>
+        <v>88</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>74</v>
+      <c r="B14" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>93</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>67</v>
+        <v>95</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="33" t="s">
+      <c r="B15" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="G18" s="49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="37" t="s">
+      <c r="G19" s="51" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="44" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>97</v>
+      <c r="C20" s="52" t="s">
+        <v>116</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>100</v>
+        <v>118</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="n">
+      <c r="A21" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>105</v>
+      <c r="B21" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>106</v>
+      <c r="B22" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>125</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="41" t="s">
-        <v>109</v>
+        <v>126</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="53" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="31" t="n">
+      <c r="A23" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>113</v>
+      <c r="B23" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="54" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="n">
+      <c r="A24" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>117</v>
+      <c r="B24" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="51" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43" t="s">
-        <v>118</v>
+      <c r="A26" s="55" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C28" s="33" t="s">
-        <v>123</v>
+      <c r="C28" s="45" t="s">
+        <v>142</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="31" t="n">
+        <v>143</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="F29" s="31" t="n">
+      <c r="C29" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="F30" s="31" t="n">
+      <c r="C30" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="F31" s="31" t="n">
+      <c r="C31" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C32" s="33" t="s">
-        <v>135</v>
+      <c r="C32" s="45" t="s">
+        <v>154</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="F32" s="31" t="n">
+        <v>155</v>
+      </c>
+      <c r="E32" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
+      <c r="A33" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="43" t="s">
-        <v>139</v>
+      <c r="A35" s="55" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
+      <c r="A36" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
+      <c r="A37" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
+      <c r="A38" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11007,18 +11932,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="46" t="s">
-        <v>143</v>
+      <c r="A1" s="58" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11026,38 +11951,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="47" t="n">
+      <c r="B6" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="59" t="n">
         <f aca="false">요약!C6</f>
         <v>200</v>
       </c>
@@ -11065,12 +11990,12 @@
         <f aca="false">'프로젝트별 구성'!F9</f>
         <v>392850</v>
       </c>
-      <c r="E6" s="48"/>
+      <c r="E6" s="60"/>
       <c r="F6" s="10" t="str">
         <f aca="false">IF(E6="","",E6-D6)</f>
         <v/>
       </c>
-      <c r="G6" s="49" t="str">
+      <c r="G6" s="61" t="str">
         <f aca="false">IF(OR(E6="",E6=0),"",F6/E6)</f>
         <v/>
       </c>
@@ -11082,39 +12007,39 @@
         <f aca="false">IF(E6="","",C6*F6)</f>
         <v/>
       </c>
-      <c r="J6" s="50" t="s">
-        <v>155</v>
+      <c r="J6" s="62" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="53" t="n">
+      <c r="B7" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="65" t="n">
         <f aca="false">요약!C6</f>
         <v>200</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="66" t="n">
         <f aca="false">'프로젝트별 구성'!F11</f>
         <v>384750</v>
       </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="56" t="str">
+      <c r="E7" s="67"/>
+      <c r="F7" s="68" t="str">
         <f aca="false">IF(E7="","",E7-D7)</f>
         <v/>
       </c>
-      <c r="G7" s="57" t="str">
+      <c r="G7" s="69" t="str">
         <f aca="false">IF(OR(E7="",E7=0),"",F7/E7)</f>
         <v/>
       </c>
-      <c r="H7" s="54" t="str">
+      <c r="H7" s="66" t="str">
         <f aca="false">IF(E7="","",C7*E7)</f>
         <v/>
       </c>
-      <c r="I7" s="56" t="str">
+      <c r="I7" s="68" t="str">
         <f aca="false">IF(E7="","",C7*F7)</f>
         <v/>
       </c>
@@ -11123,10 +12048,10 @@
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="47" t="n">
+      <c r="B8" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="59" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -11134,12 +12059,12 @@
         <f aca="false">'프로젝트별 구성'!F19</f>
         <v>417600</v>
       </c>
-      <c r="E8" s="48"/>
+      <c r="E8" s="60"/>
       <c r="F8" s="10" t="str">
         <f aca="false">IF(E8="","",E8-D8)</f>
         <v/>
       </c>
-      <c r="G8" s="49" t="str">
+      <c r="G8" s="61" t="str">
         <f aca="false">IF(OR(E8="",E8=0),"",F8/E8)</f>
         <v/>
       </c>
@@ -11153,34 +12078,34 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="53" t="n">
+      <c r="B9" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="65" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="66" t="n">
         <f aca="false">'프로젝트별 구성'!F21</f>
         <v>406350</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56" t="str">
+      <c r="E9" s="67"/>
+      <c r="F9" s="68" t="str">
         <f aca="false">IF(E9="","",E9-D9)</f>
         <v/>
       </c>
-      <c r="G9" s="57" t="str">
+      <c r="G9" s="69" t="str">
         <f aca="false">IF(OR(E9="",E9=0),"",F9/E9)</f>
         <v/>
       </c>
-      <c r="H9" s="54" t="str">
+      <c r="H9" s="66" t="str">
         <f aca="false">IF(E9="","",C9*E9)</f>
         <v/>
       </c>
-      <c r="I9" s="56" t="str">
+      <c r="I9" s="68" t="str">
         <f aca="false">IF(E9="","",C9*F9)</f>
         <v/>
       </c>
@@ -11189,10 +12114,10 @@
       <c r="A10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="47" t="n">
+      <c r="B10" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="59" t="n">
         <f aca="false">요약!C8</f>
         <v>50</v>
       </c>
@@ -11200,12 +12125,12 @@
         <f aca="false">'프로젝트별 구성'!F30</f>
         <v>531250</v>
       </c>
-      <c r="E10" s="48"/>
+      <c r="E10" s="60"/>
       <c r="F10" s="10" t="str">
         <f aca="false">IF(E10="","",E10-D10)</f>
         <v/>
       </c>
-      <c r="G10" s="49" t="str">
+      <c r="G10" s="61" t="str">
         <f aca="false">IF(OR(E10="",E10=0),"",F10/E10)</f>
         <v/>
       </c>
@@ -11219,34 +12144,34 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="53" t="n">
+      <c r="B11" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="65" t="n">
         <f aca="false">요약!C8</f>
         <v>50</v>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="66" t="n">
         <f aca="false">'프로젝트별 구성'!F33</f>
         <v>523150</v>
       </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="56" t="str">
+      <c r="E11" s="67"/>
+      <c r="F11" s="68" t="str">
         <f aca="false">IF(E11="","",E11-D11)</f>
         <v/>
       </c>
-      <c r="G11" s="57" t="str">
+      <c r="G11" s="69" t="str">
         <f aca="false">IF(OR(E11="",E11=0),"",F11/E11)</f>
         <v/>
       </c>
-      <c r="H11" s="54" t="str">
+      <c r="H11" s="66" t="str">
         <f aca="false">IF(E11="","",C11*E11)</f>
         <v/>
       </c>
-      <c r="I11" s="56" t="str">
+      <c r="I11" s="68" t="str">
         <f aca="false">IF(E11="","",C11*F11)</f>
         <v/>
       </c>
@@ -11255,10 +12180,10 @@
       <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="47" t="n">
+      <c r="B12" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="59" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
@@ -11266,12 +12191,12 @@
         <f aca="false">'프로젝트별 구성'!F44</f>
         <v>1449500</v>
       </c>
-      <c r="E12" s="48"/>
+      <c r="E12" s="60"/>
       <c r="F12" s="10" t="str">
         <f aca="false">IF(E12="","",E12-D12)</f>
         <v/>
       </c>
-      <c r="G12" s="49" t="str">
+      <c r="G12" s="61" t="str">
         <f aca="false">IF(OR(E12="",E12=0),"",F12/E12)</f>
         <v/>
       </c>
@@ -11285,33 +12210,33 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="s">
-        <v>157</v>
+      <c r="A15" s="70" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="59"/>
+      <c r="A17" s="71" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="71"/>
       <c r="C17" s="9" t="n">
         <f aca="false">C6*D6+C8*D8+C10*D10+C12*D12</f>
         <v>375362500</v>
@@ -11320,20 +12245,20 @@
         <f aca="false">IF((E6="")+(E8="")+(E10="")+(E12="")&gt;0,"타겟 "&amp;((E6="")+(E8="")+(E10="")+(E12=""))&amp;"건 미입력",H6+H8+H10+H12)</f>
         <v>타겟 4건 미입력</v>
       </c>
-      <c r="E17" s="60" t="str">
+      <c r="E17" s="72" t="str">
         <f aca="false">IF(ISNUMBER(D17),D17-C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="61" t="str">
+      <c r="F17" s="73" t="str">
         <f aca="false">IF(ISNUMBER(D17),E17/D17,"")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="59" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" s="59"/>
+      <c r="A18" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="71"/>
       <c r="C18" s="9" t="n">
         <f aca="false">C7*D7+C9*D9+C11*D11+C12*D12</f>
         <v>369962500</v>
@@ -11342,23 +12267,23 @@
         <f aca="false">IF((E7="")+(E9="")+(E11="")+(E12="")&gt;0,"타겟 "&amp;((E7="")+(E9="")+(E11="")+(E12=""))&amp;"건 미입력",H7+H9+H11+H12)</f>
         <v>타겟 4건 미입력</v>
       </c>
-      <c r="E18" s="60" t="str">
+      <c r="E18" s="72" t="str">
         <f aca="false">IF(ISNUMBER(D18),D18-C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="61" t="str">
+      <c r="F18" s="73" t="str">
         <f aca="false">IF(ISNUMBER(D18),E18/D18,"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="62" t="s">
-        <v>162</v>
+      <c r="A20" s="74" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="62" t="s">
-        <v>163</v>
+      <c r="A21" s="74" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -11403,81 +12328,81 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="46" t="s">
-        <v>164</v>
+      <c r="A1" s="58" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="65" t="s">
+      <c r="A5" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
+      <c r="A6" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="68" t="str">
+      <c r="A8" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="80" t="str">
         <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="9" t="n">
@@ -11490,30 +12415,30 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="70" t="n">
+      <c r="A9" s="81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="82" t="n">
         <f aca="false">SUM(F8:F8)</f>
         <v>392850</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="67" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="68" t="str">
+      <c r="A10" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="80" t="str">
         <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
@@ -11526,94 +12451,94 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="69" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="70" t="n">
+      <c r="A11" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="82" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>384750</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
+      <c r="A12" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="65" t="s">
+      <c r="A15" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="B15" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="B16" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
+      <c r="A16" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="B18" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="68" t="str">
+      <c r="A18" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="79" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="80" t="str">
         <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="9" t="n">
@@ -11626,30 +12551,30 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="70" t="n">
+      <c r="A19" s="81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82" t="n">
         <f aca="false">SUM(F18:F18)</f>
         <v>417600</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="B20" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="68" t="str">
+      <c r="A20" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="80" t="str">
         <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="9" t="n">
@@ -11662,94 +12587,94 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="69" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="70" t="n">
+      <c r="A21" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82" t="n">
         <f aca="false">SUM(F20:F20)</f>
         <v>406350</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="72" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
+      <c r="A22" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="B25" s="65" t="s">
+      <c r="A25" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="66" t="s">
-        <v>181</v>
-      </c>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
+      <c r="A26" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" s="78" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="B28" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" s="68" t="str">
+      <c r="A28" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="79" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="80" t="str">
         <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="9" t="n">
@@ -11762,15 +12687,15 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31"/>
-      <c r="B29" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" s="68" t="str">
+      <c r="A29" s="22"/>
+      <c r="B29" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29" s="80" t="str">
         <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="9" t="n">
@@ -11783,30 +12708,30 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="n">
+      <c r="A30" s="81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82" t="n">
         <f aca="false">SUM(F28:F29)</f>
         <v>531250</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="67" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31" s="68" t="str">
+      <c r="A31" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="80" t="str">
         <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="9" t="n">
@@ -11819,15 +12744,15 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31"/>
-      <c r="B32" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" s="68" t="str">
+      <c r="A32" s="22"/>
+      <c r="B32" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="80" t="str">
         <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D32" s="31" t="n">
+      <c r="D32" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="9" t="n">
@@ -11840,94 +12765,94 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="69" t="s">
-        <v>175</v>
-      </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="70" t="n">
+      <c r="A33" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82" t="n">
         <f aca="false">SUM(F31:F32)</f>
         <v>523150</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="71" t="s">
-        <v>183</v>
-      </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
+      <c r="A34" s="83" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="63" t="s">
+      <c r="A36" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="63"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="B37" s="65" t="s">
+      <c r="A37" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="66" t="s">
-        <v>184</v>
-      </c>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
+      <c r="A38" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="78" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="68" t="str">
+      <c r="A40" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="80" t="str">
         <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>CPU + 이더넷 (입력 14 / 출력 10)</v>
       </c>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="9" t="n">
@@ -11940,15 +12865,15 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="31"/>
-      <c r="B41" s="67" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="68" t="str">
+      <c r="A41" s="22"/>
+      <c r="B41" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="80" t="str">
         <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
-      <c r="D41" s="31" t="n">
+      <c r="D41" s="22" t="n">
         <v>6</v>
       </c>
       <c r="E41" s="9" t="n">
@@ -11961,15 +12886,15 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="31"/>
-      <c r="B42" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42" s="68" t="str">
+      <c r="A42" s="22"/>
+      <c r="B42" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="80" t="str">
         <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>릴레이 출력 16점</v>
       </c>
-      <c r="D42" s="31" t="n">
+      <c r="D42" s="22" t="n">
         <v>4</v>
       </c>
       <c r="E42" s="9" t="n">
@@ -11982,15 +12907,15 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="31"/>
-      <c r="B43" s="67" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="68" t="str">
+      <c r="A43" s="22"/>
+      <c r="B43" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="80" t="str">
         <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$22,3,FALSE())</f>
         <v>아날로그 출력 4CH</v>
       </c>
-      <c r="D43" s="31" t="n">
+      <c r="D43" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="9" t="n">
@@ -12003,27 +12928,27 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="70" t="n">
+      <c r="A44" s="81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="82" t="n">
         <f aca="false">SUM(F40:F43)</f>
         <v>1449500</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="72" t="s">
-        <v>186</v>
-      </c>
-      <c r="B45" s="72"/>
-      <c r="C45" s="72"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="72"/>
+      <c r="A45" s="84" t="s">
+        <v>205</v>
+      </c>
+      <c r="B45" s="84"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -12083,61 +13008,61 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
-        <v>187</v>
+      <c r="A1" s="40" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="73" t="n">
+      <c r="A3" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="85" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="73" t="n">
+      <c r="A4" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="85" t="n">
         <v>0.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>197</v>
+      <c r="B7" s="22" t="s">
+        <v>216</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -12151,11 +13076,11 @@
         <f aca="false">ROUND(C7*$B$4,0)</f>
         <v>349200</v>
       </c>
-      <c r="F7" s="74" t="n">
+      <c r="F7" s="86" t="n">
         <f aca="false">D7-E7</f>
         <v>43650</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="59" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -12163,16 +13088,16 @@
         <f aca="false">F7*G7</f>
         <v>10912500</v>
       </c>
-      <c r="I7" s="75" t="s">
-        <v>198</v>
+      <c r="I7" s="87" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="31" t="s">
+      <c r="A8" s="79" t="s">
         <v>197</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>216</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -12186,11 +13111,11 @@
         <f aca="false">ROUND(C8*$B$4,0)</f>
         <v>371200</v>
       </c>
-      <c r="F8" s="74" t="n">
+      <c r="F8" s="86" t="n">
         <f aca="false">D8-E8</f>
         <v>46400</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="59" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -12198,16 +13123,16 @@
         <f aca="false">F8*G8</f>
         <v>13920000</v>
       </c>
-      <c r="I8" s="75" t="s">
-        <v>199</v>
+      <c r="I8" s="87" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>197</v>
+      <c r="A9" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>216</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -12221,11 +13146,11 @@
         <f aca="false">ROUND(C9*$B$4,0)</f>
         <v>354400</v>
       </c>
-      <c r="F9" s="74" t="n">
+      <c r="F9" s="86" t="n">
         <f aca="false">D9-E9</f>
         <v>44300</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="59" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
@@ -12233,16 +13158,16 @@
         <f aca="false">F9*G9</f>
         <v>4430000</v>
       </c>
-      <c r="I9" s="75" t="s">
+      <c r="I9" s="87" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="67" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>200</v>
+      <c r="A10" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>219</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -12256,11 +13181,11 @@
         <f aca="false">ROUND(C10*$B$4,0)</f>
         <v>342000</v>
       </c>
-      <c r="F10" s="74" t="n">
+      <c r="F10" s="86" t="n">
         <f aca="false">D10-E10</f>
         <v>42750</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="59" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -12268,16 +13193,16 @@
         <f aca="false">F10*G10</f>
         <v>10687500</v>
       </c>
-      <c r="I10" s="75" t="s">
-        <v>201</v>
+      <c r="I10" s="87" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>200</v>
+      <c r="A11" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>219</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$22,4,FALSE())</f>
@@ -12291,11 +13216,11 @@
         <f aca="false">ROUND(C11*$B$4,0)</f>
         <v>361200</v>
       </c>
-      <c r="F11" s="74" t="n">
+      <c r="F11" s="86" t="n">
         <f aca="false">D11-E11</f>
         <v>45150</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="59" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -12303,43 +13228,43 @@
         <f aca="false">F11*G11</f>
         <v>13545000</v>
       </c>
-      <c r="I11" s="75" t="s">
-        <v>202</v>
+      <c r="I11" s="87" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="59" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
+      <c r="A13" s="71" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
       <c r="H13" s="16" t="n">
         <f aca="false">H7+H8+H9</f>
         <v>29262500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
+      <c r="A14" s="71" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
       <c r="H14" s="16" t="n">
         <f aca="false">H9+H10+H11</f>
         <v>28662500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="62" t="s">
-        <v>205</v>
+      <c r="A16" s="74" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -12375,55 +13300,55 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="46" t="s">
-        <v>206</v>
+      <c r="A1" s="58" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="n">
+      <c r="A5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>210</v>
+      <c r="B5" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="88" t="s">
+        <v>229</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>886000</v>
       </c>
-      <c r="F5" s="77" t="n">
+      <c r="F5" s="89" t="n">
         <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -12432,22 +13357,22 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="n">
+      <c r="A6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="76" t="s">
-        <v>211</v>
+      <c r="B6" s="79" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="88" t="s">
+        <v>230</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>873000</v>
       </c>
-      <c r="F6" s="77" t="n">
+      <c r="F6" s="89" t="n">
         <v>0.45</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -12456,22 +13381,22 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="76" t="s">
-        <v>212</v>
+      <c r="B7" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="88" t="s">
+        <v>231</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>855000</v>
       </c>
-      <c r="F7" s="77" t="n">
+      <c r="F7" s="89" t="n">
         <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -12480,22 +13405,22 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="79" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="76" t="s">
-        <v>213</v>
+      <c r="C8" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="88" t="s">
+        <v>232</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>928000</v>
       </c>
-      <c r="F8" s="77" t="n">
+      <c r="F8" s="89" t="n">
         <v>0.45</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -12504,22 +13429,22 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="n">
+      <c r="A9" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" s="76" t="s">
-        <v>214</v>
+      <c r="B9" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="88" t="s">
+        <v>233</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>903000</v>
       </c>
-      <c r="F9" s="77" t="n">
+      <c r="F9" s="89" t="n">
         <v>0.45</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -12528,22 +13453,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="n">
+      <c r="A10" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="67" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="78" t="s">
-        <v>216</v>
+      <c r="B10" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>234</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>228000</v>
       </c>
-      <c r="F10" s="77" t="n">
+      <c r="F10" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -12552,22 +13477,22 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="n">
+      <c r="A11" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="67" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>218</v>
+      <c r="B11" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>236</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>202000</v>
       </c>
-      <c r="F11" s="77" t="n">
+      <c r="F11" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -12576,22 +13501,22 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="n">
+      <c r="A12" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>219</v>
+      <c r="B12" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>237</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F12" s="77" t="n">
+      <c r="F12" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -12600,22 +13525,22 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="n">
+      <c r="A13" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="67" t="s">
-        <v>220</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>221</v>
+      <c r="B13" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>239</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F13" s="77" t="n">
+      <c r="F13" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -12624,22 +13549,22 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="67" t="s">
-        <v>222</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>223</v>
+      <c r="B14" s="79" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="90" t="s">
+        <v>241</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>213000</v>
       </c>
-      <c r="F14" s="77" t="n">
+      <c r="F14" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -12648,22 +13573,22 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>225</v>
+      <c r="B15" s="79" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="90" t="s">
+        <v>243</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>161000</v>
       </c>
-      <c r="F15" s="77" t="n">
+      <c r="F15" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -12672,22 +13597,22 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="n">
+      <c r="A16" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>227</v>
+      <c r="B16" s="79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="90" t="s">
+        <v>245</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F16" s="77" t="n">
+      <c r="F16" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -12696,22 +13621,22 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" s="78" t="s">
-        <v>229</v>
+      <c r="B17" s="79" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="90" t="s">
+        <v>247</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F17" s="77" t="n">
+      <c r="F17" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
@@ -12720,22 +13645,22 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="67" t="s">
-        <v>230</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" s="78" t="s">
-        <v>231</v>
+      <c r="B18" s="79" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="90" t="s">
+        <v>249</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>311000</v>
       </c>
-      <c r="F18" s="77" t="n">
+      <c r="F18" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -12744,22 +13669,22 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="31" t="n">
+      <c r="A19" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="67" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19" s="78" t="s">
-        <v>233</v>
+      <c r="B19" s="79" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="90" t="s">
+        <v>251</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>284000</v>
       </c>
-      <c r="F19" s="77" t="n">
+      <c r="F19" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -12768,22 +13693,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="n">
+      <c r="A20" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="67" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D20" s="78" t="s">
-        <v>235</v>
+      <c r="B20" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>253</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>331000</v>
       </c>
-      <c r="F20" s="77" t="n">
+      <c r="F20" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -12792,22 +13717,22 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="n">
+      <c r="A21" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D21" s="78" t="s">
-        <v>236</v>
+      <c r="B21" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="90" t="s">
+        <v>254</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>346000</v>
       </c>
-      <c r="F21" s="77" t="n">
+      <c r="F21" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -12816,22 +13741,22 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="67" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D22" s="78" t="s">
-        <v>237</v>
+      <c r="B22" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>255</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>351000</v>
       </c>
-      <c r="F22" s="77" t="n">
+      <c r="F22" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G22" s="10" t="n">

--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -9,9 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="요약" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="BOM 비교" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Schneider 제안 검토" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="마진 계산" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="마진 계산" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="BOM 비교" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Schneider 제안 검토" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="프로젝트별 구성" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="CPU 할인 효과" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="단가표" sheetId="7" state="visible" r:id="rId9"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="298">
   <si>
     <r>
       <rPr>
@@ -1987,7 +1987,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">BOM </t>
+      <t xml:space="preserve">LS </t>
     </r>
     <r>
       <rPr>
@@ -1997,7 +1997,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">비교 — </t>
+      <t xml:space="preserve">타겟 프라이스 → 우리 마진 </t>
     </r>
     <r>
       <rPr>
@@ -2008,7 +2008,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Schneider </t>
+      <t xml:space="preserve">&amp; </t>
     </r>
     <r>
       <rPr>
@@ -2018,8 +2018,1258 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원안 </t>
-    </r>
+      <t xml:space="preserve">필요한 추가 특가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: ① </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란 칸에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 프라이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력  ② 희망 마진율 입력  → 지금 마진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그리고 희망 마진을 남기려면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 얼마나 더 깎아야 하는지 바로 나옵니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">희망 마진율</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">← 우리가 남기고 싶은 마진율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매가 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예시로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 넣어 둠 — 바꾸세요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">① 지금 단가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 가격에 팔면</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">전원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 수량
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 프라이스
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 매입가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마진
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">마진율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 매출</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 마진</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← 마이너스면 빨간색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC220V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">② 희망 마진율을 남기려면 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 얼마나 더 받아야 하나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">허용 매입가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">더 깎아야 할 금액
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추가 할인율
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 매입가 대비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실효</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실효</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 추가 특가
+필요액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 허용 매입가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타겟 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× (1 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">희망 마진율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실효 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF = 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 매입가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 리스트가 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(CPU 0.45 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 섞인 평균 할인율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).  '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 요청할 수준입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 연간 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 프로젝트 전부</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">납품 방식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 매입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">희망 마진까지
+연간 추가 특가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC24V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 납품</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC220V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 납품 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC24V)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 매입가는 현재 할인율 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM3XTRA1/XREC1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 가격을 넣어야 매입가에 포함됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※ LS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 프로젝트별로 한 가격만 주면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC220V·DC24V </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">칸에 같은 값을 넣어 비교하세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -2029,7 +3279,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vs </t>
+      <t xml:space="preserve">BOM </t>
     </r>
     <r>
       <rPr>
@@ -2039,7 +3289,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수정본 </t>
+      <t xml:space="preserve">비교 — </t>
     </r>
     <r>
       <rPr>
@@ -2050,7 +3300,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">Schneider </t>
     </r>
     <r>
       <rPr>
@@ -2060,7 +3310,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">연간 수량 기준</t>
+      <t xml:space="preserve">원안 </t>
     </r>
     <r>
       <rPr>
@@ -2071,6 +3321,48 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정본 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 수량 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -3437,9 +4729,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">판정</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -7914,716 +9203,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">타겟 프라이스 → 우리 마진</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노란 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타겟 프라이스 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고객에게 파는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대 가격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 금액을 넣으면 마진이 바로 계산됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) TSU DC24V </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">칸에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">450,000 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마진 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타겟 프라이스 − 매입가     마진율 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마진 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타겟 프라이스 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판매가 기준</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">전원</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 수량
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">매입가
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타겟 프라이스
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마진
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">마진율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연간 매출</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연간 마진</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC24V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">← 마진이 마이너스면 빨간색</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC220V</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 합계 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 프로젝트 전부</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">납품 방식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연간 매입</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC24V</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 납품</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AC220V</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 납품 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(MCC</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC24V)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 연간 합계는 해당 납품 방식의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 칸을 모두 입력해야 나옵니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">프로젝트별 마진은 위 표에서 바로 확인하세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 매입가는 현재 할인율</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(CPU 0.45 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확장 모듈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.40) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. MCC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">버스 확장 부품은 매입가에 포함되어 있지 않습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -8877,7 +9456,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">금액</t>
+    <t xml:space="preserve">매입 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">매입 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리스트가 금액</t>
   </si>
   <si>
     <r>
@@ -10169,9 +10754,6 @@
       </rPr>
       <t xml:space="preserve">(DF)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">매입 단가</t>
   </si>
   <si>
     <r>
@@ -11188,14 +11770,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="\+#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0%;\-0.0%;\-"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11471,8 +12055,9 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1F3864"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -11492,9 +12077,25 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -11520,14 +12121,6 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1F3864"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
@@ -11566,6 +12159,14 @@
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
@@ -11652,11 +12253,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7F7F7F"/>
-        <bgColor rgb="FF808080"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -11676,21 +12277,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF808080"/>
       </bottom>
       <diagonal/>
     </border>
@@ -11733,7 +12319,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="105">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11890,6 +12476,82 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="42" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11898,20 +12560,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -11934,15 +12588,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11950,11 +12604,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11970,11 +12624,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11982,7 +12636,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11998,11 +12652,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12014,79 +12668,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12094,24 +12684,28 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="54" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -12122,7 +12716,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12130,7 +12724,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12138,11 +12732,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="58" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="59" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12155,7 +12749,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="맑은 고딕"/>
@@ -12164,6 +12758,34 @@
         <b val="1"/>
         <color rgb="FFC00000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -12192,7 +12814,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
@@ -12224,7 +12846,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -12817,8 +13439,8 @@
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="str">
-        <f aca="false">"⑧ 연간 마진 (DC24V 납품): "&amp;IF(ISNUMBER('마진 계산'!E17),TEXT('마진 계산'!E17,"#,##0")&amp;"원  (마진율 "&amp;TEXT('마진 계산'!F17,"0.0%")&amp;")","타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
-        <v>⑧ 연간 마진 (DC24V 납품): 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다</v>
+        <f aca="false">"⑧ LS 타겟 기준 연간 마진 (DC24V): "&amp;IF(ISNUMBER('마진 계산'!E30),TEXT('마진 계산'!E30,"#,##0")&amp;"원 (마진율 "&amp;TEXT('마진 계산'!F30,"0.0%")&amp;")  /  희망 마진("&amp;TEXT('마진 계산'!B4,"0%")&amp;")까지 연간 추가 특가 "&amp;TEXT('마진 계산'!G30,"#,##0")&amp;"원 필요","LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
+        <v>⑧ LS 타겟 기준 연간 마진 (DC24V): LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다</v>
       </c>
       <c r="B29" s="36"/>
       <c r="C29" s="36"/>
@@ -12869,6 +13491,758 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="42" t="n">
+        <f aca="false">요약!C6</f>
+        <v>200</v>
+      </c>
+      <c r="D8" s="43"/>
+      <c r="E8" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F9</f>
+        <v>392850</v>
+      </c>
+      <c r="F8" s="44" t="str">
+        <f aca="false">IF(D8="","",D8-E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="45" t="str">
+        <f aca="false">IF(OR(D8="",D8=0),"",F8/D8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f aca="false">IF(D8="","",C8*D8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="44" t="str">
+        <f aca="false">IF(D8="","",C8*F8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="42" t="n">
+        <f aca="false">요약!C6</f>
+        <v>200</v>
+      </c>
+      <c r="D9" s="43"/>
+      <c r="E9" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F11</f>
+        <v>384750</v>
+      </c>
+      <c r="F9" s="44" t="str">
+        <f aca="false">IF(D9="","",D9-E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="45" t="str">
+        <f aca="false">IF(OR(D9="",D9=0),"",F9/D9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9" t="str">
+        <f aca="false">IF(D9="","",C9*D9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="44" t="str">
+        <f aca="false">IF(D9="","",C9*F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="42" t="n">
+        <f aca="false">요약!C7</f>
+        <v>300</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F19</f>
+        <v>417600</v>
+      </c>
+      <c r="F10" s="44" t="str">
+        <f aca="false">IF(D10="","",D10-E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="45" t="str">
+        <f aca="false">IF(OR(D10="",D10=0),"",F10/D10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f aca="false">IF(D10="","",C10*D10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="44" t="str">
+        <f aca="false">IF(D10="","",C10*F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="42" t="n">
+        <f aca="false">요약!C7</f>
+        <v>300</v>
+      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F21</f>
+        <v>406350</v>
+      </c>
+      <c r="F11" s="44" t="str">
+        <f aca="false">IF(D11="","",D11-E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="45" t="str">
+        <f aca="false">IF(OR(D11="",D11=0),"",F11/D11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f aca="false">IF(D11="","",C11*D11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="44" t="str">
+        <f aca="false">IF(D11="","",C11*F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="42" t="n">
+        <f aca="false">요약!C8</f>
+        <v>50</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F30</f>
+        <v>531250</v>
+      </c>
+      <c r="F12" s="44" t="str">
+        <f aca="false">IF(D12="","",D12-E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="45" t="str">
+        <f aca="false">IF(OR(D12="",D12=0),"",F12/D12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f aca="false">IF(D12="","",C12*D12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="44" t="str">
+        <f aca="false">IF(D12="","",C12*F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="42" t="n">
+        <f aca="false">요약!C8</f>
+        <v>50</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F33</f>
+        <v>523150</v>
+      </c>
+      <c r="F13" s="44" t="str">
+        <f aca="false">IF(D13="","",D13-E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="45" t="str">
+        <f aca="false">IF(OR(D13="",D13=0),"",F13/D13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="9" t="str">
+        <f aca="false">IF(D13="","",C13*D13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="44" t="str">
+        <f aca="false">IF(D13="","",C13*F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="42" t="n">
+        <f aca="false">요약!C9</f>
+        <v>100</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="9" t="n">
+        <f aca="false">'프로젝트별 구성'!F46</f>
+        <v>1449500</v>
+      </c>
+      <c r="F14" s="44" t="str">
+        <f aca="false">IF(D14="","",D14-E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="45" t="str">
+        <f aca="false">IF(OR(D14="",D14=0),"",F14/D14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="9" t="str">
+        <f aca="false">IF(D14="","",C14*D14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="44" t="str">
+        <f aca="false">IF(D14="","",C14*F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="9" t="str">
+        <f aca="false">IF(D8="","",ROUND(D8*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D19" s="9" t="n">
+        <f aca="false">E8</f>
+        <v>392850</v>
+      </c>
+      <c r="E19" s="47" t="str">
+        <f aca="false">IF(C19="","",MAX(D19-C19,0))</f>
+        <v/>
+      </c>
+      <c r="F19" s="48" t="str">
+        <f aca="false">IF(C19="","",E19/D19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="49" t="n">
+        <f aca="false">IFERROR(D19/'프로젝트별 구성'!G9,"")</f>
+        <v>0.45</v>
+      </c>
+      <c r="H19" s="50" t="str">
+        <f aca="false">IF(C19="","",IFERROR(MIN(C19,D19)/'프로젝트별 구성'!G9,""))</f>
+        <v/>
+      </c>
+      <c r="I19" s="10" t="str">
+        <f aca="false">IF(C19="","",E19*C8)</f>
+        <v/>
+      </c>
+      <c r="J19" s="51" t="str">
+        <f aca="false">IF(C19="","타겟 입력 전",IF(E19=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="9" t="str">
+        <f aca="false">IF(D9="","",ROUND(D9*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D20" s="9" t="n">
+        <f aca="false">E9</f>
+        <v>384750</v>
+      </c>
+      <c r="E20" s="47" t="str">
+        <f aca="false">IF(C20="","",MAX(D20-C20,0))</f>
+        <v/>
+      </c>
+      <c r="F20" s="48" t="str">
+        <f aca="false">IF(C20="","",E20/D20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="49" t="n">
+        <f aca="false">IFERROR(D20/'프로젝트별 구성'!G11,"")</f>
+        <v>0.45</v>
+      </c>
+      <c r="H20" s="50" t="str">
+        <f aca="false">IF(C20="","",IFERROR(MIN(C20,D20)/'프로젝트별 구성'!G11,""))</f>
+        <v/>
+      </c>
+      <c r="I20" s="10" t="str">
+        <f aca="false">IF(C20="","",E20*C9)</f>
+        <v/>
+      </c>
+      <c r="J20" s="51" t="str">
+        <f aca="false">IF(C20="","타겟 입력 전",IF(E20=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="9" t="str">
+        <f aca="false">IF(D10="","",ROUND(D10*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D21" s="9" t="n">
+        <f aca="false">E10</f>
+        <v>417600</v>
+      </c>
+      <c r="E21" s="47" t="str">
+        <f aca="false">IF(C21="","",MAX(D21-C21,0))</f>
+        <v/>
+      </c>
+      <c r="F21" s="48" t="str">
+        <f aca="false">IF(C21="","",E21/D21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="49" t="n">
+        <f aca="false">IFERROR(D21/'프로젝트별 구성'!G19,"")</f>
+        <v>0.45</v>
+      </c>
+      <c r="H21" s="50" t="str">
+        <f aca="false">IF(C21="","",IFERROR(MIN(C21,D21)/'프로젝트별 구성'!G19,""))</f>
+        <v/>
+      </c>
+      <c r="I21" s="10" t="str">
+        <f aca="false">IF(C21="","",E21*C10)</f>
+        <v/>
+      </c>
+      <c r="J21" s="51" t="str">
+        <f aca="false">IF(C21="","타겟 입력 전",IF(E21=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="9" t="str">
+        <f aca="false">IF(D11="","",ROUND(D11*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D22" s="9" t="n">
+        <f aca="false">E11</f>
+        <v>406350</v>
+      </c>
+      <c r="E22" s="47" t="str">
+        <f aca="false">IF(C22="","",MAX(D22-C22,0))</f>
+        <v/>
+      </c>
+      <c r="F22" s="48" t="str">
+        <f aca="false">IF(C22="","",E22/D22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="49" t="n">
+        <f aca="false">IFERROR(D22/'프로젝트별 구성'!G21,"")</f>
+        <v>0.45</v>
+      </c>
+      <c r="H22" s="50" t="str">
+        <f aca="false">IF(C22="","",IFERROR(MIN(C22,D22)/'프로젝트별 구성'!G21,""))</f>
+        <v/>
+      </c>
+      <c r="I22" s="10" t="str">
+        <f aca="false">IF(C22="","",E22*C11)</f>
+        <v/>
+      </c>
+      <c r="J22" s="51" t="str">
+        <f aca="false">IF(C22="","타겟 입력 전",IF(E22=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="9" t="str">
+        <f aca="false">IF(D12="","",ROUND(D12*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D23" s="9" t="n">
+        <f aca="false">E12</f>
+        <v>531250</v>
+      </c>
+      <c r="E23" s="47" t="str">
+        <f aca="false">IF(C23="","",MAX(D23-C23,0))</f>
+        <v/>
+      </c>
+      <c r="F23" s="48" t="str">
+        <f aca="false">IF(C23="","",E23/D23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="49" t="n">
+        <f aca="false">IFERROR(D23/'프로젝트별 구성'!G30,"")</f>
+        <v>0.435808039376538</v>
+      </c>
+      <c r="H23" s="50" t="str">
+        <f aca="false">IF(C23="","",IFERROR(MIN(C23,D23)/'프로젝트별 구성'!G30,""))</f>
+        <v/>
+      </c>
+      <c r="I23" s="10" t="str">
+        <f aca="false">IF(C23="","",E23*C12)</f>
+        <v/>
+      </c>
+      <c r="J23" s="51" t="str">
+        <f aca="false">IF(C23="","타겟 입력 전",IF(E23=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="9" t="str">
+        <f aca="false">IF(D13="","",ROUND(D13*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D24" s="9" t="n">
+        <f aca="false">E13</f>
+        <v>523150</v>
+      </c>
+      <c r="E24" s="47" t="str">
+        <f aca="false">IF(C24="","",MAX(D24-C24,0))</f>
+        <v/>
+      </c>
+      <c r="F24" s="48" t="str">
+        <f aca="false">IF(C24="","",E24/D24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="49" t="n">
+        <f aca="false">IFERROR(D24/'프로젝트별 구성'!G33,"")</f>
+        <v>0.435595337218984</v>
+      </c>
+      <c r="H24" s="50" t="str">
+        <f aca="false">IF(C24="","",IFERROR(MIN(C24,D24)/'프로젝트별 구성'!G33,""))</f>
+        <v/>
+      </c>
+      <c r="I24" s="10" t="str">
+        <f aca="false">IF(C24="","",E24*C13)</f>
+        <v/>
+      </c>
+      <c r="J24" s="51" t="str">
+        <f aca="false">IF(C24="","타겟 입력 전",IF(E24=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="9" t="str">
+        <f aca="false">IF(D14="","",ROUND(D14*(1-$B$4),0))</f>
+        <v/>
+      </c>
+      <c r="D25" s="9" t="n">
+        <f aca="false">E14</f>
+        <v>1449500</v>
+      </c>
+      <c r="E25" s="47" t="str">
+        <f aca="false">IF(C25="","",MAX(D25-C25,0))</f>
+        <v/>
+      </c>
+      <c r="F25" s="48" t="str">
+        <f aca="false">IF(C25="","",E25/D25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="49" t="n">
+        <f aca="false">IFERROR(D25/'프로젝트별 구성'!G46,"")</f>
+        <v>0.412610304582978</v>
+      </c>
+      <c r="H25" s="50" t="str">
+        <f aca="false">IF(C25="","",IFERROR(MIN(C25,D25)/'프로젝트별 구성'!G46,""))</f>
+        <v/>
+      </c>
+      <c r="I25" s="10" t="str">
+        <f aca="false">IF(C25="","",E25*C14)</f>
+        <v/>
+      </c>
+      <c r="J25" s="51" t="str">
+        <f aca="false">IF(C25="","타겟 입력 전",IF(E25=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
+        <v>타겟 입력 전</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="41" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="52"/>
+      <c r="C30" s="9" t="n">
+        <f aca="false">C8*E8+C10*E10+C12*E12+C14*E14</f>
+        <v>375362500</v>
+      </c>
+      <c r="D30" s="9" t="str">
+        <f aca="false">IF((D8="")+(D10="")+(D12="")+(D14="")&gt;0,"타겟 "&amp;((D8="")+(D10="")+(D12="")+(D14=""))&amp;"건 미입력",H8+H10+H12+H14)</f>
+        <v>타겟 4건 미입력</v>
+      </c>
+      <c r="E30" s="53" t="str">
+        <f aca="false">IF(ISNUMBER(D30),D30-C30,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="54" t="str">
+        <f aca="false">IF(ISNUMBER(D30),E30/D30,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="55" t="str">
+        <f aca="false">IF(ISNUMBER(D30),I19+I21+I23+I25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="52"/>
+      <c r="C31" s="9" t="n">
+        <f aca="false">C9*E9+C11*E11+C13*E13+C14*E14</f>
+        <v>369962500</v>
+      </c>
+      <c r="D31" s="9" t="str">
+        <f aca="false">IF((D9="")+(D11="")+(D13="")+(D14="")&gt;0,"타겟 "&amp;((D9="")+(D11="")+(D13="")+(D14=""))&amp;"건 미입력",H9+H11+H13+H14)</f>
+        <v>타겟 4건 미입력</v>
+      </c>
+      <c r="E31" s="53" t="str">
+        <f aca="false">IF(ISNUMBER(D31),D31-C31,"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="54" t="str">
+        <f aca="false">IF(ISNUMBER(D31),E31/D31,"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="55" t="str">
+        <f aca="false">IF(ISNUMBER(D31),I20+I22+I24+I25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="57" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F8:I14">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(F8),F8&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:J25">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>J19="추가 특가 필요"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>LEFT(J19,2)="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:F31">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(E30),E30&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -12886,54 +14260,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="s">
-        <v>49</v>
+      <c r="A4" s="58" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="s">
-        <v>60</v>
+      <c r="A6" s="59" t="s">
+        <v>93</v>
       </c>
       <c r="B6" s="7" t="str">
         <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -12943,7 +14317,7 @@
         <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>392850</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -12951,7 +14325,7 @@
         <f aca="false">C6*D6</f>
         <v>98212500</v>
       </c>
-      <c r="F6" s="42" t="n">
+      <c r="F6" s="60" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -12959,7 +14333,7 @@
         <f aca="false">C6*F6</f>
         <v>98212500</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="61" t="n">
         <f aca="false">F6-D6</f>
         <v>0</v>
       </c>
@@ -12967,13 +14341,13 @@
         <f aca="false">G6-E6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="45" t="s">
-        <v>61</v>
+      <c r="J6" s="62" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="s">
-        <v>62</v>
+      <c r="A7" s="59" t="s">
+        <v>95</v>
       </c>
       <c r="B7" s="7" t="str">
         <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -12983,7 +14357,7 @@
         <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>417600</v>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="42" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -12991,7 +14365,7 @@
         <f aca="false">C7*D7</f>
         <v>125280000</v>
       </c>
-      <c r="F7" s="42" t="n">
+      <c r="F7" s="60" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -12999,7 +14373,7 @@
         <f aca="false">C7*F7</f>
         <v>125280000</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="61" t="n">
         <f aca="false">F7-D7</f>
         <v>0</v>
       </c>
@@ -13007,13 +14381,13 @@
         <f aca="false">G7-E7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="45" t="s">
-        <v>63</v>
+      <c r="J7" s="62" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="40" t="s">
-        <v>64</v>
+      <c r="A8" s="59" t="s">
+        <v>97</v>
       </c>
       <c r="B8" s="7" t="str">
         <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13023,7 +14397,7 @@
         <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>423450</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13031,14 +14405,14 @@
         <f aca="false">C8*D8</f>
         <v>42345000</v>
       </c>
-      <c r="F8" s="42" t="n">
+      <c r="F8" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <f aca="false">C8*F8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="43" t="n">
+      <c r="H8" s="61" t="n">
         <f aca="false">F8-D8</f>
         <v>-100</v>
       </c>
@@ -13047,12 +14421,12 @@
         <v>-42345000</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40" t="s">
-        <v>66</v>
+      <c r="A9" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="B9" s="7" t="str">
         <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13062,14 +14436,14 @@
         <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>398700</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">C9*D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="42" t="n">
+      <c r="F9" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13077,7 +14451,7 @@
         <f aca="false">C9*F9</f>
         <v>39870000</v>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="61" t="n">
         <f aca="false">F9-D9</f>
         <v>100</v>
       </c>
@@ -13086,12 +14460,12 @@
         <v>39870000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="s">
-        <v>68</v>
+      <c r="A10" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="B10" s="7" t="str">
         <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13101,7 +14475,7 @@
         <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>91200</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="42" t="n">
         <f aca="false">2*요약!$C$9</f>
         <v>200</v>
       </c>
@@ -13109,7 +14483,7 @@
         <f aca="false">C10*D10</f>
         <v>18240000</v>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="60" t="n">
         <f aca="false">6*요약!$C$9</f>
         <v>600</v>
       </c>
@@ -13117,7 +14491,7 @@
         <f aca="false">C10*F10</f>
         <v>54720000</v>
       </c>
-      <c r="H10" s="43" t="n">
+      <c r="H10" s="61" t="n">
         <f aca="false">F10-D10</f>
         <v>400</v>
       </c>
@@ -13126,12 +14500,12 @@
         <v>36480000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="40" t="s">
-        <v>70</v>
+      <c r="A11" s="59" t="s">
+        <v>103</v>
       </c>
       <c r="B11" s="7" t="str">
         <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13141,7 +14515,7 @@
         <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>80800</v>
       </c>
-      <c r="D11" s="41" t="n">
+      <c r="D11" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13149,14 +14523,14 @@
         <f aca="false">C11*D11</f>
         <v>8080000</v>
       </c>
-      <c r="F11" s="42" t="n">
+      <c r="F11" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
         <f aca="false">C11*F11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="61" t="n">
         <f aca="false">F11-D11</f>
         <v>-100</v>
       </c>
@@ -13165,12 +14539,12 @@
         <v>-8080000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
-        <v>72</v>
+      <c r="A12" s="59" t="s">
+        <v>105</v>
       </c>
       <c r="B12" s="7" t="str">
         <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13180,14 +14554,14 @@
         <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>90800</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">C12*D12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="42" t="n">
+      <c r="F12" s="60" t="n">
         <f aca="false">4*요약!$C$9</f>
         <v>400</v>
       </c>
@@ -13195,7 +14569,7 @@
         <f aca="false">C12*F12</f>
         <v>36320000</v>
       </c>
-      <c r="H12" s="43" t="n">
+      <c r="H12" s="61" t="n">
         <f aca="false">F12-D12</f>
         <v>400</v>
       </c>
@@ -13204,12 +14578,12 @@
         <v>36320000</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="40" t="s">
-        <v>74</v>
+      <c r="A13" s="59" t="s">
+        <v>107</v>
       </c>
       <c r="B13" s="7" t="str">
         <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13219,7 +14593,7 @@
         <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>90800</v>
       </c>
-      <c r="D13" s="41" t="n">
+      <c r="D13" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13227,14 +14601,14 @@
         <f aca="false">C13*D13</f>
         <v>9080000</v>
       </c>
-      <c r="F13" s="42" t="n">
+      <c r="F13" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <f aca="false">C13*F13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="61" t="n">
         <f aca="false">F13-D13</f>
         <v>-100</v>
       </c>
@@ -13243,12 +14617,12 @@
         <v>-9080000</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="s">
-        <v>76</v>
+      <c r="A14" s="59" t="s">
+        <v>109</v>
       </c>
       <c r="B14" s="7" t="str">
         <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13258,7 +14632,7 @@
         <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>67200</v>
       </c>
-      <c r="D14" s="41" t="n">
+      <c r="D14" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13266,14 +14640,14 @@
         <f aca="false">C14*D14</f>
         <v>6720000</v>
       </c>
-      <c r="F14" s="42" t="n">
+      <c r="F14" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <f aca="false">C14*F14</f>
         <v>0</v>
       </c>
-      <c r="H14" s="43" t="n">
+      <c r="H14" s="61" t="n">
         <f aca="false">F14-D14</f>
         <v>-100</v>
       </c>
@@ -13282,12 +14656,12 @@
         <v>-6720000</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="40" t="s">
-        <v>77</v>
+      <c r="A15" s="59" t="s">
+        <v>110</v>
       </c>
       <c r="B15" s="7" t="str">
         <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13297,7 +14671,7 @@
         <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>138400</v>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D15" s="42" t="n">
         <f aca="false">1*요약!$C$8+1*요약!$C$9</f>
         <v>150</v>
       </c>
@@ -13305,7 +14679,7 @@
         <f aca="false">C15*D15</f>
         <v>20760000</v>
       </c>
-      <c r="F15" s="42" t="n">
+      <c r="F15" s="60" t="n">
         <f aca="false">1*요약!$C$8</f>
         <v>50</v>
       </c>
@@ -13313,7 +14687,7 @@
         <f aca="false">C15*F15</f>
         <v>6920000</v>
       </c>
-      <c r="H15" s="43" t="n">
+      <c r="H15" s="61" t="n">
         <f aca="false">F15-D15</f>
         <v>-100</v>
       </c>
@@ -13322,12 +14696,12 @@
         <v>-13840000</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="s">
-        <v>79</v>
+      <c r="A16" s="59" t="s">
+        <v>112</v>
       </c>
       <c r="B16" s="7" t="str">
         <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13337,14 +14711,14 @@
         <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>140400</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="42" t="n">
+      <c r="F16" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13352,7 +14726,7 @@
         <f aca="false">C16*F16</f>
         <v>14040000</v>
       </c>
-      <c r="H16" s="43" t="n">
+      <c r="H16" s="61" t="n">
         <f aca="false">F16-D16</f>
         <v>100</v>
       </c>
@@ -13361,12 +14735,12 @@
         <v>14040000</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40" t="s">
-        <v>81</v>
+      <c r="A17" s="59" t="s">
+        <v>114</v>
       </c>
       <c r="B17" s="7" t="str">
         <f aca="false">VLOOKUP(A17,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13376,14 +14750,14 @@
         <f aca="false">VLOOKUP(A17,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>0</v>
       </c>
-      <c r="D17" s="41" t="n">
+      <c r="D17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">C17*D17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="42" t="n">
+      <c r="F17" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13391,7 +14765,7 @@
         <f aca="false">C17*F17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="43" t="n">
+      <c r="H17" s="61" t="n">
         <f aca="false">F17-D17</f>
         <v>100</v>
       </c>
@@ -13400,12 +14774,12 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="40" t="s">
-        <v>83</v>
+      <c r="A18" s="59" t="s">
+        <v>116</v>
       </c>
       <c r="B18" s="7" t="str">
         <f aca="false">VLOOKUP(A18,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13415,14 +14789,14 @@
         <f aca="false">VLOOKUP(A18,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>0</v>
       </c>
-      <c r="D18" s="41" t="n">
+      <c r="D18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">C18*D18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="42" t="n">
+      <c r="F18" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13430,7 +14804,7 @@
         <f aca="false">C18*F18</f>
         <v>0</v>
       </c>
-      <c r="H18" s="43" t="n">
+      <c r="H18" s="61" t="n">
         <f aca="false">F18-D18</f>
         <v>100</v>
       </c>
@@ -13439,7 +14813,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13448,75 +14822,75 @@
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="63" t="n">
         <f aca="false">SUM(D6:D18)</f>
         <v>1300</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="64" t="n">
         <f aca="false">SUM(E6:E18)</f>
         <v>328717500</v>
       </c>
-      <c r="F19" s="46" t="n">
+      <c r="F19" s="63" t="n">
         <f aca="false">SUM(F6:F18)</f>
         <v>2000</v>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="64" t="n">
         <f aca="false">SUM(G6:G18)</f>
         <v>375362500</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="65" t="n">
         <f aca="false">SUM(H6:H18)</f>
         <v>700</v>
       </c>
-      <c r="I19" s="49" t="n">
+      <c r="I19" s="66" t="n">
         <f aca="false">SUM(I6:I18)</f>
         <v>46645000</v>
       </c>
-      <c r="J19" s="50" t="str">
+      <c r="J19" s="67" t="str">
         <f aca="false">IF(E19=0,"","증감률 "&amp;TEXT(I19/E19,"+0.0%;-0.0%"))</f>
         <v>증감률 +14.2%</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="s">
-        <v>84</v>
+      <c r="A21" s="58" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40" t="s">
-        <v>85</v>
+      <c r="A23" s="59" t="s">
+        <v>118</v>
       </c>
       <c r="B23" s="7" t="str">
         <f aca="false">VLOOKUP(A23,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13526,7 +14900,7 @@
         <f aca="false">VLOOKUP(A23,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>384750</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="42" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -13534,7 +14908,7 @@
         <f aca="false">C23*D23</f>
         <v>96187500</v>
       </c>
-      <c r="F23" s="42" t="n">
+      <c r="F23" s="60" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -13542,7 +14916,7 @@
         <f aca="false">C23*F23</f>
         <v>96187500</v>
       </c>
-      <c r="H23" s="43" t="n">
+      <c r="H23" s="61" t="n">
         <f aca="false">F23-D23</f>
         <v>0</v>
       </c>
@@ -13550,13 +14924,13 @@
         <f aca="false">G23-E23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="45" t="s">
-        <v>61</v>
+      <c r="J23" s="62" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40" t="s">
-        <v>86</v>
+      <c r="A24" s="59" t="s">
+        <v>119</v>
       </c>
       <c r="B24" s="7" t="str">
         <f aca="false">VLOOKUP(A24,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13566,7 +14940,7 @@
         <f aca="false">VLOOKUP(A24,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>406350</v>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="42" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -13574,7 +14948,7 @@
         <f aca="false">C24*D24</f>
         <v>121905000</v>
       </c>
-      <c r="F24" s="42" t="n">
+      <c r="F24" s="60" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -13582,7 +14956,7 @@
         <f aca="false">C24*F24</f>
         <v>121905000</v>
       </c>
-      <c r="H24" s="43" t="n">
+      <c r="H24" s="61" t="n">
         <f aca="false">F24-D24</f>
         <v>0</v>
       </c>
@@ -13590,13 +14964,13 @@
         <f aca="false">G24-E24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="45" t="s">
-        <v>63</v>
+      <c r="J24" s="62" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="40" t="s">
-        <v>64</v>
+      <c r="A25" s="59" t="s">
+        <v>97</v>
       </c>
       <c r="B25" s="7" t="str">
         <f aca="false">VLOOKUP(A25,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13606,7 +14980,7 @@
         <f aca="false">VLOOKUP(A25,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>423450</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13614,14 +14988,14 @@
         <f aca="false">C25*D25</f>
         <v>42345000</v>
       </c>
-      <c r="F25" s="42" t="n">
+      <c r="F25" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="10" t="n">
         <f aca="false">C25*F25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="43" t="n">
+      <c r="H25" s="61" t="n">
         <f aca="false">F25-D25</f>
         <v>-100</v>
       </c>
@@ -13630,12 +15004,12 @@
         <v>-42345000</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40" t="s">
-        <v>66</v>
+      <c r="A26" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="B26" s="7" t="str">
         <f aca="false">VLOOKUP(A26,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13645,14 +15019,14 @@
         <f aca="false">VLOOKUP(A26,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>398700</v>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
         <f aca="false">C26*D26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="42" t="n">
+      <c r="F26" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13660,7 +15034,7 @@
         <f aca="false">C26*F26</f>
         <v>39870000</v>
       </c>
-      <c r="H26" s="43" t="n">
+      <c r="H26" s="61" t="n">
         <f aca="false">F26-D26</f>
         <v>100</v>
       </c>
@@ -13669,12 +15043,12 @@
         <v>39870000</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="40" t="s">
-        <v>68</v>
+      <c r="A27" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="B27" s="7" t="str">
         <f aca="false">VLOOKUP(A27,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13684,7 +15058,7 @@
         <f aca="false">VLOOKUP(A27,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>91200</v>
       </c>
-      <c r="D27" s="41" t="n">
+      <c r="D27" s="42" t="n">
         <f aca="false">2*요약!$C$9</f>
         <v>200</v>
       </c>
@@ -13692,7 +15066,7 @@
         <f aca="false">C27*D27</f>
         <v>18240000</v>
       </c>
-      <c r="F27" s="42" t="n">
+      <c r="F27" s="60" t="n">
         <f aca="false">6*요약!$C$9</f>
         <v>600</v>
       </c>
@@ -13700,7 +15074,7 @@
         <f aca="false">C27*F27</f>
         <v>54720000</v>
       </c>
-      <c r="H27" s="43" t="n">
+      <c r="H27" s="61" t="n">
         <f aca="false">F27-D27</f>
         <v>400</v>
       </c>
@@ -13709,12 +15083,12 @@
         <v>36480000</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="s">
-        <v>70</v>
+      <c r="A28" s="59" t="s">
+        <v>103</v>
       </c>
       <c r="B28" s="7" t="str">
         <f aca="false">VLOOKUP(A28,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13724,7 +15098,7 @@
         <f aca="false">VLOOKUP(A28,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>80800</v>
       </c>
-      <c r="D28" s="41" t="n">
+      <c r="D28" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13732,14 +15106,14 @@
         <f aca="false">C28*D28</f>
         <v>8080000</v>
       </c>
-      <c r="F28" s="42" t="n">
+      <c r="F28" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="10" t="n">
         <f aca="false">C28*F28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="43" t="n">
+      <c r="H28" s="61" t="n">
         <f aca="false">F28-D28</f>
         <v>-100</v>
       </c>
@@ -13748,12 +15122,12 @@
         <v>-8080000</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40" t="s">
-        <v>72</v>
+      <c r="A29" s="59" t="s">
+        <v>105</v>
       </c>
       <c r="B29" s="7" t="str">
         <f aca="false">VLOOKUP(A29,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13763,14 +15137,14 @@
         <f aca="false">VLOOKUP(A29,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>90800</v>
       </c>
-      <c r="D29" s="41" t="n">
+      <c r="D29" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">C29*D29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="42" t="n">
+      <c r="F29" s="60" t="n">
         <f aca="false">4*요약!$C$9</f>
         <v>400</v>
       </c>
@@ -13778,7 +15152,7 @@
         <f aca="false">C29*F29</f>
         <v>36320000</v>
       </c>
-      <c r="H29" s="43" t="n">
+      <c r="H29" s="61" t="n">
         <f aca="false">F29-D29</f>
         <v>400</v>
       </c>
@@ -13787,12 +15161,12 @@
         <v>36320000</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40" t="s">
-        <v>74</v>
+      <c r="A30" s="59" t="s">
+        <v>107</v>
       </c>
       <c r="B30" s="7" t="str">
         <f aca="false">VLOOKUP(A30,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13802,7 +15176,7 @@
         <f aca="false">VLOOKUP(A30,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>90800</v>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D30" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13810,14 +15184,14 @@
         <f aca="false">C30*D30</f>
         <v>9080000</v>
       </c>
-      <c r="F30" s="42" t="n">
+      <c r="F30" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="10" t="n">
         <f aca="false">C30*F30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="43" t="n">
+      <c r="H30" s="61" t="n">
         <f aca="false">F30-D30</f>
         <v>-100</v>
       </c>
@@ -13826,12 +15200,12 @@
         <v>-9080000</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="40" t="s">
-        <v>76</v>
+      <c r="A31" s="59" t="s">
+        <v>109</v>
       </c>
       <c r="B31" s="7" t="str">
         <f aca="false">VLOOKUP(A31,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13841,7 +15215,7 @@
         <f aca="false">VLOOKUP(A31,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>67200</v>
       </c>
-      <c r="D31" s="41" t="n">
+      <c r="D31" s="42" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13849,14 +15223,14 @@
         <f aca="false">C31*D31</f>
         <v>6720000</v>
       </c>
-      <c r="F31" s="42" t="n">
+      <c r="F31" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="10" t="n">
         <f aca="false">C31*F31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="43" t="n">
+      <c r="H31" s="61" t="n">
         <f aca="false">F31-D31</f>
         <v>-100</v>
       </c>
@@ -13865,12 +15239,12 @@
         <v>-6720000</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40" t="s">
-        <v>77</v>
+      <c r="A32" s="59" t="s">
+        <v>110</v>
       </c>
       <c r="B32" s="7" t="str">
         <f aca="false">VLOOKUP(A32,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13880,7 +15254,7 @@
         <f aca="false">VLOOKUP(A32,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>138400</v>
       </c>
-      <c r="D32" s="41" t="n">
+      <c r="D32" s="42" t="n">
         <f aca="false">1*요약!$C$8+1*요약!$C$9</f>
         <v>150</v>
       </c>
@@ -13888,7 +15262,7 @@
         <f aca="false">C32*D32</f>
         <v>20760000</v>
       </c>
-      <c r="F32" s="42" t="n">
+      <c r="F32" s="60" t="n">
         <f aca="false">1*요약!$C$8</f>
         <v>50</v>
       </c>
@@ -13896,7 +15270,7 @@
         <f aca="false">C32*F32</f>
         <v>6920000</v>
       </c>
-      <c r="H32" s="43" t="n">
+      <c r="H32" s="61" t="n">
         <f aca="false">F32-D32</f>
         <v>-100</v>
       </c>
@@ -13905,12 +15279,12 @@
         <v>-13840000</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="40" t="s">
-        <v>79</v>
+      <c r="A33" s="59" t="s">
+        <v>112</v>
       </c>
       <c r="B33" s="7" t="str">
         <f aca="false">VLOOKUP(A33,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13920,14 +15294,14 @@
         <f aca="false">VLOOKUP(A33,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>140400</v>
       </c>
-      <c r="D33" s="41" t="n">
+      <c r="D33" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">C33*D33</f>
         <v>0</v>
       </c>
-      <c r="F33" s="42" t="n">
+      <c r="F33" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13935,7 +15309,7 @@
         <f aca="false">C33*F33</f>
         <v>14040000</v>
       </c>
-      <c r="H33" s="43" t="n">
+      <c r="H33" s="61" t="n">
         <f aca="false">F33-D33</f>
         <v>100</v>
       </c>
@@ -13944,12 +15318,12 @@
         <v>14040000</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="40" t="s">
-        <v>81</v>
+      <c r="A34" s="59" t="s">
+        <v>114</v>
       </c>
       <c r="B34" s="7" t="str">
         <f aca="false">VLOOKUP(A34,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13959,14 +15333,14 @@
         <f aca="false">VLOOKUP(A34,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>0</v>
       </c>
-      <c r="D34" s="41" t="n">
+      <c r="D34" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
         <f aca="false">C34*D34</f>
         <v>0</v>
       </c>
-      <c r="F34" s="42" t="n">
+      <c r="F34" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -13974,7 +15348,7 @@
         <f aca="false">C34*F34</f>
         <v>0</v>
       </c>
-      <c r="H34" s="43" t="n">
+      <c r="H34" s="61" t="n">
         <f aca="false">F34-D34</f>
         <v>100</v>
       </c>
@@ -13983,12 +15357,12 @@
         <v>0</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="40" t="s">
-        <v>83</v>
+      <c r="A35" s="59" t="s">
+        <v>116</v>
       </c>
       <c r="B35" s="7" t="str">
         <f aca="false">VLOOKUP(A35,단가표!$B$5:$G$26,3,FALSE())</f>
@@ -13998,14 +15372,14 @@
         <f aca="false">VLOOKUP(A35,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>0</v>
       </c>
-      <c r="D35" s="41" t="n">
+      <c r="D35" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
         <f aca="false">C35*D35</f>
         <v>0</v>
       </c>
-      <c r="F35" s="42" t="n">
+      <c r="F35" s="60" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -14013,7 +15387,7 @@
         <f aca="false">C35*F35</f>
         <v>0</v>
       </c>
-      <c r="H35" s="43" t="n">
+      <c r="H35" s="61" t="n">
         <f aca="false">F35-D35</f>
         <v>100</v>
       </c>
@@ -14022,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14031,43 +15405,43 @@
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
-      <c r="D36" s="46" t="n">
+      <c r="D36" s="63" t="n">
         <f aca="false">SUM(D23:D35)</f>
         <v>1300</v>
       </c>
-      <c r="E36" s="47" t="n">
+      <c r="E36" s="64" t="n">
         <f aca="false">SUM(E23:E35)</f>
         <v>323317500</v>
       </c>
-      <c r="F36" s="46" t="n">
+      <c r="F36" s="63" t="n">
         <f aca="false">SUM(F23:F35)</f>
         <v>2000</v>
       </c>
-      <c r="G36" s="47" t="n">
+      <c r="G36" s="64" t="n">
         <f aca="false">SUM(G23:G35)</f>
         <v>369962500</v>
       </c>
-      <c r="H36" s="48" t="n">
+      <c r="H36" s="65" t="n">
         <f aca="false">SUM(H23:H35)</f>
         <v>700</v>
       </c>
-      <c r="I36" s="49" t="n">
+      <c r="I36" s="66" t="n">
         <f aca="false">SUM(I23:I35)</f>
         <v>46645000</v>
       </c>
-      <c r="J36" s="50" t="str">
+      <c r="J36" s="67" t="str">
         <f aca="false">IF(E36=0,"","증감률 "&amp;TEXT(I36/E36,"+0.0%;-0.0%"))</f>
         <v>증감률 +14.4%</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="51" t="s">
-        <v>87</v>
+      <c r="A38" s="68" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="52" t="s">
-        <v>88</v>
+      <c r="A39" s="69" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -14079,7 +15453,7 @@
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(H6),H6&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(H6),H6&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14087,7 +15461,7 @@
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(H23),H23&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(H23),H23&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14101,7 +15475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -14120,577 +15494,577 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="B3" s="24"/>
-      <c r="C3" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="55" t="str">
+      <c r="C3" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="72" t="str">
         <f aca="false">"✕ "&amp;COUNTIF(F7:F24,"✕")&amp;"건   △ "&amp;COUNTIF(F7:F24,"△")&amp;"건   ○ "&amp;COUNTIF(F7:F24,"○")&amp;"건"</f>
         <v>✕ 4건   △ 6건   ○ 8건</v>
       </c>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>102</v>
+      <c r="B7" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>134</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>105</v>
+        <v>135</v>
+      </c>
+      <c r="F7" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="75" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>107</v>
+      <c r="B8" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="74" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>139</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="58" t="s">
-        <v>109</v>
+        <v>140</v>
+      </c>
+      <c r="F8" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="58" t="s">
-        <v>111</v>
+      <c r="B9" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="74" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="75" t="s">
+        <v>143</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>113</v>
+        <v>144</v>
+      </c>
+      <c r="F9" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="75" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>114</v>
+      <c r="B10" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="74" t="s">
+        <v>146</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="61" t="s">
-        <v>118</v>
+        <v>147</v>
+      </c>
+      <c r="E10" s="75" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="78" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="61" t="s">
-        <v>122</v>
+      <c r="B11" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="75" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="78" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>123</v>
+      <c r="B12" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>155</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="58" t="s">
-        <v>126</v>
+        <v>157</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="75" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>127</v>
+      <c r="B13" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>159</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" s="63" t="s">
-        <v>131</v>
+        <v>160</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="G13" s="80" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>133</v>
+      <c r="B14" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="81" t="s">
+        <v>165</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F14" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="58" t="s">
-        <v>126</v>
+        <v>167</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" s="75" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="57" t="s">
+      <c r="B15" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>139</v>
+      <c r="G15" s="75" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>140</v>
+      <c r="B16" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>172</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" s="59" t="s">
-        <v>104</v>
+        <v>174</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>136</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>144</v>
+      <c r="B17" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>176</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="65" t="s">
-        <v>147</v>
+        <v>178</v>
+      </c>
+      <c r="F17" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="82" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>148</v>
+      <c r="B18" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>180</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="77" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="61" t="s">
-        <v>151</v>
+      <c r="G18" s="78" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="58" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="F19" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="63" t="s">
-        <v>155</v>
+      <c r="B19" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>156</v>
+      <c r="B20" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>188</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="58" t="s">
-        <v>159</v>
+        <v>190</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="75" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="D21" s="58" t="s">
+      <c r="B21" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="81" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="75" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="E21" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="63" t="s">
-        <v>164</v>
+      <c r="G21" s="80" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>165</v>
+      <c r="B22" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="74" t="s">
+        <v>197</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="65" t="s">
-        <v>168</v>
+        <v>198</v>
+      </c>
+      <c r="E22" s="75" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="82" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="66" t="s">
-        <v>172</v>
+      <c r="B23" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="F23" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="83" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="58" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G24" s="63" t="s">
-        <v>176</v>
+      <c r="B24" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="F24" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="80" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
-        <v>177</v>
+      <c r="A26" s="58" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C28" s="57" t="s">
-        <v>66</v>
+      <c r="C28" s="74" t="s">
+        <v>99</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="58" t="s">
-        <v>181</v>
+        <v>212</v>
+      </c>
+      <c r="E28" s="75" t="s">
+        <v>213</v>
       </c>
       <c r="F28" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="E29" s="58" t="s">
-        <v>183</v>
+      <c r="C29" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="75" t="s">
+        <v>215</v>
       </c>
       <c r="F29" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="E30" s="58" t="s">
-        <v>185</v>
+      <c r="C30" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" s="75" t="s">
+        <v>217</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="58" t="s">
-        <v>187</v>
+      <c r="C31" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>219</v>
       </c>
       <c r="F31" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C32" s="57" t="s">
-        <v>188</v>
+      <c r="C32" s="74" t="s">
+        <v>220</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="E32" s="67" t="s">
-        <v>190</v>
+        <v>221</v>
+      </c>
+      <c r="E32" s="84" t="s">
+        <v>222</v>
       </c>
       <c r="F32" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="68" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="68"/>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
+      <c r="A33" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="39" t="s">
-        <v>192</v>
+      <c r="A35" s="58" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -14701,7 +16075,7 @@
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="34" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -14712,7 +16086,7 @@
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -14740,412 +16114,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="69" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="41" t="n">
-        <f aca="false">요약!C6</f>
-        <v>200</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">'프로젝트별 구성'!F9</f>
-        <v>392850</v>
-      </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="10" t="str">
-        <f aca="false">IF(E6="","",E6-D6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="71" t="str">
-        <f aca="false">IF(OR(E6="",E6=0),"",F6/E6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="9" t="str">
-        <f aca="false">IF(E6="","",C6*E6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="10" t="str">
-        <f aca="false">IF(E6="","",C6*F6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="75" t="n">
-        <f aca="false">요약!C6</f>
-        <v>200</v>
-      </c>
-      <c r="D7" s="76" t="n">
-        <f aca="false">'프로젝트별 구성'!F11</f>
-        <v>384750</v>
-      </c>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78" t="str">
-        <f aca="false">IF(E7="","",E7-D7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="79" t="str">
-        <f aca="false">IF(OR(E7="",E7=0),"",F7/E7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="76" t="str">
-        <f aca="false">IF(E7="","",C7*E7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="78" t="str">
-        <f aca="false">IF(E7="","",C7*F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="41" t="n">
-        <f aca="false">요약!C7</f>
-        <v>300</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <f aca="false">'프로젝트별 구성'!F19</f>
-        <v>417600</v>
-      </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="10" t="str">
-        <f aca="false">IF(E8="","",E8-D8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="71" t="str">
-        <f aca="false">IF(OR(E8="",E8=0),"",F8/E8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="9" t="str">
-        <f aca="false">IF(E8="","",C8*E8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="10" t="str">
-        <f aca="false">IF(E8="","",C8*F8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" s="75" t="n">
-        <f aca="false">요약!C7</f>
-        <v>300</v>
-      </c>
-      <c r="D9" s="76" t="n">
-        <f aca="false">'프로젝트별 구성'!F21</f>
-        <v>406350</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="78" t="str">
-        <f aca="false">IF(E9="","",E9-D9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="79" t="str">
-        <f aca="false">IF(OR(E9="",E9=0),"",F9/E9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="76" t="str">
-        <f aca="false">IF(E9="","",C9*E9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="78" t="str">
-        <f aca="false">IF(E9="","",C9*F9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="41" t="n">
-        <f aca="false">요약!C8</f>
-        <v>50</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">'프로젝트별 구성'!F30</f>
-        <v>531250</v>
-      </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="10" t="str">
-        <f aca="false">IF(E10="","",E10-D10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="71" t="str">
-        <f aca="false">IF(OR(E10="",E10=0),"",F10/E10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="9" t="str">
-        <f aca="false">IF(E10="","",C10*E10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="10" t="str">
-        <f aca="false">IF(E10="","",C10*F10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="74" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="75" t="n">
-        <f aca="false">요약!C8</f>
-        <v>50</v>
-      </c>
-      <c r="D11" s="76" t="n">
-        <f aca="false">'프로젝트별 구성'!F33</f>
-        <v>523150</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78" t="str">
-        <f aca="false">IF(E11="","",E11-D11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="79" t="str">
-        <f aca="false">IF(OR(E11="",E11=0),"",F11/E11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="76" t="str">
-        <f aca="false">IF(E11="","",C11*E11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="78" t="str">
-        <f aca="false">IF(E11="","",C11*F11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12" s="41" t="n">
-        <f aca="false">요약!C9</f>
-        <v>100</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">'프로젝트별 구성'!F46</f>
-        <v>1449500</v>
-      </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="10" t="str">
-        <f aca="false">IF(E12="","",E12-D12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="71" t="str">
-        <f aca="false">IF(OR(E12="",E12=0),"",F12/E12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="9" t="str">
-        <f aca="false">IF(E12="","",C12*E12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="10" t="str">
-        <f aca="false">IF(E12="","",C12*F12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="80" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="9" t="n">
-        <f aca="false">C6*D6+C8*D8+C10*D10+C12*D12</f>
-        <v>375362500</v>
-      </c>
-      <c r="D17" s="9" t="str">
-        <f aca="false">IF((E6="")+(E8="")+(E10="")+(E12="")&gt;0,"타겟 "&amp;((E6="")+(E8="")+(E10="")+(E12=""))&amp;"건 미입력",H6+H8+H10+H12)</f>
-        <v>타겟 4건 미입력</v>
-      </c>
-      <c r="E17" s="82" t="str">
-        <f aca="false">IF(ISNUMBER(D17),D17-C17,"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="83" t="str">
-        <f aca="false">IF(ISNUMBER(D17),E17/D17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="81" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="9" t="n">
-        <f aca="false">C7*D7+C9*D9+C11*D11+C12*D12</f>
-        <v>369962500</v>
-      </c>
-      <c r="D18" s="9" t="str">
-        <f aca="false">IF((E7="")+(E9="")+(E11="")+(E12="")&gt;0,"타겟 "&amp;((E7="")+(E9="")+(E11="")+(E12=""))&amp;"건 미입력",H7+H9+H11+H12)</f>
-        <v>타겟 4건 미입력</v>
-      </c>
-      <c r="E18" s="82" t="str">
-        <f aca="false">IF(ISNUMBER(D18),D18-C18,"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="83" t="str">
-        <f aca="false">IF(ISNUMBER(D18),E18/D18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="84" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="84" t="s">
-        <v>216</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-  </mergeCells>
-  <conditionalFormatting sqref="F6:I12">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND(ISNUMBER(F6),F6&lt;0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:F18">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND(ISNUMBER(E17),E17&lt;0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
@@ -15153,80 +16127,87 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="69" t="s">
-        <v>217</v>
+      <c r="A1" s="86" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="86" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="87" t="s">
+      <c r="A5" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="86" t="s">
-        <v>220</v>
-      </c>
-      <c r="B6" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
+      <c r="A6" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="89" t="str">
+        <v>236</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="90" t="str">
         <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
@@ -15241,28 +16222,36 @@
         <f aca="false">D8*E8</f>
         <v>392850</v>
       </c>
+      <c r="G8" s="91" t="n">
+        <f aca="false">D8*VLOOKUP(B8,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>873000</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="90"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="47" t="n">
+      <c r="A9" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="64" t="n">
         <f aca="false">SUM(F8:F8)</f>
         <v>392850</v>
       </c>
+      <c r="G9" s="93" t="n">
+        <f aca="false">SUM(G8:G8)</f>
+        <v>873000</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="89" t="str">
+        <v>62</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="90" t="str">
         <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
@@ -15277,92 +16266,107 @@
         <f aca="false">D10*E10</f>
         <v>384750</v>
       </c>
+      <c r="G10" s="91" t="n">
+        <f aca="false">D10*VLOOKUP(B10,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>855000</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="B11" s="90"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="47" t="n">
+      <c r="A11" s="92" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="64" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>384750</v>
       </c>
+      <c r="G11" s="93" t="n">
+        <f aca="false">SUM(G10:G10)</f>
+        <v>855000</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="91" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="91"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
+      <c r="A12" s="94" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="86" t="s">
-        <v>219</v>
-      </c>
-      <c r="B15" s="87" t="s">
+      <c r="A15" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="87"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="86" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="88" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
+      <c r="A16" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="89" t="str">
+        <v>236</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="90" t="str">
         <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
@@ -15377,28 +16381,36 @@
         <f aca="false">D18*E18</f>
         <v>417600</v>
       </c>
+      <c r="G18" s="91" t="n">
+        <f aca="false">D18*VLOOKUP(B18,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>928000</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="47" t="n">
+      <c r="A19" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="64" t="n">
         <f aca="false">SUM(F18:F18)</f>
         <v>417600</v>
       </c>
+      <c r="G19" s="93" t="n">
+        <f aca="false">SUM(G18:G18)</f>
+        <v>928000</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="89" t="str">
+        <v>62</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="90" t="str">
         <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
@@ -15413,92 +16425,107 @@
         <f aca="false">D20*E20</f>
         <v>406350</v>
       </c>
+      <c r="G20" s="91" t="n">
+        <f aca="false">D20*VLOOKUP(B20,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>903000</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="47" t="n">
+      <c r="A21" s="92" t="s">
+        <v>238</v>
+      </c>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="64" t="n">
         <f aca="false">SUM(F20:F20)</f>
         <v>406350</v>
       </c>
+      <c r="G21" s="93" t="n">
+        <f aca="false">SUM(G20:G20)</f>
+        <v>903000</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="92" t="s">
-        <v>228</v>
-      </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
+      <c r="A22" s="95" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" s="95"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="95"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="85" t="s">
+      <c r="A24" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="85"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="86" t="s">
-        <v>219</v>
-      </c>
-      <c r="B25" s="87" t="s">
+      <c r="A25" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="86" t="s">
-        <v>220</v>
-      </c>
-      <c r="B26" s="88" t="s">
-        <v>229</v>
-      </c>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
+      <c r="A26" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="89" t="str">
+        <v>236</v>
+      </c>
+      <c r="B28" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="90" t="str">
         <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
@@ -15513,13 +16540,17 @@
         <f aca="false">D28*E28</f>
         <v>392850</v>
       </c>
+      <c r="G28" s="91" t="n">
+        <f aca="false">D28*VLOOKUP(B28,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>873000</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22"/>
-      <c r="B29" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="89" t="str">
+      <c r="B29" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="90" t="str">
         <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
@@ -15534,28 +16565,36 @@
         <f aca="false">D29*E29</f>
         <v>138400</v>
       </c>
+      <c r="G29" s="91" t="n">
+        <f aca="false">D29*VLOOKUP(B29,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>346000</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="47" t="n">
+      <c r="A30" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="64" t="n">
         <f aca="false">SUM(F28:F29)</f>
         <v>531250</v>
       </c>
+      <c r="G30" s="93" t="n">
+        <f aca="false">SUM(G28:G29)</f>
+        <v>1219000</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="B31" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="89" t="str">
+        <v>62</v>
+      </c>
+      <c r="B31" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="90" t="str">
         <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
@@ -15570,13 +16609,17 @@
         <f aca="false">D31*E31</f>
         <v>384750</v>
       </c>
+      <c r="G31" s="91" t="n">
+        <f aca="false">D31*VLOOKUP(B31,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>855000</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22"/>
-      <c r="B32" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="89" t="str">
+      <c r="B32" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="90" t="str">
         <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
@@ -15591,92 +16634,107 @@
         <f aca="false">D32*E32</f>
         <v>138400</v>
       </c>
+      <c r="G32" s="91" t="n">
+        <f aca="false">D32*VLOOKUP(B32,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>346000</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="47" t="n">
+      <c r="A33" s="92" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="64" t="n">
         <f aca="false">SUM(F31:F32)</f>
         <v>523150</v>
       </c>
+      <c r="G33" s="93" t="n">
+        <f aca="false">SUM(G31:G32)</f>
+        <v>1201000</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="91" t="s">
+      <c r="A34" s="94" t="s">
+        <v>243</v>
+      </c>
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="87" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-    </row>
-    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="86" t="s">
-        <v>219</v>
-      </c>
-      <c r="B37" s="87" t="s">
+      <c r="B37" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="87"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="86" t="s">
-        <v>220</v>
-      </c>
-      <c r="B38" s="88" t="s">
+      <c r="A38" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
+      <c r="B38" s="89" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="89" t="str">
+        <v>245</v>
+      </c>
+      <c r="B40" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="90" t="str">
         <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU + 이더넷 (입력 14 / 출력 10)</v>
       </c>
@@ -15691,13 +16749,17 @@
         <f aca="false">D40*E40</f>
         <v>398700</v>
       </c>
+      <c r="G40" s="91" t="n">
+        <f aca="false">D40*VLOOKUP(B40,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>886000</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22"/>
-      <c r="B41" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="89" t="str">
+      <c r="B41" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="90" t="str">
         <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
@@ -15712,13 +16774,17 @@
         <f aca="false">D41*E41</f>
         <v>547200</v>
       </c>
+      <c r="G41" s="91" t="n">
+        <f aca="false">D41*VLOOKUP(B41,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>1368000</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22"/>
-      <c r="B42" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="89" t="str">
+      <c r="B42" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="90" t="str">
         <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>릴레이 출력 16점</v>
       </c>
@@ -15733,13 +16799,17 @@
         <f aca="false">D42*E42</f>
         <v>363200</v>
       </c>
+      <c r="G42" s="91" t="n">
+        <f aca="false">D42*VLOOKUP(B42,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>908000</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22"/>
-      <c r="B43" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" s="89" t="str">
+      <c r="B43" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="90" t="str">
         <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>아날로그 출력 4CH</v>
       </c>
@@ -15754,13 +16824,17 @@
         <f aca="false">D43*E43</f>
         <v>140400</v>
       </c>
+      <c r="G43" s="91" t="n">
+        <f aca="false">D43*VLOOKUP(B43,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>351000</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22"/>
-      <c r="B44" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="89" t="str">
+      <c r="B44" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="90" t="str">
         <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>TM3 버스 확장 송신 (MCC)</v>
       </c>
@@ -15775,13 +16849,17 @@
         <f aca="false">D44*E44</f>
         <v>0</v>
       </c>
+      <c r="G44" s="91" t="n">
+        <f aca="false">D44*VLOOKUP(B44,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22"/>
-      <c r="B45" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="89" t="str">
+      <c r="B45" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="90" t="str">
         <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>TM3 버스 확장 수신 (MCC)</v>
       </c>
@@ -15796,58 +16874,67 @@
         <f aca="false">D45*E45</f>
         <v>0</v>
       </c>
+      <c r="G45" s="91" t="n">
+        <f aca="false">D45*VLOOKUP(B45,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="90"/>
-      <c r="F46" s="47" t="n">
+      <c r="A46" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" s="92"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="92"/>
+      <c r="E46" s="92"/>
+      <c r="F46" s="64" t="n">
         <f aca="false">SUM(F40:F45)</f>
         <v>1449500</v>
       </c>
+      <c r="G46" s="93" t="n">
+        <f aca="false">SUM(G40:G45)</f>
+        <v>3513000</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="92" t="s">
-        <v>233</v>
-      </c>
-      <c r="B47" s="92"/>
-      <c r="C47" s="92"/>
-      <c r="D47" s="92"/>
-      <c r="E47" s="92"/>
-      <c r="F47" s="92"/>
+      <c r="A47" s="95" t="s">
+        <v>246</v>
+      </c>
+      <c r="B47" s="95"/>
+      <c r="C47" s="95"/>
+      <c r="D47" s="95"/>
+      <c r="E47" s="95"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
     <mergeCell ref="A40:A45"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15879,60 +16966,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="86" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="93" t="n">
+      <c r="A3" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="96" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="86" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="93" t="n">
+      <c r="A4" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="96" t="n">
         <v>0.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>200</v>
+        <v>53</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="s">
-        <v>60</v>
+      <c r="A7" s="59" t="s">
+        <v>93</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,4,FALSE())</f>
@@ -15946,11 +17033,11 @@
         <f aca="false">ROUND(C7*$B$4,0)</f>
         <v>349200</v>
       </c>
-      <c r="F7" s="94" t="n">
+      <c r="F7" s="47" t="n">
         <f aca="false">D7-E7</f>
         <v>43650</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -15958,16 +17045,16 @@
         <f aca="false">F7*G7</f>
         <v>10912500</v>
       </c>
-      <c r="I7" s="95" t="s">
-        <v>245</v>
+      <c r="I7" s="97" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="40" t="s">
-        <v>62</v>
+      <c r="A8" s="59" t="s">
+        <v>95</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,4,FALSE())</f>
@@ -15981,11 +17068,11 @@
         <f aca="false">ROUND(C8*$B$4,0)</f>
         <v>371200</v>
       </c>
-      <c r="F8" s="94" t="n">
+      <c r="F8" s="47" t="n">
         <f aca="false">D8-E8</f>
         <v>46400</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -15993,16 +17080,16 @@
         <f aca="false">F8*G8</f>
         <v>13920000</v>
       </c>
-      <c r="I8" s="95" t="s">
-        <v>246</v>
+      <c r="I8" s="97" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40" t="s">
-        <v>66</v>
+      <c r="A9" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,4,FALSE())</f>
@@ -16016,11 +17103,11 @@
         <f aca="false">ROUND(C9*$B$4,0)</f>
         <v>354400</v>
       </c>
-      <c r="F9" s="94" t="n">
+      <c r="F9" s="47" t="n">
         <f aca="false">D9-E9</f>
         <v>44300</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
@@ -16028,16 +17115,16 @@
         <f aca="false">F9*G9</f>
         <v>4430000</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="97" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="s">
-        <v>85</v>
+      <c r="A10" s="59" t="s">
+        <v>118</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,4,FALSE())</f>
@@ -16051,11 +17138,11 @@
         <f aca="false">ROUND(C10*$B$4,0)</f>
         <v>342000</v>
       </c>
-      <c r="F10" s="94" t="n">
+      <c r="F10" s="47" t="n">
         <f aca="false">D10-E10</f>
         <v>42750</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -16063,16 +17150,16 @@
         <f aca="false">F10*G10</f>
         <v>10687500</v>
       </c>
-      <c r="I10" s="95" t="s">
-        <v>248</v>
+      <c r="I10" s="97" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="40" t="s">
-        <v>86</v>
+      <c r="A11" s="59" t="s">
+        <v>119</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,4,FALSE())</f>
@@ -16086,11 +17173,11 @@
         <f aca="false">ROUND(C11*$B$4,0)</f>
         <v>361200</v>
       </c>
-      <c r="F11" s="94" t="n">
+      <c r="F11" s="47" t="n">
         <f aca="false">D11-E11</f>
         <v>45150</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -16098,43 +17185,43 @@
         <f aca="false">F11*G11</f>
         <v>13545000</v>
       </c>
-      <c r="I11" s="95" t="s">
-        <v>249</v>
+      <c r="I11" s="97" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="81" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
+      <c r="A13" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
       <c r="H13" s="16" t="n">
         <f aca="false">H7+H8+H9</f>
         <v>29262500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
+      <c r="A14" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
       <c r="H14" s="16" t="n">
         <f aca="false">H9+H10+H11</f>
         <v>28662500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="84" t="s">
-        <v>252</v>
+      <c r="A16" s="56" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -16170,55 +17257,55 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="69" t="s">
-        <v>253</v>
+      <c r="A1" s="86" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="40" t="s">
-        <v>66</v>
+      <c r="B5" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="D5" s="96" t="s">
         <v>257</v>
+      </c>
+      <c r="D5" s="98" t="s">
+        <v>269</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>886000</v>
       </c>
-      <c r="F5" s="97" t="n">
+      <c r="F5" s="99" t="n">
         <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -16230,19 +17317,19 @@
       <c r="A6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="40" t="s">
-        <v>60</v>
+      <c r="B6" s="59" t="s">
+        <v>93</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" s="96" t="s">
-        <v>258</v>
+        <v>257</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>270</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>873000</v>
       </c>
-      <c r="F6" s="97" t="n">
+      <c r="F6" s="99" t="n">
         <v>0.45</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -16254,19 +17341,19 @@
       <c r="A7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="40" t="s">
-        <v>85</v>
+      <c r="B7" s="59" t="s">
+        <v>118</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="D7" s="96" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="D7" s="98" t="s">
+        <v>271</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>855000</v>
       </c>
-      <c r="F7" s="97" t="n">
+      <c r="F7" s="99" t="n">
         <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -16278,19 +17365,19 @@
       <c r="A8" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="40" t="s">
-        <v>62</v>
+      <c r="B8" s="59" t="s">
+        <v>95</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="96" t="s">
-        <v>260</v>
+        <v>257</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>272</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>928000</v>
       </c>
-      <c r="F8" s="97" t="n">
+      <c r="F8" s="99" t="n">
         <v>0.45</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -16302,19 +17389,19 @@
       <c r="A9" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="40" t="s">
-        <v>86</v>
+      <c r="B9" s="59" t="s">
+        <v>119</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="D9" s="96" t="s">
-        <v>261</v>
+        <v>260</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>273</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>903000</v>
       </c>
-      <c r="F9" s="97" t="n">
+      <c r="F9" s="99" t="n">
         <v>0.45</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -16326,19 +17413,19 @@
       <c r="A10" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="40" t="s">
-        <v>68</v>
+      <c r="B10" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="98" t="s">
-        <v>262</v>
+      <c r="D10" s="100" t="s">
+        <v>274</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>228000</v>
       </c>
-      <c r="F10" s="97" t="n">
+      <c r="F10" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -16350,19 +17437,19 @@
       <c r="A11" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="40" t="s">
-        <v>70</v>
+      <c r="B11" s="59" t="s">
+        <v>103</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="98" t="s">
-        <v>263</v>
+      <c r="D11" s="100" t="s">
+        <v>275</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>202000</v>
       </c>
-      <c r="F11" s="97" t="n">
+      <c r="F11" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -16374,19 +17461,19 @@
       <c r="A12" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>72</v>
+      <c r="B12" s="59" t="s">
+        <v>105</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="98" t="s">
-        <v>264</v>
+      <c r="D12" s="100" t="s">
+        <v>276</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F12" s="97" t="n">
+      <c r="F12" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -16398,19 +17485,19 @@
       <c r="A13" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>74</v>
+      <c r="B13" s="59" t="s">
+        <v>107</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="98" t="s">
-        <v>265</v>
+      <c r="D13" s="100" t="s">
+        <v>277</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F13" s="97" t="n">
+      <c r="F13" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -16422,19 +17509,19 @@
       <c r="A14" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="40" t="s">
-        <v>266</v>
+      <c r="B14" s="59" t="s">
+        <v>278</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="98" t="s">
-        <v>267</v>
+      <c r="D14" s="100" t="s">
+        <v>279</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>213000</v>
       </c>
-      <c r="F14" s="97" t="n">
+      <c r="F14" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -16446,19 +17533,19 @@
       <c r="A15" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>268</v>
+      <c r="B15" s="59" t="s">
+        <v>280</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="98" t="s">
-        <v>269</v>
+      <c r="D15" s="100" t="s">
+        <v>281</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>161000</v>
       </c>
-      <c r="F15" s="97" t="n">
+      <c r="F15" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -16470,19 +17557,19 @@
       <c r="A16" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>76</v>
+      <c r="B16" s="59" t="s">
+        <v>109</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="98" t="s">
-        <v>270</v>
+      <c r="D16" s="100" t="s">
+        <v>282</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F16" s="97" t="n">
+      <c r="F16" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -16494,19 +17581,19 @@
       <c r="A17" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>271</v>
+      <c r="B17" s="59" t="s">
+        <v>283</v>
       </c>
       <c r="C17" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="98" t="s">
-        <v>272</v>
+      <c r="D17" s="100" t="s">
+        <v>284</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F17" s="97" t="n">
+      <c r="F17" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
@@ -16518,19 +17605,19 @@
       <c r="A18" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="40" t="s">
-        <v>273</v>
+      <c r="B18" s="59" t="s">
+        <v>285</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="98" t="s">
-        <v>274</v>
+      <c r="D18" s="100" t="s">
+        <v>286</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>311000</v>
       </c>
-      <c r="F18" s="97" t="n">
+      <c r="F18" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -16542,19 +17629,19 @@
       <c r="A19" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="40" t="s">
-        <v>275</v>
+      <c r="B19" s="59" t="s">
+        <v>287</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="98" t="s">
-        <v>276</v>
+      <c r="D19" s="100" t="s">
+        <v>288</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>284000</v>
       </c>
-      <c r="F19" s="97" t="n">
+      <c r="F19" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -16566,19 +17653,19 @@
       <c r="A20" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="40" t="s">
-        <v>277</v>
+      <c r="B20" s="59" t="s">
+        <v>289</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="98" t="s">
-        <v>278</v>
+      <c r="D20" s="100" t="s">
+        <v>290</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>331000</v>
       </c>
-      <c r="F20" s="97" t="n">
+      <c r="F20" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -16590,19 +17677,19 @@
       <c r="A21" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="40" t="s">
-        <v>77</v>
+      <c r="B21" s="59" t="s">
+        <v>110</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="98" t="s">
-        <v>279</v>
+      <c r="D21" s="100" t="s">
+        <v>291</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>346000</v>
       </c>
-      <c r="F21" s="97" t="n">
+      <c r="F21" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -16614,19 +17701,19 @@
       <c r="A22" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="40" t="s">
-        <v>79</v>
+      <c r="B22" s="59" t="s">
+        <v>112</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="98" t="s">
-        <v>280</v>
+      <c r="D22" s="100" t="s">
+        <v>292</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>351000</v>
       </c>
-      <c r="F22" s="97" t="n">
+      <c r="F22" s="99" t="n">
         <v>0.4</v>
       </c>
       <c r="G22" s="10" t="n">
@@ -16635,33 +17722,33 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="99" t="s">
-        <v>281</v>
-      </c>
-      <c r="B23" s="99"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="99"/>
+      <c r="A23" s="101" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="40" t="s">
-        <v>64</v>
+      <c r="B24" s="59" t="s">
+        <v>97</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="D24" s="100" t="s">
-        <v>282</v>
-      </c>
-      <c r="E24" s="101" t="n">
+        <v>257</v>
+      </c>
+      <c r="D24" s="102" t="s">
+        <v>294</v>
+      </c>
+      <c r="E24" s="103" t="n">
         <v>941000</v>
       </c>
-      <c r="F24" s="102" t="n">
+      <c r="F24" s="104" t="n">
         <v>0.45</v>
       </c>
       <c r="G24" s="10" t="n">
@@ -16673,17 +17760,17 @@
       <c r="A25" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="40" t="s">
-        <v>81</v>
+      <c r="B25" s="59" t="s">
+        <v>114</v>
       </c>
       <c r="C25" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="100" t="s">
-        <v>283</v>
-      </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="102" t="n">
+      <c r="D25" s="102" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="103"/>
+      <c r="F25" s="104" t="n">
         <v>0.4</v>
       </c>
       <c r="G25" s="10" t="n">
@@ -16695,17 +17782,17 @@
       <c r="A26" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>83</v>
+      <c r="B26" s="59" t="s">
+        <v>116</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="100" t="s">
-        <v>284</v>
-      </c>
-      <c r="E26" s="101"/>
-      <c r="F26" s="102" t="n">
+      <c r="D26" s="102" t="s">
+        <v>296</v>
+      </c>
+      <c r="E26" s="103"/>
+      <c r="F26" s="104" t="n">
         <v>0.4</v>
       </c>
       <c r="G26" s="10" t="n">
@@ -16715,7 +17802,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="253">
   <si>
     <r>
       <rPr>
@@ -606,7 +606,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MCC — Techross </t>
+      <t xml:space="preserve">MCC — Schneider </t>
     </r>
     <r>
       <rPr>
@@ -616,7 +616,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">협의로 </t>
+      <t xml:space="preserve">제안이 </t>
     </r>
     <r>
       <rPr>
@@ -627,7 +627,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Schneider </t>
+      <t xml:space="preserve">Techross </t>
     </r>
     <r>
       <rPr>
@@ -637,7 +637,39 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원안 확정</t>
+      <t xml:space="preserve">요구와 일치 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -696,7 +728,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">40 TR / </t>
+      <t xml:space="preserve">40 (Relay·TR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
     </r>
     <r>
       <rPr>
@@ -768,7 +819,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">② TSU · ANU · ANU-S: Schneider </t>
+      <t xml:space="preserve">② 4</t>
     </r>
     <r>
       <rPr>
@@ -777,7 +828,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제안 구성 그대로 — </t>
+      <t xml:space="preserve">개 프로젝트 모두 </t>
     </r>
     <r>
       <rPr>
@@ -787,7 +838,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">RFQ </t>
+      <t xml:space="preserve">Schneider </t>
     </r>
     <r>
       <rPr>
@@ -796,7 +847,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">조건 충족</t>
+      <t xml:space="preserve">제안 구성이 </t>
     </r>
     <r>
       <rPr>
@@ -806,71 +857,147 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">Techross </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">③ MCC: Schneider–Techross </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구와 일치합니다 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">협의로 원안</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TM241CE40T </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구성</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Relay·TR </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무관</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확정</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원안 점수 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">③ MCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 확장 모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개라 버스 확장 부품이 필요 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -884,7 +1011,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확장 모듈 </t>
+      <t xml:space="preserve">남은 보완은 서류</t>
     </r>
     <r>
       <rPr>
@@ -894,7 +1021,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -903,7 +1030,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">개라 버스 확장 부품은 필요 없습니다</t>
+      <t xml:space="preserve">제안 가격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외형도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CAD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">뿐입니다</t>
     </r>
     <r>
       <rPr>
@@ -2716,7 +2900,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·  MCC</t>
+      <t xml:space="preserve">·  4</t>
     </r>
     <r>
       <rPr>
@@ -2725,7 +2909,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 </t>
+      <t xml:space="preserve">개 프로젝트 모두 </t>
     </r>
     <r>
       <rPr>
@@ -2735,7 +2919,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Techross </t>
+      <t xml:space="preserve">Schneider </t>
     </r>
     <r>
       <rPr>
@@ -2744,7 +2928,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">협의로 </t>
+      <t xml:space="preserve">제안 구성 </t>
     </r>
     <r>
       <rPr>
@@ -2754,7 +2938,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Schneider </t>
+      <t xml:space="preserve">(Techross </t>
     </r>
     <r>
       <rPr>
@@ -2763,7 +2947,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원안 확정</t>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -4090,29 +4284,208 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Relay Type Only (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공통사항 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">Relay·TR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무관 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 2026-10-06)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트랜지스터 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM241CE40T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TR + TM3DQ16T + TM3DQ8T)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. RFQ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문서의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'Relay Type Only'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Techross</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 무관하다고 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MCC I/O </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64 / </t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4130,150 +4503,145 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 전부 트랜지스터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TM241CE40T </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내장 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TR + TM3DQ16T + TM3DQ8T)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">협의</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Schneider–Techross </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">협의로 원안</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TR </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확정 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-10-06).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MCC I/O </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점수</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">40 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2CH (Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2CH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. RFQ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문서의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4291,157 +4659,45 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">102 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">54 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4CH</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">64 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2CH</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Schneider–Techross </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">협의로 원안 점수 확정 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-10-06).</t>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대신 제안 점수가 맞다고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -7586,26 +7842,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">협의로 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Schneider </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원안 확정 </t>
+      <t xml:space="preserve">확인 </t>
     </r>
     <r>
       <rPr>
@@ -7653,7 +7890,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">40 (TR) / </t>
+      <t xml:space="preserve">40 (Relay·TR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
     </r>
     <r>
       <rPr>
@@ -7691,7 +7947,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1CH</t>
+      <t xml:space="preserve">1CH — Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제안과 일치</t>
     </r>
   </si>
   <si>
@@ -9237,7 +9502,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9584,28 +9849,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1F3864"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF1F3864"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF1F3864"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF7F6000"/>
       <name val="맑은 고딕"/>
@@ -9785,7 +10028,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="90">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10042,19 +10285,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10062,7 +10297,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="54" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10070,7 +10305,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10082,7 +10317,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10106,11 +10341,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="53" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10146,11 +10381,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="59" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="56" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="60" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10673,7 +10908,7 @@
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
@@ -10684,7 +10919,7 @@
       <c r="F19" s="23"/>
       <c r="G19" s="23"/>
     </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
         <v>26</v>
       </c>
@@ -10754,8 +10989,8 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="str">
-        <f aca="false">"⑨ Schneider 제안 검토: 반드시 수정 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"✕")&amp;"건, 보완 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"△")&amp;"건, Techross 협의 완료 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"협의")&amp;"건  → 'Schneider 제안 검토' 시트"</f>
-        <v>⑨ Schneider 제안 검토: 반드시 수정 2건, 보완 5건, Techross 협의 완료 2건  → 'Schneider 제안 검토' 시트</v>
+        <f aca="false">"⑨ Schneider 제안 검토: 반드시 수정 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"✕")&amp;"건, 보완 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"△")&amp;"건  (구성은 4개 프로젝트 모두 적합)  → 'Schneider 제안 검토' 시트"</f>
+        <v>⑨ Schneider 제안 검토: 반드시 수정 2건, 보완 5건  (구성은 4개 프로젝트 모두 적합)  → 'Schneider 제안 검토' 시트</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -11998,8 +12233,8 @@
         <v>93</v>
       </c>
       <c r="E3" s="59" t="str">
-        <f aca="false">"✕ "&amp;COUNTIF(F7:F24,"✕")&amp;"건   △ "&amp;COUNTIF(F7:F24,"△")&amp;"건   ○ "&amp;COUNTIF(F7:F24,"○")&amp;"건   협의 완료 "&amp;COUNTIF(F7:F24,"협의")&amp;"건"</f>
-        <v>✕ 2건   △ 5건   ○ 9건   협의 완료 2건</v>
+        <f aca="false">"✕ "&amp;COUNTIF(F7:F24,"✕")&amp;"건   △ "&amp;COUNTIF(F7:F24,"△")&amp;"건   ○ "&amp;COUNTIF(F7:F24,"○")&amp;"건"</f>
+        <v>✕ 2건   △ 5건   ○ 11건</v>
       </c>
       <c r="F3" s="59"/>
       <c r="G3" s="59"/>
@@ -12096,7 +12331,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="n">
         <v>4</v>
       </c>
@@ -12112,11 +12347,11 @@
       <c r="E10" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F10" s="64" t="s">
+      <c r="F10" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="62" t="s">
         <v>117</v>
-      </c>
-      <c r="G10" s="65" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12127,19 +12362,19 @@
         <v>100</v>
       </c>
       <c r="C11" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="E11" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="F11" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="62" t="s">
         <v>121</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12150,19 +12385,19 @@
         <v>100</v>
       </c>
       <c r="C12" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="F12" s="63" t="s">
         <v>104</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12173,19 +12408,19 @@
         <v>100</v>
       </c>
       <c r="C13" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="62" t="s">
         <v>128</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>129</v>
       </c>
       <c r="F13" s="63" t="s">
         <v>104</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12193,22 +12428,22 @@
         <v>8</v>
       </c>
       <c r="B14" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="D14" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>134</v>
       </c>
       <c r="F14" s="63" t="s">
         <v>104</v>
       </c>
       <c r="G14" s="62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12216,22 +12451,22 @@
         <v>9</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="61" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>136</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="F15" s="63" t="s">
         <v>104</v>
       </c>
       <c r="G15" s="62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12239,22 +12474,22 @@
         <v>10</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="F16" s="63" t="s">
         <v>104</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12262,22 +12497,22 @@
         <v>11</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="F17" s="67" t="s">
+      <c r="G17" s="66" t="s">
         <v>146</v>
-      </c>
-      <c r="G17" s="68" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12285,22 +12520,22 @@
         <v>12</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="G18" s="68" t="s">
         <v>151</v>
-      </c>
-      <c r="G18" s="70" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12308,22 +12543,22 @@
         <v>13</v>
       </c>
       <c r="B19" s="60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="62" t="s">
+      <c r="E19" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="F19" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="69" t="s">
         <v>155</v>
-      </c>
-      <c r="F19" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="71" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12331,22 +12566,22 @@
         <v>14</v>
       </c>
       <c r="B20" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="F20" s="63" t="s">
         <v>104</v>
       </c>
       <c r="G20" s="62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12354,22 +12589,22 @@
         <v>15</v>
       </c>
       <c r="B21" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="D21" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="D21" s="62" t="s">
+      <c r="E21" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="E21" s="62" t="s">
+      <c r="F21" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="69" t="s">
         <v>164</v>
-      </c>
-      <c r="F21" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="71" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12377,22 +12612,22 @@
         <v>16</v>
       </c>
       <c r="B22" s="60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C22" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="62" t="s">
         <v>167</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="F22" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="66" t="s">
         <v>168</v>
-      </c>
-      <c r="F22" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" s="68" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12400,22 +12635,22 @@
         <v>17</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="E23" s="62" t="s">
         <v>171</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="F23" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="70" t="s">
         <v>172</v>
-      </c>
-      <c r="F23" s="69" t="s">
-        <v>151</v>
-      </c>
-      <c r="G23" s="72" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12423,32 +12658,32 @@
         <v>18</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="62" t="s">
         <v>174</v>
       </c>
-      <c r="D24" s="62" t="s">
+      <c r="E24" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="E24" s="62" t="s">
+      <c r="F24" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="G24" s="71" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="71" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="73" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -12491,50 +12726,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="76" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -12547,26 +12782,26 @@
         <v>66</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="77" t="str">
+      <c r="C8" s="75" t="str">
         <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
@@ -12581,24 +12816,24 @@
         <f aca="false">D8*E8</f>
         <v>392850</v>
       </c>
-      <c r="G8" s="78" t="n">
+      <c r="G8" s="76" t="n">
         <f aca="false">D8*VLOOKUP(B8,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>873000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
+      <c r="A9" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
       <c r="F9" s="54" t="n">
         <f aca="false">SUM(F8:F8)</f>
         <v>392850</v>
       </c>
-      <c r="G9" s="80" t="n">
+      <c r="G9" s="78" t="n">
         <f aca="false">SUM(G8:G8)</f>
         <v>873000</v>
       </c>
@@ -12610,7 +12845,7 @@
       <c r="B10" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="77" t="str">
+      <c r="C10" s="75" t="str">
         <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
@@ -12625,75 +12860,75 @@
         <f aca="false">D10*E10</f>
         <v>384750</v>
       </c>
-      <c r="G10" s="78" t="n">
+      <c r="G10" s="76" t="n">
         <f aca="false">D10*VLOOKUP(B10,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>855000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
+      <c r="A11" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
       <c r="F11" s="54" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>384750</v>
       </c>
-      <c r="G11" s="80" t="n">
+      <c r="G11" s="78" t="n">
         <f aca="false">SUM(G10:G10)</f>
         <v>855000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="81" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
+      <c r="A12" s="79" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B15" s="75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
+        <v>182</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -12706,26 +12941,26 @@
         <v>66</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="77" t="str">
+      <c r="C18" s="75" t="str">
         <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
@@ -12740,24 +12975,24 @@
         <f aca="false">D18*E18</f>
         <v>417600</v>
       </c>
-      <c r="G18" s="78" t="n">
+      <c r="G18" s="76" t="n">
         <f aca="false">D18*VLOOKUP(B18,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>928000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
+      <c r="A19" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
       <c r="F19" s="54" t="n">
         <f aca="false">SUM(F18:F18)</f>
         <v>417600</v>
       </c>
-      <c r="G19" s="80" t="n">
+      <c r="G19" s="78" t="n">
         <f aca="false">SUM(G18:G18)</f>
         <v>928000</v>
       </c>
@@ -12769,7 +13004,7 @@
       <c r="B20" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="77" t="str">
+      <c r="C20" s="75" t="str">
         <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
@@ -12784,75 +13019,75 @@
         <f aca="false">D20*E20</f>
         <v>406350</v>
       </c>
-      <c r="G20" s="78" t="n">
+      <c r="G20" s="76" t="n">
         <f aca="false">D20*VLOOKUP(B20,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>903000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
+      <c r="A21" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
       <c r="F21" s="54" t="n">
         <f aca="false">SUM(F20:F20)</f>
         <v>406350</v>
       </c>
-      <c r="G21" s="80" t="n">
+      <c r="G21" s="78" t="n">
         <f aca="false">SUM(G20:G20)</f>
         <v>903000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="82" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
+      <c r="A22" s="80" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B25" s="75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="B26" s="76" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
+        <v>182</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
@@ -12865,26 +13100,26 @@
         <v>66</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B28" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="77" t="str">
+      <c r="C28" s="75" t="str">
         <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
@@ -12899,7 +13134,7 @@
         <f aca="false">D28*E28</f>
         <v>392850</v>
       </c>
-      <c r="G28" s="78" t="n">
+      <c r="G28" s="76" t="n">
         <f aca="false">D28*VLOOKUP(B28,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>873000</v>
       </c>
@@ -12909,7 +13144,7 @@
       <c r="B29" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="77" t="str">
+      <c r="C29" s="75" t="str">
         <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
@@ -12924,24 +13159,24 @@
         <f aca="false">D29*E29</f>
         <v>138400</v>
       </c>
-      <c r="G29" s="78" t="n">
+      <c r="G29" s="76" t="n">
         <f aca="false">D29*VLOOKUP(B29,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
+      <c r="A30" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
       <c r="F30" s="54" t="n">
         <f aca="false">SUM(F28:F29)</f>
         <v>531250</v>
       </c>
-      <c r="G30" s="80" t="n">
+      <c r="G30" s="78" t="n">
         <f aca="false">SUM(G28:G29)</f>
         <v>1219000</v>
       </c>
@@ -12953,7 +13188,7 @@
       <c r="B31" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="77" t="str">
+      <c r="C31" s="75" t="str">
         <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
@@ -12968,7 +13203,7 @@
         <f aca="false">D31*E31</f>
         <v>384750</v>
       </c>
-      <c r="G31" s="78" t="n">
+      <c r="G31" s="76" t="n">
         <f aca="false">D31*VLOOKUP(B31,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>855000</v>
       </c>
@@ -12978,7 +13213,7 @@
       <c r="B32" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="77" t="str">
+      <c r="C32" s="75" t="str">
         <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
@@ -12993,75 +13228,75 @@
         <f aca="false">D32*E32</f>
         <v>138400</v>
       </c>
-      <c r="G32" s="78" t="n">
+      <c r="G32" s="76" t="n">
         <f aca="false">D32*VLOOKUP(B32,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
+      <c r="A33" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
       <c r="F33" s="54" t="n">
         <f aca="false">SUM(F31:F32)</f>
         <v>523150</v>
       </c>
-      <c r="G33" s="80" t="n">
+      <c r="G33" s="78" t="n">
         <f aca="false">SUM(G31:G32)</f>
         <v>1201000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="81" t="s">
-        <v>196</v>
-      </c>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
+      <c r="A34" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="74" t="s">
+      <c r="A36" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="74"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B37" s="75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="75"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="B38" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
+        <v>182</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
@@ -13074,26 +13309,26 @@
         <v>66</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="77" t="str">
+      <c r="C40" s="75" t="str">
         <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>CPU + 이더넷 (입력 24 / 출력 16) — MCC, 견적에 없어 추정가</v>
       </c>
@@ -13108,7 +13343,7 @@
         <f aca="false">D40*E40</f>
         <v>423450</v>
       </c>
-      <c r="G40" s="78" t="n">
+      <c r="G40" s="76" t="n">
         <f aca="false">D40*VLOOKUP(B40,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>941000</v>
       </c>
@@ -13118,7 +13353,7 @@
       <c r="B41" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="77" t="str">
+      <c r="C41" s="75" t="str">
         <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
@@ -13133,7 +13368,7 @@
         <f aca="false">D41*E41</f>
         <v>182400</v>
       </c>
-      <c r="G41" s="78" t="n">
+      <c r="G41" s="76" t="n">
         <f aca="false">D41*VLOOKUP(B41,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>456000</v>
       </c>
@@ -13143,7 +13378,7 @@
       <c r="B42" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="77" t="str">
+      <c r="C42" s="75" t="str">
         <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>디지털 입력 8점</v>
       </c>
@@ -13158,7 +13393,7 @@
         <f aca="false">D42*E42</f>
         <v>80800</v>
       </c>
-      <c r="G42" s="78" t="n">
+      <c r="G42" s="76" t="n">
         <f aca="false">D42*VLOOKUP(B42,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>202000</v>
       </c>
@@ -13168,7 +13403,7 @@
       <c r="B43" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="77" t="str">
+      <c r="C43" s="75" t="str">
         <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>트랜지스터 출력 16점</v>
       </c>
@@ -13183,7 +13418,7 @@
         <f aca="false">D43*E43</f>
         <v>90800</v>
       </c>
-      <c r="G43" s="78" t="n">
+      <c r="G43" s="76" t="n">
         <f aca="false">D43*VLOOKUP(B43,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>227000</v>
       </c>
@@ -13193,7 +13428,7 @@
       <c r="B44" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="C44" s="77" t="str">
+      <c r="C44" s="75" t="str">
         <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>트랜지스터 출력 8점</v>
       </c>
@@ -13208,7 +13443,7 @@
         <f aca="false">D44*E44</f>
         <v>67200</v>
       </c>
-      <c r="G44" s="78" t="n">
+      <c r="G44" s="76" t="n">
         <f aca="false">D44*VLOOKUP(B44,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>168000</v>
       </c>
@@ -13218,7 +13453,7 @@
       <c r="B45" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="77" t="str">
+      <c r="C45" s="75" t="str">
         <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$24,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
@@ -13233,38 +13468,38 @@
         <f aca="false">D45*E45</f>
         <v>138400</v>
       </c>
-      <c r="G45" s="78" t="n">
+      <c r="G45" s="76" t="n">
         <f aca="false">D45*VLOOKUP(B45,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="B46" s="79"/>
-      <c r="C46" s="79"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
+      <c r="A46" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
       <c r="F46" s="54" t="n">
         <f aca="false">SUM(F40:F45)</f>
         <v>983050</v>
       </c>
-      <c r="G46" s="80" t="n">
+      <c r="G46" s="78" t="n">
         <f aca="false">SUM(G40:G45)</f>
         <v>2340000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="82" t="s">
-        <v>199</v>
-      </c>
-      <c r="B47" s="82"/>
-      <c r="C47" s="82"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
+      <c r="A47" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" s="80"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -13325,52 +13560,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="83" t="n">
+        <v>200</v>
+      </c>
+      <c r="B3" s="81" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B4" s="83" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13378,7 +13613,7 @@
         <v>73</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$24,4,FALSE())</f>
@@ -13404,8 +13639,8 @@
         <f aca="false">F7*G7</f>
         <v>10912500</v>
       </c>
-      <c r="I7" s="84" t="s">
-        <v>211</v>
+      <c r="I7" s="82" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13413,7 +13648,7 @@
         <v>76</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$24,4,FALSE())</f>
@@ -13439,8 +13674,8 @@
         <f aca="false">F8*G8</f>
         <v>13920000</v>
       </c>
-      <c r="I8" s="84" t="s">
-        <v>212</v>
+      <c r="I8" s="82" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13448,7 +13683,7 @@
         <v>78</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$24,4,FALSE())</f>
@@ -13474,8 +13709,8 @@
         <f aca="false">F9*G9</f>
         <v>4705000</v>
       </c>
-      <c r="I9" s="84" t="s">
-        <v>213</v>
+      <c r="I9" s="82" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13483,7 +13718,7 @@
         <v>75</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$24,4,FALSE())</f>
@@ -13509,8 +13744,8 @@
         <f aca="false">F10*G10</f>
         <v>10687500</v>
       </c>
-      <c r="I10" s="84" t="s">
-        <v>215</v>
+      <c r="I10" s="82" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13518,7 +13753,7 @@
         <v>77</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$24,4,FALSE())</f>
@@ -13544,13 +13779,13 @@
         <f aca="false">F11*G11</f>
         <v>13545000</v>
       </c>
-      <c r="I11" s="84" t="s">
-        <v>216</v>
+      <c r="I11" s="82" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -13565,7 +13800,7 @@
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -13580,7 +13815,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="46" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -13617,12 +13852,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13639,13 +13874,13 @@
         <v>66</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13653,18 +13888,18 @@
         <v>1</v>
       </c>
       <c r="B5" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="83" t="s">
         <v>223</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="D5" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>886000</v>
       </c>
-      <c r="F5" s="86" t="n">
+      <c r="F5" s="84" t="n">
         <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -13680,15 +13915,15 @@
         <v>73</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="D6" s="85" t="s">
-        <v>225</v>
+        <v>209</v>
+      </c>
+      <c r="D6" s="83" t="s">
+        <v>224</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>873000</v>
       </c>
-      <c r="F6" s="86" t="n">
+      <c r="F6" s="84" t="n">
         <v>0.45</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -13704,15 +13939,15 @@
         <v>75</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="85" t="s">
-        <v>226</v>
+        <v>213</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>225</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>855000</v>
       </c>
-      <c r="F7" s="86" t="n">
+      <c r="F7" s="84" t="n">
         <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -13728,15 +13963,15 @@
         <v>76</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="D8" s="85" t="s">
-        <v>227</v>
+        <v>209</v>
+      </c>
+      <c r="D8" s="83" t="s">
+        <v>226</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>928000</v>
       </c>
-      <c r="F8" s="86" t="n">
+      <c r="F8" s="84" t="n">
         <v>0.45</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -13752,15 +13987,15 @@
         <v>77</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="85" t="s">
-        <v>228</v>
+        <v>213</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>227</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>903000</v>
       </c>
-      <c r="F9" s="86" t="n">
+      <c r="F9" s="84" t="n">
         <v>0.45</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -13776,15 +14011,15 @@
         <v>80</v>
       </c>
       <c r="C10" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="85" t="s">
         <v>229</v>
-      </c>
-      <c r="D10" s="87" t="s">
-        <v>230</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>228000</v>
       </c>
-      <c r="F10" s="86" t="n">
+      <c r="F10" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -13800,15 +14035,15 @@
         <v>82</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="87" t="s">
-        <v>231</v>
+        <v>228</v>
+      </c>
+      <c r="D11" s="85" t="s">
+        <v>230</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>202000</v>
       </c>
-      <c r="F11" s="86" t="n">
+      <c r="F11" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -13821,18 +14056,18 @@
         <v>8</v>
       </c>
       <c r="B12" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="85" t="s">
         <v>232</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="87" t="s">
-        <v>233</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F12" s="86" t="n">
+      <c r="F12" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -13848,15 +14083,15 @@
         <v>83</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D13" s="87" t="s">
-        <v>234</v>
+        <v>228</v>
+      </c>
+      <c r="D13" s="85" t="s">
+        <v>233</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F13" s="86" t="n">
+      <c r="F13" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -13869,18 +14104,18 @@
         <v>10</v>
       </c>
       <c r="B14" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="85" t="s">
         <v>235</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D14" s="87" t="s">
-        <v>236</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>213000</v>
       </c>
-      <c r="F14" s="86" t="n">
+      <c r="F14" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -13893,18 +14128,18 @@
         <v>11</v>
       </c>
       <c r="B15" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="85" t="s">
         <v>237</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D15" s="87" t="s">
-        <v>238</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>161000</v>
       </c>
-      <c r="F15" s="86" t="n">
+      <c r="F15" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -13920,15 +14155,15 @@
         <v>84</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D16" s="87" t="s">
-        <v>239</v>
+        <v>228</v>
+      </c>
+      <c r="D16" s="85" t="s">
+        <v>238</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F16" s="86" t="n">
+      <c r="F16" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -13941,18 +14176,18 @@
         <v>13</v>
       </c>
       <c r="B17" s="49" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" s="85" t="s">
         <v>240</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D17" s="87" t="s">
-        <v>241</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F17" s="86" t="n">
+      <c r="F17" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
@@ -13965,18 +14200,18 @@
         <v>14</v>
       </c>
       <c r="B18" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="85" t="s">
         <v>242</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D18" s="87" t="s">
-        <v>243</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>311000</v>
       </c>
-      <c r="F18" s="86" t="n">
+      <c r="F18" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -13989,18 +14224,18 @@
         <v>15</v>
       </c>
       <c r="B19" s="49" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="85" t="s">
         <v>244</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D19" s="87" t="s">
-        <v>245</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>284000</v>
       </c>
-      <c r="F19" s="86" t="n">
+      <c r="F19" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -14013,18 +14248,18 @@
         <v>16</v>
       </c>
       <c r="B20" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="85" t="s">
         <v>246</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D20" s="87" t="s">
-        <v>247</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>331000</v>
       </c>
-      <c r="F20" s="86" t="n">
+      <c r="F20" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -14040,15 +14275,15 @@
         <v>85</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D21" s="87" t="s">
-        <v>248</v>
+        <v>228</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>247</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>346000</v>
       </c>
-      <c r="F21" s="86" t="n">
+      <c r="F21" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -14061,18 +14296,18 @@
         <v>18</v>
       </c>
       <c r="B22" s="49" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" s="85" t="s">
         <v>249</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D22" s="87" t="s">
-        <v>250</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>351000</v>
       </c>
-      <c r="F22" s="86" t="n">
+      <c r="F22" s="84" t="n">
         <v>0.4</v>
       </c>
       <c r="G22" s="10" t="n">
@@ -14081,33 +14316,33 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="88" t="s">
-        <v>251</v>
-      </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
+      <c r="A23" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="86"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>78</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="D24" s="89" t="s">
-        <v>252</v>
-      </c>
-      <c r="E24" s="90" t="n">
+        <v>209</v>
+      </c>
+      <c r="D24" s="87" t="s">
+        <v>251</v>
+      </c>
+      <c r="E24" s="88" t="n">
         <v>941000</v>
       </c>
-      <c r="F24" s="91" t="n">
+      <c r="F24" s="89" t="n">
         <v>0.45</v>
       </c>
       <c r="G24" s="10" t="n">
@@ -14117,7 +14352,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="269">
   <si>
     <r>
       <rPr>
@@ -606,7 +606,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MCC — Schneider </t>
+      <t xml:space="preserve">MCC — Techross </t>
     </r>
     <r>
       <rPr>
@@ -616,7 +616,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제안이 </t>
+      <t xml:space="preserve">기준</t>
     </r>
     <r>
       <rPr>
@@ -627,7 +627,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Techross </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -637,7 +637,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">요구와 일치 </t>
+      <t xml:space="preserve">입력 </t>
     </r>
     <r>
       <rPr>
@@ -648,7 +648,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(Techross </t>
+      <t xml:space="preserve">102 / </t>
     </r>
     <r>
       <rPr>
@@ -658,7 +658,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">출력 </t>
     </r>
     <r>
       <rPr>
@@ -669,32 +669,350 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">54 / AO 4)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 재구성  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Relay·TR </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무관</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: TM241CE40T + TM3DI16×2 + TM3DI8 + TM3DQ16T + TM3DQ8T + TM3AQ2   (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)  /  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제공 점수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">판정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 가격</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원안
+대비 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 금액
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원안
+대비 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원안</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241CE40T + TM3DI16×2 + TM3DI8 + TM3DQ16T + TM3DQ8T + TM3AQ2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
@@ -703,7 +1021,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -713,7 +1031,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
@@ -722,56 +1040,370 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 (Relay·TR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2CH · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40 / AO 2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">✕ 점수 부족</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">채택</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+CPU CE40T</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241CE40T + TM3DI16×5 + TM3DQ16T×2 + TM3DQ8T + TM3AQ4 + TM3XTRA1·XREC1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">104 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">56 / AO 4 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○ 충족</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU CE24T</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241CE24T + TM3DI16×5 + TM3DI8 + TM3DQ16T×3 + TM3AQ4 + TM3XTRA1·XREC1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">102 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58 / AO 4 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전부 견적 단가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심 정리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">② TSU · ANU · ANU-S: Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제안 구성 그대로 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구 충족</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">④ MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -780,402 +1412,135 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 → 버스 확장 불필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 → 버스 확장 부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM3XTRA1/XREC1) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가격 미정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.  TM241CE40T(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">핵심 정리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">② 4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 프로젝트 모두 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Schneider </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제안 구성이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Techross </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요구와 일치합니다 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(MCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Relay·TR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원안 점수 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Techross </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">③ MCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 확장 모듈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개라 버스 확장 부품이 필요 없습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">남은 보완은 서류</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제안 가격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외형도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CAD </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">뿐입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF375623"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">④ TM241CE40T(MCC CPU, </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도 견적에 없어 추정 단가 → </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연 </t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 받은 견적에 없어 추정 단가로 계산 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Schneider</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 실단가 요청 필요</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 두 가지 모두 요청</t>
     </r>
     <r>
       <rPr>
@@ -2192,9 +2557,6 @@
 필요액</t>
   </si>
   <si>
-    <t xml:space="preserve">판정</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="8"/>
@@ -2900,7 +3262,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·  4</t>
+      <t xml:space="preserve">·  MCC</t>
     </r>
     <r>
       <rPr>
@@ -2909,7 +3271,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">개 프로젝트 모두 </t>
+      <t xml:space="preserve">는 </t>
     </r>
     <r>
       <rPr>
@@ -2919,7 +3281,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Schneider </t>
+      <t xml:space="preserve">Techross </t>
     </r>
     <r>
       <rPr>
@@ -2928,7 +3290,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제안 구성 </t>
+      <t xml:space="preserve">기준</t>
     </r>
     <r>
       <rPr>
@@ -2938,7 +3300,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(Techross </t>
+      <t xml:space="preserve">(A</t>
     </r>
     <r>
       <rPr>
@@ -2947,7 +3309,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">안</t>
     </r>
     <r>
       <rPr>
@@ -3152,22 +3514,49 @@
     <t xml:space="preserve">TM3DI16</t>
   </si>
   <si>
+    <t xml:space="preserve">MCC×5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DQ16T</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCC×2</t>
   </si>
   <si>
-    <t xml:space="preserve">TM3DI8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DQ16T</t>
-  </si>
-  <si>
     <t xml:space="preserve">TM3DQ8T</t>
   </si>
   <si>
     <t xml:space="preserve">TM3AQ2</t>
   </si>
   <si>
-    <t xml:space="preserve">ANU-S, MCC</t>
+    <t xml:space="preserve">TM3AQ4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3XTRA1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MCC  ※ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가격 미정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3XREC1</t>
   </si>
   <si>
     <r>
@@ -3178,7 +3567,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">※ TM241CE40T(MCC CPU)</t>
+      <t xml:space="preserve">※ TM241CE40T</t>
     </r>
     <r>
       <rPr>
@@ -3187,7 +3576,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 받은 견적에 없어 추정 단가입니다</t>
+      <t xml:space="preserve">는 추정 단가</t>
     </r>
     <r>
       <rPr>
@@ -3197,7 +3586,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">, TM3XTRA1/XREC1</t>
     </r>
     <r>
       <rPr>
@@ -3206,7 +3595,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실단가를 </t>
+      <t xml:space="preserve">은 가격 미정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가격을 </t>
     </r>
     <r>
       <rPr>
@@ -3521,9 +3948,6 @@
     <t xml:space="preserve">No.</t>
   </si>
   <si>
-    <t xml:space="preserve">구분</t>
-  </si>
-  <si>
     <t xml:space="preserve">검토 항목</t>
   </si>
   <si>
@@ -4471,6 +4895,54 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Techross </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현행 유지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4484,6 +4956,65 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">102 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4CH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">64 / </t>
     </r>
     <r>
@@ -4522,16 +5053,209 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2CH (Techross </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">2CH</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">✕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 · AO 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부족 → 재구성 필요 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: CE40T + TM3DI16×5 + TM3DQ16T×2 + TM3DQ8T + TM3AQ4).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통신</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Serial 1CH + Ethernet 1CH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TM241CE40T: Serial 2CH + Ethernet 1CH</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확장 모듈 수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수를 맞추면 모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9~10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
     </r>
     <r>
       <rPr>
@@ -4552,109 +5276,743 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">64 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2CH</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. RFQ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문서의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현행 유지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">모듈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수가 부족해서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">△</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M241 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접 연결 한도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 초과 → 버스 확장</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM3XTRA1 + TM3XREC1) </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원 용량 검토</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공통</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정격 전압</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TSU·ANU·ANU-S: AC220V, DC24V </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">각각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ MCC: DC24V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TSU·ANU·ANU-S: AC·DC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">각각 제안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ MCC: DC24V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I/O </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(RFQ #1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후보군</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Schneider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: TM3DI8, TM3DQ8R/T/U, TM3AI2H, TM3AQ2 (16·4CH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DI16, TM3DI8, TM3DQ16T, TM3DQ8T, TM3AQ2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후보군 안에서 선택함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. MCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타입 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타입으로만 바꾸면 됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC220V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 릴레이 수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TSU·ANU·ANU-S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Relay·TR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">둘 다 가능</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM241C24R: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 + TR 4 / TM241C40R: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 + TR 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상 문제없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TSU·ANU AC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 릴레이가 필수 점수와 딱 같아서 여유분은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TR — Techross</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 알려줄 것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용 가능해야 함</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EcoStruxure Machine Expert (IEC 61131-3 → ST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제품은 지원하지만 제안서에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'ST </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지원</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4663,36 +6021,19 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대신 제안 점수가 맞다고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Techross </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문구가 없음 → 한 줄 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F6000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4701,749 +6042,72 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MCC </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통신</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Serial 1CH + Ethernet 1CH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TM241CE40T: Serial 2CH + Ethernet 1CH</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MCC </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확장 모듈 수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M241 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 확장 최대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모듈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이내 → 버스 확장 불필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">공통</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정격 전압</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TSU·ANU·ANU-S: AC220V, DC24V </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">각각 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ MCC: DC24V</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TSU·ANU·ANU-S: AC·DC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">각각 제안 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ MCC: DC24V</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">I/O </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모델 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(RFQ #1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">후보군</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Schneider </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">후보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: TM3DI8, TM3DQ8R/T/U, TM3AI2H, TM3AQ2 (16·4CH </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">포함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DI16, TM3DI8, TM3DQ16T, TM3DQ8T, TM3AQ2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">후보군 안에서 선택함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. MCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타입 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">R </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타입으로만 바꾸면 됨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AC220V</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안 릴레이 수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TSU·ANU·ANU-S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Relay·TR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">둘 다 가능</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TM241C24R: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 + TR 4 / TM241C40R: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 + TR 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFQ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상 문제없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TSU·ANU AC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안은 릴레이가 필수 점수와 딱 같아서 여유분은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TR — Techross</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 알려줄 것</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">언어</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용 가능해야 함</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EcoStruxure Machine Expert (IEC 61131-3 → ST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">△</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제품은 지원하지만 제안서에 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'ST </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지원</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F6000"/>
+    <t xml:space="preserve">제안 가격</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년 가격 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Benefit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기재</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Table1 '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제안 가격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -5452,101 +6116,6 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문구가 없음 → 한 줄 추가</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제안 가격</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 가격 기준 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ Benefit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기재</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Table1 '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제안 가격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
@@ -5554,9 +6123,6 @@
       </rPr>
       <t xml:space="preserve">칸 공란</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✕</t>
   </si>
   <si>
     <r>
@@ -7842,17 +8408,36 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-10-06): </t>
+      <t xml:space="preserve">기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현행 유지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
     </r>
     <r>
       <rPr>
@@ -7871,7 +8456,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">64 / </t>
+      <t xml:space="preserve">102 / </t>
     </r>
     <r>
       <rPr>
@@ -7890,7 +8475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">40 (Relay·TR </t>
+      <t xml:space="preserve">54 (Relay·TR </t>
     </r>
     <r>
       <rPr>
@@ -7928,7 +8513,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2CH / Serial 2CH + </t>
+      <t xml:space="preserve">4CH / Serial 1CH + </t>
     </r>
     <r>
       <rPr>
@@ -7947,37 +8532,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1CH — Schneider </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제안과 일치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC24V (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확정</t>
+      <t xml:space="preserve">1CH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC24V (A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안</t>
     </r>
     <r>
       <rPr>
@@ -7998,6 +8574,101 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">제공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">104 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">56 (TR) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4CH / Serial 2CH + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이더넷 → 충족</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.  ※ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">확장 모듈 </t>
     </r>
     <r>
@@ -8008,7 +8679,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">9</t>
     </r>
     <r>
       <rPr>
@@ -8017,7 +8688,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">개 → 버스 확장 불필요</t>
+      <t xml:space="preserve">개 → 버스 확장</t>
     </r>
     <r>
       <rPr>
@@ -8027,7 +8698,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.  ※ TM241CE40T</t>
+      <t xml:space="preserve">(TM3XTRA1/XREC1) </t>
     </r>
     <r>
       <rPr>
@@ -8036,7 +8707,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 받은 견적에 없어 추정 단가</t>
+      <t xml:space="preserve">필요</t>
     </r>
     <r>
       <rPr>
@@ -8046,7 +8717,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(423,450</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -8055,7 +8726,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원</t>
+      <t xml:space="preserve">가격 미정</t>
     </r>
     <r>
       <rPr>
@@ -8065,7 +8736,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) — Schneider </t>
+      <t xml:space="preserve">.  TM241CE40T</t>
     </r>
     <r>
       <rPr>
@@ -8074,45 +8745,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실단가 받으면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단가표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 입력</t>
+      <t xml:space="preserve">는 추정 단가</t>
     </r>
   </si>
   <si>
@@ -8858,9 +9491,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8891,6 +9521,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">TM3DI8</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -9226,9 +9859,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">TM3AQ4</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -9379,6 +10009,68 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">견적에 없어 추정가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 송신 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 수신 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(MCC)</t>
     </r>
   </si>
   <si>
@@ -9496,13 +10188,13 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="\+#,##0;\-#,##0;\-"/>
+    <numFmt numFmtId="166" formatCode="\+#,##0;\-#,##0;\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0%;\-0.0%;\-"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9678,10 +10370,39 @@
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF375623"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -9694,7 +10415,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1F3864"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -9725,12 +10446,10 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1F3864"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -9764,7 +10483,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF1F3864"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
@@ -9807,13 +10526,6 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FF375623"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
       <color rgb="FF7F6000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
@@ -9828,21 +10540,16 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
+      <sz val="14"/>
+      <color rgb="FF375623"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <color rgb="FF375623"/>
+      <color rgb="FFC00000"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
@@ -9859,14 +10566,6 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF7F6000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFC00000"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
@@ -9943,8 +10642,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -9955,8 +10654,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -10028,7 +10727,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10105,11 +10804,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10117,11 +10844,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10129,32 +10868,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="35" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -10165,11 +10892,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10177,11 +10904,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10189,7 +10916,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10201,15 +10928,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10221,7 +10948,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10233,39 +10960,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="37" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="37" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10277,11 +11000,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10289,27 +11016,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10317,7 +11040,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10325,7 +11048,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10341,15 +11064,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="53" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="54" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10369,7 +11092,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10381,11 +11104,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="58" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10680,7 +11403,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -10823,19 +11546,19 @@
         <v>100</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">'프로젝트별 구성'!F46</f>
-        <v>983050</v>
+        <f aca="false">'프로젝트별 구성'!F47</f>
+        <v>1268650</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">C9*D9</f>
-        <v>98305000</v>
+        <v>126865000</v>
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">F9</f>
-        <v>98305000</v>
+        <v>126865000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10851,11 +11574,11 @@
       <c r="E10" s="15"/>
       <c r="F10" s="16" t="n">
         <f aca="false">SUM(F6:F9)</f>
-        <v>328717500</v>
+        <v>357277500</v>
       </c>
       <c r="G10" s="16" t="n">
         <f aca="false">SUM(G6:G9)</f>
-        <v>323317500</v>
+        <v>351877500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10868,151 +11591,255 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="str">
-        <f aca="false">"1대 "&amp;TEXT(D9,"#,##0")&amp;"원 · 연간 "&amp;TEXT(F9,"#,##0")&amp;"원  —  이 중 TM241CE40T "&amp;TEXT(VLOOKUP("TM241CE40T",단가표!$B$5:$G$24,6,FALSE()),"#,##0")&amp;"원은 추정 단가 (견적에 없음) → Schneider 실단가 확인 필요"</f>
-        <v>1대 983,050원 · 연간 98,305,000원  —  이 중 TM241CE40T 423,450원은 추정 단가 (견적에 없음) → Schneider 실단가 확인 필요</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="B14" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="str">
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <f aca="false">VLOOKUP("TM241CE40T",단가표!$B$5:$G$26,6,FALSE())+2*VLOOKUP("TM3DI16",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3DI8",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3DQ16T",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3DQ8T",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3AQ2",단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>983050</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <f aca="false">D15*$C$9</f>
+        <v>98305000</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <f aca="false">'프로젝트별 구성'!F47</f>
+        <v>1268650</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <f aca="false">D16-$D$15</f>
+        <v>285600</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <f aca="false">D16*$C$9</f>
+        <v>126865000</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <f aca="false">F16-$F$15</f>
+        <v>28560000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <f aca="false">VLOOKUP("TM241CE24T",단가표!$B$5:$G$26,6,FALSE())+5*VLOOKUP("TM3DI16",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3DI8",단가표!$B$5:$G$26,6,FALSE())+3*VLOOKUP("TM3DQ16T",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3AQ4",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3XTRA1",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3XREC1",단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>1348300</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <f aca="false">D17-$D$15</f>
+        <v>365250</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <f aca="false">D17*$C$9</f>
+        <v>134830000</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <f aca="false">F17-$F$15</f>
+        <v>36525000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="str">
+        <f aca="false">IF(D16&lt;=D17,"→ 현재 단가로는 A안(CE40T)이 1대 "&amp;TEXT(D17-D16,"#,##0")&amp;"원 저렴 — 단, CE40T 단가는 추정값","→ 현재 단가로는 B안(CE24T)이 1대 "&amp;TEXT(D16-D17,"#,##0")&amp;"원 저렴 — 프로젝트별 구성의 MCC를 B안으로 바꾸는 것 검토")</f>
+        <v>→ 현재 단가로는 A안(CE40T)이 1대 79,650원 저렴 — 단, CE40T 단가는 추정값</v>
+      </c>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27" t="str">
+        <f aca="false">IF(VLOOKUP("TM3XTRA1",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3XREC1",단가표!$B$5:$G$26,6,FALSE())=0,"⚠ 버스 확장 부품(TM3XTRA1/XREC1) 가격 미입력 → A·B안 가격에 0원으로 들어가 있음.  TM241CE40T도 추정 단가.  가격 받으면 단가표 노란 칸에 입력","버스 확장 부품 반영됨 (1대 "&amp;TEXT(VLOOKUP("TM3XTRA1",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3XREC1",단가표!$B$5:$G$26,6,FALSE()),"#,##0")&amp;"원).  TM241CE40T 단가 확인 필요")</f>
+        <v>⚠ 버스 확장 부품(TM3XTRA1/XREC1) 가격 미입력 → A·B안 가격에 0원으로 들어가 있음.  TM241CE40T도 추정 단가.  가격 받으면 단가표 노란 칸에 입력</v>
+      </c>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="str">
         <f aca="false">"① 연간 구매금액: DC24V 기준 약 "&amp;TEXT(F10/100000000,"0.00")&amp;"억 원,  AC220V 기준 약 "&amp;TEXT(G10/100000000,"0.00")&amp;"억 원"</f>
-        <v>① 연간 구매금액: DC24V 기준 약 3.29억 원,  AC220V 기준 약 3.23억 원</v>
-      </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-    </row>
-    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="str">
+        <v>① 연간 구매금액: DC24V 기준 약 3.57억 원,  AC220V 기준 약 3.52억 원</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="31" t="str">
+        <f aca="false">"③ MCC: Schneider 원안은 Techross 기준보다 입력 38 · 출력 14 · AO 2 부족 → Techross 기준으로 재구성 (출력은 TR 그대로). 1대 "&amp;TEXT(D16,"#,##0")&amp;"원, 원안보다 연 "&amp;TEXT(G16,"#,##0")&amp;"원 증가"</f>
+        <v>③ MCC: Schneider 원안은 Techross 기준보다 입력 38 · 출력 14 · AO 2 부족 → Techross 기준으로 재구성 (출력은 TR 그대로). 1대 1,268,650원, 원안보다 연 28,560,000원 증가</v>
+      </c>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="32" t="str">
         <f aca="false">"⑥ CPU 할인율을 "&amp;TEXT('CPU 할인 효과'!B3,"0.00")&amp;" → "&amp;TEXT('CPU 할인 효과'!B4,"0.00")&amp;"으로 받으면 연간 약 "&amp;TEXT('CPU 할인 효과'!H13/10000,"#,##0")&amp;"만 원 절감 (DC24V 기준)"</f>
         <v>⑥ CPU 할인율을 0.45 → 0.40으로 받으면 연간 약 2,954만 원 절감 (DC24V 기준)</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="str">
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="str">
         <f aca="false">"⑧ LS 타겟 기준 연간 마진 (DC24V): "&amp;IF(ISNUMBER('마진 계산'!E30),TEXT('마진 계산'!E30,"#,##0")&amp;"원 (마진율 "&amp;TEXT('마진 계산'!F30,"0.0%")&amp;")  /  희망 마진("&amp;TEXT('마진 계산'!B4,"0%")&amp;")까지 연간 추가 특가 "&amp;TEXT('마진 계산'!G30,"#,##0")&amp;"원 필요","LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
         <v>⑧ LS 타겟 기준 연간 마진 (DC24V): LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-    </row>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="str">
-        <f aca="false">"⑨ Schneider 제안 검토: 반드시 수정 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"✕")&amp;"건, 보완 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"△")&amp;"건  (구성은 4개 프로젝트 모두 적합)  → 'Schneider 제안 검토' 시트"</f>
-        <v>⑨ Schneider 제안 검토: 반드시 수정 2건, 보완 5건  (구성은 4개 프로젝트 모두 적합)  → 'Schneider 제안 검토' 시트</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="34" t="str">
+        <f aca="false">"⑨ Schneider 제안 검토: 반드시 수정 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"✕")&amp;"건, 보완 "&amp;COUNTIF('Schneider 제안 검토'!F7:F24,"△")&amp;"건  → 'Schneider 제안 검토' 시트"</f>
+        <v>⑨ Schneider 제안 검토: 반드시 수정 3건, 보완 6건  → 'Schneider 제안 검토' 시트</v>
+      </c>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11044,29 +11871,29 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>30</v>
+      <c r="A1" s="35" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="29" t="n">
+      <c r="A4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="37" t="n">
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>34</v>
+      <c r="A6" s="38" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11074,51 +11901,51 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="32" t="n">
+      <c r="B8" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="39" t="n">
         <f aca="false">요약!C6</f>
         <v>200</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F9</f>
         <v>392850</v>
       </c>
-      <c r="F8" s="34" t="str">
+      <c r="F8" s="41" t="str">
         <f aca="false">IF(D8="","",D8-E8)</f>
         <v/>
       </c>
-      <c r="G8" s="35" t="str">
+      <c r="G8" s="42" t="str">
         <f aca="false">IF(OR(D8="",D8=0),"",F8/D8)</f>
         <v/>
       </c>
@@ -11126,35 +11953,35 @@
         <f aca="false">IF(D8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="I8" s="34" t="str">
+      <c r="I8" s="41" t="str">
         <f aca="false">IF(D8="","",C8*F8)</f>
         <v/>
       </c>
-      <c r="J8" s="36" t="s">
-        <v>44</v>
+      <c r="J8" s="43" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="32" t="n">
+      <c r="B9" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="39" t="n">
         <f aca="false">요약!C6</f>
         <v>200</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="40"/>
       <c r="E9" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F11</f>
         <v>384750</v>
       </c>
-      <c r="F9" s="34" t="str">
+      <c r="F9" s="41" t="str">
         <f aca="false">IF(D9="","",D9-E9)</f>
         <v/>
       </c>
-      <c r="G9" s="35" t="str">
+      <c r="G9" s="42" t="str">
         <f aca="false">IF(OR(D9="",D9=0),"",F9/D9)</f>
         <v/>
       </c>
@@ -11162,7 +11989,7 @@
         <f aca="false">IF(D9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="I9" s="34" t="str">
+      <c r="I9" s="41" t="str">
         <f aca="false">IF(D9="","",C9*F9)</f>
         <v/>
       </c>
@@ -11171,23 +11998,23 @@
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="32" t="n">
+      <c r="B10" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="39" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F19</f>
         <v>417600</v>
       </c>
-      <c r="F10" s="34" t="str">
+      <c r="F10" s="41" t="str">
         <f aca="false">IF(D10="","",D10-E10)</f>
         <v/>
       </c>
-      <c r="G10" s="35" t="str">
+      <c r="G10" s="42" t="str">
         <f aca="false">IF(OR(D10="",D10=0),"",F10/D10)</f>
         <v/>
       </c>
@@ -11195,7 +12022,7 @@
         <f aca="false">IF(D10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="I10" s="34" t="str">
+      <c r="I10" s="41" t="str">
         <f aca="false">IF(D10="","",C10*F10)</f>
         <v/>
       </c>
@@ -11204,23 +12031,23 @@
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="32" t="n">
+      <c r="B11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="39" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="40"/>
       <c r="E11" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F21</f>
         <v>406350</v>
       </c>
-      <c r="F11" s="34" t="str">
+      <c r="F11" s="41" t="str">
         <f aca="false">IF(D11="","",D11-E11)</f>
         <v/>
       </c>
-      <c r="G11" s="35" t="str">
+      <c r="G11" s="42" t="str">
         <f aca="false">IF(OR(D11="",D11=0),"",F11/D11)</f>
         <v/>
       </c>
@@ -11228,7 +12055,7 @@
         <f aca="false">IF(D11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="I11" s="34" t="str">
+      <c r="I11" s="41" t="str">
         <f aca="false">IF(D11="","",C11*F11)</f>
         <v/>
       </c>
@@ -11237,23 +12064,23 @@
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="32" t="n">
+      <c r="B12" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="39" t="n">
         <f aca="false">요약!C8</f>
         <v>50</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="40"/>
       <c r="E12" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F30</f>
         <v>531250</v>
       </c>
-      <c r="F12" s="34" t="str">
+      <c r="F12" s="41" t="str">
         <f aca="false">IF(D12="","",D12-E12)</f>
         <v/>
       </c>
-      <c r="G12" s="35" t="str">
+      <c r="G12" s="42" t="str">
         <f aca="false">IF(OR(D12="",D12=0),"",F12/D12)</f>
         <v/>
       </c>
@@ -11261,7 +12088,7 @@
         <f aca="false">IF(D12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="I12" s="34" t="str">
+      <c r="I12" s="41" t="str">
         <f aca="false">IF(D12="","",C12*F12)</f>
         <v/>
       </c>
@@ -11270,23 +12097,23 @@
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="32" t="n">
+      <c r="B13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="39" t="n">
         <f aca="false">요약!C8</f>
         <v>50</v>
       </c>
-      <c r="D13" s="33"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F33</f>
         <v>523150</v>
       </c>
-      <c r="F13" s="34" t="str">
+      <c r="F13" s="41" t="str">
         <f aca="false">IF(D13="","",D13-E13)</f>
         <v/>
       </c>
-      <c r="G13" s="35" t="str">
+      <c r="G13" s="42" t="str">
         <f aca="false">IF(OR(D13="",D13=0),"",F13/D13)</f>
         <v/>
       </c>
@@ -11294,7 +12121,7 @@
         <f aca="false">IF(D13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="I13" s="34" t="str">
+      <c r="I13" s="41" t="str">
         <f aca="false">IF(D13="","",C13*F13)</f>
         <v/>
       </c>
@@ -11303,23 +12130,23 @@
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="32" t="n">
+      <c r="B14" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="39" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="9" t="n">
-        <f aca="false">'프로젝트별 구성'!F46</f>
-        <v>983050</v>
-      </c>
-      <c r="F14" s="34" t="str">
+        <f aca="false">'프로젝트별 구성'!F47</f>
+        <v>1268650</v>
+      </c>
+      <c r="F14" s="41" t="str">
         <f aca="false">IF(D14="","",D14-E14)</f>
         <v/>
       </c>
-      <c r="G14" s="35" t="str">
+      <c r="G14" s="42" t="str">
         <f aca="false">IF(OR(D14="",D14=0),"",F14/D14)</f>
         <v/>
       </c>
@@ -11327,14 +12154,14 @@
         <f aca="false">IF(D14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="I14" s="34" t="str">
+      <c r="I14" s="41" t="str">
         <f aca="false">IF(D14="","",C14*F14)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
-        <v>46</v>
+      <c r="A17" s="38" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11342,39 +12169,39 @@
         <v>4</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>43</v>
+      <c r="B19" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="C19" s="9" t="str">
         <f aca="false">IF(D8="","",ROUND(D8*(1-$B$4),0))</f>
@@ -11384,19 +12211,19 @@
         <f aca="false">E8</f>
         <v>392850</v>
       </c>
-      <c r="E19" s="37" t="str">
+      <c r="E19" s="44" t="str">
         <f aca="false">IF(C19="","",MAX(D19-C19,0))</f>
         <v/>
       </c>
-      <c r="F19" s="38" t="str">
+      <c r="F19" s="45" t="str">
         <f aca="false">IF(C19="","",E19/D19)</f>
         <v/>
       </c>
-      <c r="G19" s="39" t="n">
+      <c r="G19" s="46" t="n">
         <f aca="false">IFERROR(D19/'프로젝트별 구성'!G9,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H19" s="40" t="str">
+      <c r="H19" s="47" t="str">
         <f aca="false">IF(C19="","",IFERROR(MIN(C19,D19)/'프로젝트별 구성'!G9,""))</f>
         <v/>
       </c>
@@ -11404,7 +12231,7 @@
         <f aca="false">IF(C19="","",E19*C8)</f>
         <v/>
       </c>
-      <c r="J19" s="41" t="str">
+      <c r="J19" s="48" t="str">
         <f aca="false">IF(C19="","타겟 입력 전",IF(E19=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -11413,8 +12240,8 @@
       <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>45</v>
+      <c r="B20" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="C20" s="9" t="str">
         <f aca="false">IF(D9="","",ROUND(D9*(1-$B$4),0))</f>
@@ -11424,19 +12251,19 @@
         <f aca="false">E9</f>
         <v>384750</v>
       </c>
-      <c r="E20" s="37" t="str">
+      <c r="E20" s="44" t="str">
         <f aca="false">IF(C20="","",MAX(D20-C20,0))</f>
         <v/>
       </c>
-      <c r="F20" s="38" t="str">
+      <c r="F20" s="45" t="str">
         <f aca="false">IF(C20="","",E20/D20)</f>
         <v/>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="46" t="n">
         <f aca="false">IFERROR(D20/'프로젝트별 구성'!G11,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H20" s="40" t="str">
+      <c r="H20" s="47" t="str">
         <f aca="false">IF(C20="","",IFERROR(MIN(C20,D20)/'프로젝트별 구성'!G11,""))</f>
         <v/>
       </c>
@@ -11444,7 +12271,7 @@
         <f aca="false">IF(C20="","",E20*C9)</f>
         <v/>
       </c>
-      <c r="J20" s="41" t="str">
+      <c r="J20" s="48" t="str">
         <f aca="false">IF(C20="","타겟 입력 전",IF(E20=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -11453,8 +12280,8 @@
       <c r="A21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>43</v>
+      <c r="B21" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="C21" s="9" t="str">
         <f aca="false">IF(D10="","",ROUND(D10*(1-$B$4),0))</f>
@@ -11464,19 +12291,19 @@
         <f aca="false">E10</f>
         <v>417600</v>
       </c>
-      <c r="E21" s="37" t="str">
+      <c r="E21" s="44" t="str">
         <f aca="false">IF(C21="","",MAX(D21-C21,0))</f>
         <v/>
       </c>
-      <c r="F21" s="38" t="str">
+      <c r="F21" s="45" t="str">
         <f aca="false">IF(C21="","",E21/D21)</f>
         <v/>
       </c>
-      <c r="G21" s="39" t="n">
+      <c r="G21" s="46" t="n">
         <f aca="false">IFERROR(D21/'프로젝트별 구성'!G19,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H21" s="40" t="str">
+      <c r="H21" s="47" t="str">
         <f aca="false">IF(C21="","",IFERROR(MIN(C21,D21)/'프로젝트별 구성'!G19,""))</f>
         <v/>
       </c>
@@ -11484,7 +12311,7 @@
         <f aca="false">IF(C21="","",E21*C10)</f>
         <v/>
       </c>
-      <c r="J21" s="41" t="str">
+      <c r="J21" s="48" t="str">
         <f aca="false">IF(C21="","타겟 입력 전",IF(E21=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -11493,8 +12320,8 @@
       <c r="A22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="31" t="s">
-        <v>45</v>
+      <c r="B22" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="C22" s="9" t="str">
         <f aca="false">IF(D11="","",ROUND(D11*(1-$B$4),0))</f>
@@ -11504,19 +12331,19 @@
         <f aca="false">E11</f>
         <v>406350</v>
       </c>
-      <c r="E22" s="37" t="str">
+      <c r="E22" s="44" t="str">
         <f aca="false">IF(C22="","",MAX(D22-C22,0))</f>
         <v/>
       </c>
-      <c r="F22" s="38" t="str">
+      <c r="F22" s="45" t="str">
         <f aca="false">IF(C22="","",E22/D22)</f>
         <v/>
       </c>
-      <c r="G22" s="39" t="n">
+      <c r="G22" s="46" t="n">
         <f aca="false">IFERROR(D22/'프로젝트별 구성'!G21,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H22" s="40" t="str">
+      <c r="H22" s="47" t="str">
         <f aca="false">IF(C22="","",IFERROR(MIN(C22,D22)/'프로젝트별 구성'!G21,""))</f>
         <v/>
       </c>
@@ -11524,7 +12351,7 @@
         <f aca="false">IF(C22="","",E22*C11)</f>
         <v/>
       </c>
-      <c r="J22" s="41" t="str">
+      <c r="J22" s="48" t="str">
         <f aca="false">IF(C22="","타겟 입력 전",IF(E22=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -11533,8 +12360,8 @@
       <c r="A23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>43</v>
+      <c r="B23" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="C23" s="9" t="str">
         <f aca="false">IF(D12="","",ROUND(D12*(1-$B$4),0))</f>
@@ -11544,19 +12371,19 @@
         <f aca="false">E12</f>
         <v>531250</v>
       </c>
-      <c r="E23" s="37" t="str">
+      <c r="E23" s="44" t="str">
         <f aca="false">IF(C23="","",MAX(D23-C23,0))</f>
         <v/>
       </c>
-      <c r="F23" s="38" t="str">
+      <c r="F23" s="45" t="str">
         <f aca="false">IF(C23="","",E23/D23)</f>
         <v/>
       </c>
-      <c r="G23" s="39" t="n">
+      <c r="G23" s="46" t="n">
         <f aca="false">IFERROR(D23/'프로젝트별 구성'!G30,"")</f>
         <v>0.435808039376538</v>
       </c>
-      <c r="H23" s="40" t="str">
+      <c r="H23" s="47" t="str">
         <f aca="false">IF(C23="","",IFERROR(MIN(C23,D23)/'프로젝트별 구성'!G30,""))</f>
         <v/>
       </c>
@@ -11564,7 +12391,7 @@
         <f aca="false">IF(C23="","",E23*C12)</f>
         <v/>
       </c>
-      <c r="J23" s="41" t="str">
+      <c r="J23" s="48" t="str">
         <f aca="false">IF(C23="","타겟 입력 전",IF(E23=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -11573,8 +12400,8 @@
       <c r="A24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="31" t="s">
-        <v>45</v>
+      <c r="B24" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="C24" s="9" t="str">
         <f aca="false">IF(D13="","",ROUND(D13*(1-$B$4),0))</f>
@@ -11584,19 +12411,19 @@
         <f aca="false">E13</f>
         <v>523150</v>
       </c>
-      <c r="E24" s="37" t="str">
+      <c r="E24" s="44" t="str">
         <f aca="false">IF(C24="","",MAX(D24-C24,0))</f>
         <v/>
       </c>
-      <c r="F24" s="38" t="str">
+      <c r="F24" s="45" t="str">
         <f aca="false">IF(C24="","",E24/D24)</f>
         <v/>
       </c>
-      <c r="G24" s="39" t="n">
+      <c r="G24" s="46" t="n">
         <f aca="false">IFERROR(D24/'프로젝트별 구성'!G33,"")</f>
         <v>0.435595337218984</v>
       </c>
-      <c r="H24" s="40" t="str">
+      <c r="H24" s="47" t="str">
         <f aca="false">IF(C24="","",IFERROR(MIN(C24,D24)/'프로젝트별 구성'!G33,""))</f>
         <v/>
       </c>
@@ -11604,7 +12431,7 @@
         <f aca="false">IF(C24="","",E24*C13)</f>
         <v/>
       </c>
-      <c r="J24" s="41" t="str">
+      <c r="J24" s="48" t="str">
         <f aca="false">IF(C24="","타겟 입력 전",IF(E24=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -11613,8 +12440,8 @@
       <c r="A25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>43</v>
+      <c r="B25" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="C25" s="9" t="str">
         <f aca="false">IF(D14="","",ROUND(D14*(1-$B$4),0))</f>
@@ -11622,124 +12449,124 @@
       </c>
       <c r="D25" s="9" t="n">
         <f aca="false">E14</f>
-        <v>983050</v>
-      </c>
-      <c r="E25" s="37" t="str">
+        <v>1268650</v>
+      </c>
+      <c r="E25" s="44" t="str">
         <f aca="false">IF(C25="","",MAX(D25-C25,0))</f>
         <v/>
       </c>
-      <c r="F25" s="38" t="str">
+      <c r="F25" s="45" t="str">
         <f aca="false">IF(C25="","",E25/D25)</f>
         <v/>
       </c>
-      <c r="G25" s="39" t="n">
-        <f aca="false">IFERROR(D25/'프로젝트별 구성'!G46,"")</f>
-        <v>0.420106837606838</v>
-      </c>
-      <c r="H25" s="40" t="str">
-        <f aca="false">IF(C25="","",IFERROR(MIN(C25,D25)/'프로젝트별 구성'!G46,""))</f>
+      <c r="G25" s="46" t="n">
+        <f aca="false">IFERROR(D25/'프로젝트별 구성'!G47,"")</f>
+        <v>0.415406024885396</v>
+      </c>
+      <c r="H25" s="47" t="str">
+        <f aca="false">IF(C25="","",IFERROR(MIN(C25,D25)/'프로젝트별 구성'!G47,""))</f>
         <v/>
       </c>
       <c r="I25" s="10" t="str">
         <f aca="false">IF(C25="","",E25*C14)</f>
         <v/>
       </c>
-      <c r="J25" s="41" t="str">
+      <c r="J25" s="48" t="str">
         <f aca="false">IF(C25="","타겟 입력 전",IF(E25=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
-        <v>54</v>
+      <c r="A26" s="43" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30" t="s">
-        <v>55</v>
+      <c r="A28" s="38" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="42"/>
+      <c r="A30" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="49"/>
       <c r="C30" s="9" t="n">
         <f aca="false">C8*E8+C10*E10+C12*E12+C14*E14</f>
-        <v>328717500</v>
+        <v>357277500</v>
       </c>
       <c r="D30" s="9" t="str">
         <f aca="false">IF((D8="")+(D10="")+(D12="")+(D14="")&gt;0,"타겟 "&amp;((D8="")+(D10="")+(D12="")+(D14=""))&amp;"건 미입력",H8+H10+H12+H14)</f>
         <v>타겟 4건 미입력</v>
       </c>
-      <c r="E30" s="43" t="str">
+      <c r="E30" s="50" t="str">
         <f aca="false">IF(ISNUMBER(D30),D30-C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="44" t="str">
+      <c r="F30" s="51" t="str">
         <f aca="false">IF(ISNUMBER(D30),E30/D30,"")</f>
         <v/>
       </c>
-      <c r="G30" s="45" t="str">
+      <c r="G30" s="52" t="str">
         <f aca="false">IF(ISNUMBER(D30),I19+I21+I23+I25,"")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="42"/>
+      <c r="A31" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="49"/>
       <c r="C31" s="9" t="n">
         <f aca="false">C9*E9+C11*E11+C13*E13+C14*E14</f>
-        <v>323317500</v>
+        <v>351877500</v>
       </c>
       <c r="D31" s="9" t="str">
         <f aca="false">IF((D9="")+(D11="")+(D13="")+(D14="")&gt;0,"타겟 "&amp;((D9="")+(D11="")+(D13="")+(D14=""))&amp;"건 미입력",H9+H11+H13+H14)</f>
         <v>타겟 4건 미입력</v>
       </c>
-      <c r="E31" s="43" t="str">
+      <c r="E31" s="50" t="str">
         <f aca="false">IF(ISNUMBER(D31),D31-C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="44" t="str">
+      <c r="F31" s="51" t="str">
         <f aca="false">IF(ISNUMBER(D31),E31/D31,"")</f>
         <v/>
       </c>
-      <c r="G31" s="45" t="str">
+      <c r="G31" s="52" t="str">
         <f aca="false">IF(ISNUMBER(D31),I20+I22+I24+I25,"")</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="46" t="s">
-        <v>61</v>
+      <c r="A33" s="53" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>62</v>
+      <c r="A34" s="54" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -11781,7 +12608,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -11795,54 +12622,54 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
-        <v>63</v>
+      <c r="A1" s="55" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>73</v>
+      <c r="A5" s="56" t="s">
+        <v>86</v>
       </c>
       <c r="B5" s="7" t="str">
-        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$24,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>392850</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="57" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -11850,37 +12677,37 @@
         <f aca="false">C5*D5</f>
         <v>98212500</v>
       </c>
-      <c r="F5" s="50" t="n">
+      <c r="F5" s="57" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">C5*F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="51" t="s">
-        <v>74</v>
+      <c r="H5" s="58" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49" t="s">
-        <v>75</v>
+      <c r="A6" s="56" t="s">
+        <v>88</v>
       </c>
       <c r="B6" s="7" t="str">
-        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$24,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>384750</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="57" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">C6*D6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="50" t="n">
+      <c r="F6" s="57" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -11888,23 +12715,23 @@
         <f aca="false">C6*F6</f>
         <v>96187500</v>
       </c>
-      <c r="H6" s="51" t="s">
-        <v>74</v>
+      <c r="H6" s="58" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>76</v>
+      <c r="A7" s="56" t="s">
+        <v>89</v>
       </c>
       <c r="B7" s="7" t="str">
-        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$24,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>417600</v>
       </c>
-      <c r="D7" s="50" t="n">
+      <c r="D7" s="57" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -11912,37 +12739,37 @@
         <f aca="false">C7*D7</f>
         <v>125280000</v>
       </c>
-      <c r="F7" s="50" t="n">
+      <c r="F7" s="57" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">C7*F7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="58" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>77</v>
+      <c r="A8" s="56" t="s">
+        <v>90</v>
       </c>
       <c r="B8" s="7" t="str">
-        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$24,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>406350</v>
       </c>
-      <c r="D8" s="50" t="n">
+      <c r="D8" s="57" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">C8*D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="50" t="n">
+      <c r="F8" s="57" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -11950,23 +12777,23 @@
         <f aca="false">C8*F8</f>
         <v>121905000</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="58" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>78</v>
+      <c r="A9" s="56" t="s">
+        <v>91</v>
       </c>
       <c r="B9" s="7" t="str">
-        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$24,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU + 이더넷 (입력 24 / 출력 16) — MCC, 견적에 없어 추정가</v>
       </c>
-      <c r="C9" s="37" t="n">
-        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$24,6,FALSE())</f>
+      <c r="C9" s="44" t="n">
+        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>423450</v>
       </c>
-      <c r="D9" s="50" t="n">
+      <c r="D9" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -11974,7 +12801,7 @@
         <f aca="false">C9*D9</f>
         <v>42345000</v>
       </c>
-      <c r="F9" s="50" t="n">
+      <c r="F9" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -11982,207 +12809,271 @@
         <f aca="false">C9*F9</f>
         <v>42345000</v>
       </c>
-      <c r="H9" s="52" t="s">
-        <v>79</v>
+      <c r="H9" s="59" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="s">
-        <v>80</v>
+      <c r="A10" s="56" t="s">
+        <v>93</v>
       </c>
       <c r="B10" s="7" t="str">
-        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$24,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>91200</v>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="57" t="n">
+        <f aca="false">5*요약!$C$9</f>
+        <v>500</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <f aca="false">C10*D10</f>
+        <v>45600000</v>
+      </c>
+      <c r="F10" s="57" t="n">
+        <f aca="false">5*요약!$C$9</f>
+        <v>500</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <f aca="false">C10*F10</f>
+        <v>45600000</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>트랜지스터 출력 16점</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>90800</v>
+      </c>
+      <c r="D11" s="57" t="n">
         <f aca="false">2*요약!$C$9</f>
         <v>200</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <f aca="false">C10*D10</f>
-        <v>18240000</v>
-      </c>
-      <c r="F10" s="50" t="n">
+      <c r="E11" s="9" t="n">
+        <f aca="false">C11*D11</f>
+        <v>18160000</v>
+      </c>
+      <c r="F11" s="57" t="n">
         <f aca="false">2*요약!$C$9</f>
         <v>200</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <f aca="false">C10*F10</f>
-        <v>18240000</v>
-      </c>
-      <c r="H10" s="51" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="7" t="str">
-        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>디지털 입력 8점</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>80800</v>
-      </c>
-      <c r="D11" s="50" t="n">
+      <c r="G11" s="9" t="n">
+        <f aca="false">C11*F11</f>
+        <v>18160000</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>트랜지스터 출력 8점</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>67200</v>
+      </c>
+      <c r="D12" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <f aca="false">C11*D11</f>
-        <v>8080000</v>
-      </c>
-      <c r="F11" s="50" t="n">
+      <c r="E12" s="9" t="n">
+        <f aca="false">C12*D12</f>
+        <v>6720000</v>
+      </c>
+      <c r="F12" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <f aca="false">C11*F11</f>
-        <v>8080000</v>
-      </c>
-      <c r="H11" s="51" t="s">
+      <c r="G12" s="9" t="n">
+        <f aca="false">C12*F12</f>
+        <v>6720000</v>
+      </c>
+      <c r="H12" s="58" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="7" t="str">
-        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>트랜지스터 출력 16점</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>90800</v>
-      </c>
-      <c r="D12" s="50" t="n">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>아날로그 출력 2CH</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>138400</v>
+      </c>
+      <c r="D13" s="57" t="n">
+        <f aca="false">1*요약!$C$8</f>
+        <v>50</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <f aca="false">C13*D13</f>
+        <v>6920000</v>
+      </c>
+      <c r="F13" s="57" t="n">
+        <f aca="false">1*요약!$C$8</f>
+        <v>50</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <f aca="false">C13*F13</f>
+        <v>6920000</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>아날로그 출력 4CH</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>140400</v>
+      </c>
+      <c r="D14" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <f aca="false">C12*D12</f>
-        <v>9080000</v>
-      </c>
-      <c r="F12" s="50" t="n">
+      <c r="E14" s="9" t="n">
+        <f aca="false">C14*D14</f>
+        <v>14040000</v>
+      </c>
+      <c r="F14" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <f aca="false">C12*F12</f>
-        <v>9080000</v>
-      </c>
-      <c r="H12" s="51" t="s">
+      <c r="G14" s="9" t="n">
+        <f aca="false">C14*F14</f>
+        <v>14040000</v>
+      </c>
+      <c r="H14" s="58" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="7" t="str">
-        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>트랜지스터 출력 8점</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>67200</v>
-      </c>
-      <c r="D13" s="50" t="n">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="7" t="str">
+        <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>TM3 버스 확장 송신 (MCC)</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">C13*D13</f>
-        <v>6720000</v>
-      </c>
-      <c r="F13" s="50" t="n">
+      <c r="E15" s="9" t="n">
+        <f aca="false">C15*D15</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="57" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <f aca="false">C13*F13</f>
-        <v>6720000</v>
-      </c>
-      <c r="H13" s="51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="7" t="str">
-        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>아날로그 출력 2CH</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>138400</v>
-      </c>
-      <c r="D14" s="50" t="n">
-        <f aca="false">1*요약!$C$8+1*요약!$C$9</f>
-        <v>150</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <f aca="false">C14*D14</f>
-        <v>20760000</v>
-      </c>
-      <c r="F14" s="50" t="n">
-        <f aca="false">1*요약!$C$8+1*요약!$C$9</f>
-        <v>150</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <f aca="false">C14*F14</f>
-        <v>20760000</v>
-      </c>
-      <c r="H14" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="G15" s="9" t="n">
+        <f aca="false">C15*F15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="7" t="str">
+        <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>TM3 버스 확장 수신 (MCC)</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="57" t="n">
+        <f aca="false">1*요약!$C$9</f>
+        <v>100</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <f aca="false">C16*D16</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="57" t="n">
+        <f aca="false">1*요약!$C$9</f>
+        <v>100</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <f aca="false">C16*F16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="53" t="n">
-        <f aca="false">SUM(D5:D14)</f>
-        <v>1300</v>
-      </c>
-      <c r="E15" s="54" t="n">
-        <f aca="false">SUM(E5:E14)</f>
-        <v>328717500</v>
-      </c>
-      <c r="F15" s="53" t="n">
-        <f aca="false">SUM(F5:F14)</f>
-        <v>1300</v>
-      </c>
-      <c r="G15" s="54" t="n">
-        <f aca="false">SUM(G5:G14)</f>
-        <v>323317500</v>
-      </c>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="55" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="55" t="s">
-        <v>88</v>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="60" t="n">
+        <f aca="false">SUM(D5:D16)</f>
+        <v>1800</v>
+      </c>
+      <c r="E17" s="61" t="n">
+        <f aca="false">SUM(E5:E16)</f>
+        <v>357277500</v>
+      </c>
+      <c r="F17" s="60" t="n">
+        <f aca="false">SUM(F5:F16)</f>
+        <v>1800</v>
+      </c>
+      <c r="G17" s="61" t="n">
+        <f aca="false">SUM(G5:G16)</f>
+        <v>351877500</v>
+      </c>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="62" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="62" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12212,485 +13103,485 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>89</v>
+      <c r="A1" s="35" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="59" t="str">
+      <c r="A3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="65" t="str">
         <f aca="false">"✕ "&amp;COUNTIF(F7:F24,"✕")&amp;"건   △ "&amp;COUNTIF(F7:F24,"△")&amp;"건   ○ "&amp;COUNTIF(F7:F24,"○")&amp;"건"</f>
-        <v>✕ 2건   △ 5건   ○ 11건</v>
-      </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
+        <v>✕ 3건   △ 6건   ○ 9건</v>
+      </c>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="62" t="s">
-        <v>102</v>
+      <c r="B7" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>117</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="62" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="68" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>107</v>
+      <c r="B8" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>122</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="62" t="s">
-        <v>109</v>
+        <v>123</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="n">
+      <c r="A9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="62" t="s">
-        <v>111</v>
+      <c r="B9" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>126</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="62" t="s">
-        <v>113</v>
+        <v>127</v>
+      </c>
+      <c r="F9" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="n">
+      <c r="A10" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>114</v>
+      <c r="B10" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>129</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="68" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="E10" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="62" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="62" t="s">
+      <c r="C11" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="62" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="62" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="n">
+      <c r="G12" s="68" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>126</v>
+      <c r="B13" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>142</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>129</v>
+        <v>143</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="73" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>131</v>
+      <c r="B14" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="74" t="s">
+        <v>148</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="62" t="s">
-        <v>125</v>
+        <v>150</v>
+      </c>
+      <c r="F14" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>134</v>
+      <c r="B15" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>151</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="68" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="G17" s="75" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="62" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F17" s="65" t="s">
+      <c r="G18" s="71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="F19" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="G17" s="66" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="64" t="s">
+      <c r="G19" s="73" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="66" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="67" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" s="68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="62" t="s">
-        <v>154</v>
-      </c>
-      <c r="F19" s="65" t="s">
+      <c r="C20" s="74" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F20" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="74" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="G19" s="69" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="D21" s="62" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="65" t="s">
+      <c r="G21" s="73" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="G21" s="69" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="B22" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="61" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="65" t="s">
+      <c r="G22" s="75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="F23" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" s="76" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="G22" s="66" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="62" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="62" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="67" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="70" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="D24" s="62" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="62" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" s="65" t="s">
-        <v>145</v>
-      </c>
-      <c r="G24" s="69" t="s">
-        <v>176</v>
+      <c r="G24" s="73" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71" t="s">
-        <v>177</v>
+      <c r="A26" s="77" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
+      <c r="A27" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12713,7 +13604,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
@@ -12725,781 +13616,806 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
-        <v>179</v>
+      <c r="A1" s="55" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="73" t="s">
+      <c r="A5" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
+      <c r="A6" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="75" t="str">
-        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A8" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="81" t="str">
+        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>392850</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">D8*E8</f>
         <v>392850</v>
       </c>
-      <c r="G8" s="76" t="n">
-        <f aca="false">D8*VLOOKUP(B8,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G8" s="82" t="n">
+        <f aca="false">D8*VLOOKUP(B8,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>873000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="54" t="n">
+      <c r="A9" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="61" t="n">
         <f aca="false">SUM(F8:F8)</f>
         <v>392850</v>
       </c>
-      <c r="G9" s="78" t="n">
+      <c r="G9" s="84" t="n">
         <f aca="false">SUM(G8:G8)</f>
         <v>873000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="75" t="str">
-        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A10" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="81" t="str">
+        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>384750</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">D10*E10</f>
         <v>384750</v>
       </c>
-      <c r="G10" s="76" t="n">
-        <f aca="false">D10*VLOOKUP(B10,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G10" s="82" t="n">
+        <f aca="false">D10*VLOOKUP(B10,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>855000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="54" t="n">
+      <c r="A11" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="61" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>384750</v>
       </c>
-      <c r="G11" s="78" t="n">
+      <c r="G11" s="84" t="n">
         <f aca="false">SUM(G10:G10)</f>
         <v>855000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
+      <c r="A12" s="85" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="73" t="s">
+      <c r="A15" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B16" s="74" t="s">
-        <v>192</v>
-      </c>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
+      <c r="A16" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B18" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="75" t="str">
-        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A18" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="81" t="str">
+        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>417600</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">D18*E18</f>
         <v>417600</v>
       </c>
-      <c r="G18" s="76" t="n">
-        <f aca="false">D18*VLOOKUP(B18,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G18" s="82" t="n">
+        <f aca="false">D18*VLOOKUP(B18,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>928000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="54" t="n">
+      <c r="A19" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="61" t="n">
         <f aca="false">SUM(F18:F18)</f>
         <v>417600</v>
       </c>
-      <c r="G19" s="78" t="n">
+      <c r="G19" s="84" t="n">
         <f aca="false">SUM(G18:G18)</f>
         <v>928000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="75" t="str">
-        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A20" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="81" t="str">
+        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>406350</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">D20*E20</f>
         <v>406350</v>
       </c>
-      <c r="G20" s="76" t="n">
-        <f aca="false">D20*VLOOKUP(B20,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G20" s="82" t="n">
+        <f aca="false">D20*VLOOKUP(B20,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>903000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="54" t="n">
+      <c r="A21" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="61" t="n">
         <f aca="false">SUM(F20:F20)</f>
         <v>406350</v>
       </c>
-      <c r="G21" s="78" t="n">
+      <c r="G21" s="84" t="n">
         <f aca="false">SUM(G20:G20)</f>
         <v>903000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="80" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
+      <c r="A22" s="86" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B25" s="73" t="s">
+      <c r="A25" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B26" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
+      <c r="A26" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="75" t="str">
-        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A28" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="81" t="str">
+        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="9" t="n">
-        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>392850</v>
       </c>
       <c r="F28" s="9" t="n">
         <f aca="false">D28*E28</f>
         <v>392850</v>
       </c>
-      <c r="G28" s="76" t="n">
-        <f aca="false">D28*VLOOKUP(B28,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G28" s="82" t="n">
+        <f aca="false">D28*VLOOKUP(B28,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>873000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31"/>
-      <c r="B29" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="75" t="str">
-        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A29" s="22"/>
+      <c r="B29" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="81" t="str">
+        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="9" t="n">
-        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>138400</v>
       </c>
       <c r="F29" s="9" t="n">
         <f aca="false">D29*E29</f>
         <v>138400</v>
       </c>
-      <c r="G29" s="76" t="n">
-        <f aca="false">D29*VLOOKUP(B29,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G29" s="82" t="n">
+        <f aca="false">D29*VLOOKUP(B29,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="B30" s="77"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="54" t="n">
+      <c r="A30" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="61" t="n">
         <f aca="false">SUM(F28:F29)</f>
         <v>531250</v>
       </c>
-      <c r="G30" s="78" t="n">
+      <c r="G30" s="84" t="n">
         <f aca="false">SUM(G28:G29)</f>
         <v>1219000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="75" t="str">
-        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A31" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="81" t="str">
+        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="9" t="n">
-        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>384750</v>
       </c>
       <c r="F31" s="9" t="n">
         <f aca="false">D31*E31</f>
         <v>384750</v>
       </c>
-      <c r="G31" s="76" t="n">
-        <f aca="false">D31*VLOOKUP(B31,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G31" s="82" t="n">
+        <f aca="false">D31*VLOOKUP(B31,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>855000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31"/>
-      <c r="B32" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="75" t="str">
-        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A32" s="22"/>
+      <c r="B32" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="81" t="str">
+        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D32" s="31" t="n">
+      <c r="D32" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="9" t="n">
-        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>138400</v>
       </c>
       <c r="F32" s="9" t="n">
         <f aca="false">D32*E32</f>
         <v>138400</v>
       </c>
-      <c r="G32" s="76" t="n">
-        <f aca="false">D32*VLOOKUP(B32,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G32" s="82" t="n">
+        <f aca="false">D32*VLOOKUP(B32,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="54" t="n">
+      <c r="A33" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="61" t="n">
         <f aca="false">SUM(F31:F32)</f>
         <v>523150</v>
       </c>
-      <c r="G33" s="78" t="n">
+      <c r="G33" s="84" t="n">
         <f aca="false">SUM(G31:G32)</f>
         <v>1201000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="79" t="s">
-        <v>195</v>
-      </c>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
+      <c r="A34" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="72" t="s">
+      <c r="A36" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B37" s="73" t="s">
+      <c r="A37" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="73"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="73"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B38" s="73" t="s">
-        <v>196</v>
-      </c>
-      <c r="C38" s="73"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="73"/>
+      <c r="A38" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" s="79" t="s">
+        <v>211</v>
+      </c>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B40" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="75" t="str">
-        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A40" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="81" t="str">
+        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>CPU + 이더넷 (입력 24 / 출력 16) — MCC, 견적에 없어 추정가</v>
       </c>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="9" t="n">
-        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>423450</v>
       </c>
       <c r="F40" s="9" t="n">
         <f aca="false">D40*E40</f>
         <v>423450</v>
       </c>
-      <c r="G40" s="76" t="n">
-        <f aca="false">D40*VLOOKUP(B40,단가표!$B$5:$G$24,4,FALSE())</f>
+      <c r="G40" s="82" t="n">
+        <f aca="false">D40*VLOOKUP(B40,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>941000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="31"/>
-      <c r="B41" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="75" t="str">
-        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$24,3,FALSE())</f>
+      <c r="A41" s="22"/>
+      <c r="B41" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="81" t="str">
+        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$26,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
-      <c r="D41" s="31" t="n">
-        <v>2</v>
+      <c r="D41" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="E41" s="9" t="n">
-        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$24,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$26,6,FALSE())</f>
         <v>91200</v>
       </c>
       <c r="F41" s="9" t="n">
         <f aca="false">D41*E41</f>
-        <v>182400</v>
-      </c>
-      <c r="G41" s="76" t="n">
-        <f aca="false">D41*VLOOKUP(B41,단가표!$B$5:$G$24,4,FALSE())</f>
         <v>456000</v>
       </c>
+      <c r="G41" s="82" t="n">
+        <f aca="false">D41*VLOOKUP(B41,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>1140000</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="31"/>
-      <c r="B42" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="75" t="str">
-        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>디지털 입력 8점</v>
-      </c>
-      <c r="D42" s="31" t="n">
-        <v>1</v>
+      <c r="A42" s="22"/>
+      <c r="B42" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="81" t="str">
+        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>트랜지스터 출력 16점</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="E42" s="9" t="n">
-        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>80800</v>
+        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>90800</v>
       </c>
       <c r="F42" s="9" t="n">
         <f aca="false">D42*E42</f>
-        <v>80800</v>
-      </c>
-      <c r="G42" s="76" t="n">
-        <f aca="false">D42*VLOOKUP(B42,단가표!$B$5:$G$24,4,FALSE())</f>
-        <v>202000</v>
+        <v>181600</v>
+      </c>
+      <c r="G42" s="82" t="n">
+        <f aca="false">D42*VLOOKUP(B42,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>454000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="31"/>
-      <c r="B43" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="75" t="str">
-        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>트랜지스터 출력 16점</v>
-      </c>
-      <c r="D43" s="31" t="n">
+      <c r="A43" s="22"/>
+      <c r="B43" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="81" t="str">
+        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>트랜지스터 출력 8점</v>
+      </c>
+      <c r="D43" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="9" t="n">
-        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>90800</v>
+        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>67200</v>
       </c>
       <c r="F43" s="9" t="n">
         <f aca="false">D43*E43</f>
-        <v>90800</v>
-      </c>
-      <c r="G43" s="76" t="n">
-        <f aca="false">D43*VLOOKUP(B43,단가표!$B$5:$G$24,4,FALSE())</f>
-        <v>227000</v>
+        <v>67200</v>
+      </c>
+      <c r="G43" s="82" t="n">
+        <f aca="false">D43*VLOOKUP(B43,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>168000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="31"/>
-      <c r="B44" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="75" t="str">
-        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>트랜지스터 출력 8점</v>
-      </c>
-      <c r="D44" s="31" t="n">
+      <c r="A44" s="22"/>
+      <c r="B44" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="81" t="str">
+        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>아날로그 출력 4CH</v>
+      </c>
+      <c r="D44" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="9" t="n">
-        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>67200</v>
+        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>140400</v>
       </c>
       <c r="F44" s="9" t="n">
         <f aca="false">D44*E44</f>
-        <v>67200</v>
-      </c>
-      <c r="G44" s="76" t="n">
-        <f aca="false">D44*VLOOKUP(B44,단가표!$B$5:$G$24,4,FALSE())</f>
-        <v>168000</v>
+        <v>140400</v>
+      </c>
+      <c r="G44" s="82" t="n">
+        <f aca="false">D44*VLOOKUP(B44,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>351000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="31"/>
-      <c r="B45" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" s="75" t="str">
-        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$24,3,FALSE())</f>
-        <v>아날로그 출력 2CH</v>
-      </c>
-      <c r="D45" s="31" t="n">
+      <c r="A45" s="22"/>
+      <c r="B45" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="81" t="str">
+        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>TM3 버스 확장 송신 (MCC)</v>
+      </c>
+      <c r="D45" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="9" t="n">
-        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$24,6,FALSE())</f>
-        <v>138400</v>
+        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>0</v>
       </c>
       <c r="F45" s="9" t="n">
         <f aca="false">D45*E45</f>
-        <v>138400</v>
-      </c>
-      <c r="G45" s="76" t="n">
-        <f aca="false">D45*VLOOKUP(B45,단가표!$B$5:$G$24,4,FALSE())</f>
-        <v>346000</v>
+        <v>0</v>
+      </c>
+      <c r="G45" s="82" t="n">
+        <f aca="false">D45*VLOOKUP(B45,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="54" t="n">
-        <f aca="false">SUM(F40:F45)</f>
-        <v>983050</v>
-      </c>
-      <c r="G46" s="78" t="n">
-        <f aca="false">SUM(G40:G45)</f>
-        <v>2340000</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="80" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" s="80"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="81" t="str">
+        <f aca="false">VLOOKUP(B46,단가표!$B$5:$G$26,3,FALSE())</f>
+        <v>TM3 버스 확장 수신 (MCC)</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <f aca="false">VLOOKUP(B46,단가표!$B$5:$G$26,6,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <f aca="false">D46*E46</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="82" t="n">
+        <f aca="false">D46*VLOOKUP(B46,단가표!$B$5:$G$26,4,FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="B47" s="83"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="61" t="n">
+        <f aca="false">SUM(F40:F46)</f>
+        <v>1268650</v>
+      </c>
+      <c r="G47" s="84" t="n">
+        <f aca="false">SUM(G40:G46)</f>
+        <v>3054000</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="86" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -13526,9 +14442,9 @@
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G38"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A48:G48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13559,64 +14475,64 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>199</v>
+      <c r="A1" s="35" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="81" t="n">
+      <c r="A3" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="87" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="81" t="n">
+      <c r="A4" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="87" t="n">
         <v>0.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>209</v>
+      <c r="A7" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>224</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$24,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>873000</v>
       </c>
       <c r="D7" s="9" t="n">
@@ -13627,11 +14543,11 @@
         <f aca="false">ROUND(C7*$B$4,0)</f>
         <v>349200</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="44" t="n">
         <f aca="false">D7-E7</f>
         <v>43650</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="39" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -13639,19 +14555,19 @@
         <f aca="false">F7*G7</f>
         <v>10912500</v>
       </c>
-      <c r="I7" s="82" t="s">
-        <v>210</v>
+      <c r="I7" s="88" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>209</v>
+      <c r="A8" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>224</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$24,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>928000</v>
       </c>
       <c r="D8" s="9" t="n">
@@ -13662,11 +14578,11 @@
         <f aca="false">ROUND(C8*$B$4,0)</f>
         <v>371200</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="44" t="n">
         <f aca="false">D8-E8</f>
         <v>46400</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="39" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -13674,19 +14590,19 @@
         <f aca="false">F8*G8</f>
         <v>13920000</v>
       </c>
-      <c r="I8" s="82" t="s">
-        <v>211</v>
+      <c r="I8" s="88" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>209</v>
+      <c r="A9" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>224</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$24,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>941000</v>
       </c>
       <c r="D9" s="9" t="n">
@@ -13697,11 +14613,11 @@
         <f aca="false">ROUND(C9*$B$4,0)</f>
         <v>376400</v>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F9" s="44" t="n">
         <f aca="false">D9-E9</f>
         <v>47050</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="39" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
@@ -13709,19 +14625,19 @@
         <f aca="false">F9*G9</f>
         <v>4705000</v>
       </c>
-      <c r="I9" s="82" t="s">
-        <v>212</v>
+      <c r="I9" s="88" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>213</v>
+      <c r="A10" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>228</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$24,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>855000</v>
       </c>
       <c r="D10" s="9" t="n">
@@ -13732,11 +14648,11 @@
         <f aca="false">ROUND(C10*$B$4,0)</f>
         <v>342000</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="44" t="n">
         <f aca="false">D10-E10</f>
         <v>42750</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="39" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -13744,19 +14660,19 @@
         <f aca="false">F10*G10</f>
         <v>10687500</v>
       </c>
-      <c r="I10" s="82" t="s">
-        <v>214</v>
+      <c r="I10" s="88" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>213</v>
+      <c r="A11" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>228</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$24,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,4,FALSE())</f>
         <v>903000</v>
       </c>
       <c r="D11" s="9" t="n">
@@ -13767,11 +14683,11 @@
         <f aca="false">ROUND(C11*$B$4,0)</f>
         <v>361200</v>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="44" t="n">
         <f aca="false">D11-E11</f>
         <v>45150</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="39" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -13779,43 +14695,43 @@
         <f aca="false">F11*G11</f>
         <v>13545000</v>
       </c>
-      <c r="I11" s="82" t="s">
-        <v>215</v>
+      <c r="I11" s="88" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
+      <c r="A13" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
       <c r="H13" s="16" t="n">
         <f aca="false">H7+H8+H9</f>
         <v>29537500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
+      <c r="A14" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
       <c r="H14" s="16" t="n">
         <f aca="false">H9+H10+H11</f>
         <v>28937500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
-        <v>218</v>
+      <c r="A16" s="53" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -13838,7 +14754,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -13851,55 +14767,55 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
-        <v>219</v>
+      <c r="A1" s="55" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="n">
+      <c r="A5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="83" t="s">
-        <v>223</v>
+      <c r="B5" s="56" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="89" t="s">
+        <v>238</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>886000</v>
       </c>
-      <c r="F5" s="84" t="n">
+      <c r="F5" s="90" t="n">
         <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -13908,22 +14824,22 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="n">
+      <c r="A6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="83" t="s">
+      <c r="B6" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>224</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>239</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>873000</v>
       </c>
-      <c r="F6" s="84" t="n">
+      <c r="F6" s="90" t="n">
         <v>0.45</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -13932,22 +14848,22 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" s="83" t="s">
-        <v>225</v>
+      <c r="B7" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" s="89" t="s">
+        <v>240</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>855000</v>
       </c>
-      <c r="F7" s="84" t="n">
+      <c r="F7" s="90" t="n">
         <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -13956,22 +14872,22 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="D8" s="83" t="s">
-        <v>226</v>
+      <c r="B8" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="89" t="s">
+        <v>241</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>928000</v>
       </c>
-      <c r="F8" s="84" t="n">
+      <c r="F8" s="90" t="n">
         <v>0.45</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -13980,22 +14896,22 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="n">
+      <c r="A9" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" s="83" t="s">
-        <v>227</v>
+      <c r="B9" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="89" t="s">
+        <v>242</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>903000</v>
       </c>
-      <c r="F9" s="84" t="n">
+      <c r="F9" s="90" t="n">
         <v>0.45</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -14004,22 +14920,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="n">
+      <c r="A10" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="85" t="s">
-        <v>229</v>
+      <c r="B10" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="91" t="s">
+        <v>243</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>228000</v>
       </c>
-      <c r="F10" s="84" t="n">
+      <c r="F10" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -14028,22 +14944,22 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="n">
+      <c r="A11" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="85" t="s">
-        <v>230</v>
+      <c r="B11" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="91" t="s">
+        <v>245</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>202000</v>
       </c>
-      <c r="F11" s="84" t="n">
+      <c r="F11" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -14052,22 +14968,22 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="n">
+      <c r="A12" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="85" t="s">
-        <v>232</v>
+      <c r="B12" s="56" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>247</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F12" s="84" t="n">
+      <c r="F12" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -14076,22 +14992,22 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="n">
+      <c r="A13" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="85" t="s">
-        <v>233</v>
+      <c r="B13" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="91" t="s">
+        <v>248</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F13" s="84" t="n">
+      <c r="F13" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -14100,22 +15016,22 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="49" t="s">
-        <v>234</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="85" t="s">
-        <v>235</v>
+      <c r="B14" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="91" t="s">
+        <v>250</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>213000</v>
       </c>
-      <c r="F14" s="84" t="n">
+      <c r="F14" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -14124,22 +15040,22 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="85" t="s">
-        <v>237</v>
+      <c r="B15" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="91" t="s">
+        <v>252</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>161000</v>
       </c>
-      <c r="F15" s="84" t="n">
+      <c r="F15" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -14148,22 +15064,22 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="n">
+      <c r="A16" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="85" t="s">
-        <v>238</v>
+      <c r="B16" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="91" t="s">
+        <v>253</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F16" s="84" t="n">
+      <c r="F16" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -14172,22 +15088,22 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="49" t="s">
-        <v>239</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D17" s="85" t="s">
-        <v>240</v>
+      <c r="B17" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="91" t="s">
+        <v>255</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F17" s="84" t="n">
+      <c r="F17" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
@@ -14196,22 +15112,22 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D18" s="85" t="s">
-        <v>242</v>
+      <c r="B18" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="91" t="s">
+        <v>257</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>311000</v>
       </c>
-      <c r="F18" s="84" t="n">
+      <c r="F18" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -14220,22 +15136,22 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="31" t="n">
+      <c r="A19" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="49" t="s">
-        <v>243</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D19" s="85" t="s">
-        <v>244</v>
+      <c r="B19" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="91" t="s">
+        <v>259</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>284000</v>
       </c>
-      <c r="F19" s="84" t="n">
+      <c r="F19" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -14244,22 +15160,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="n">
+      <c r="A20" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D20" s="85" t="s">
-        <v>246</v>
+      <c r="B20" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="91" t="s">
+        <v>261</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>331000</v>
       </c>
-      <c r="F20" s="84" t="n">
+      <c r="F20" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -14268,22 +15184,22 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="n">
+      <c r="A21" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D21" s="85" t="s">
-        <v>247</v>
+      <c r="B21" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="91" t="s">
+        <v>262</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>346000</v>
       </c>
-      <c r="F21" s="84" t="n">
+      <c r="F21" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -14292,22 +15208,22 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D22" s="85" t="s">
-        <v>249</v>
+      <c r="B22" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="91" t="s">
+        <v>263</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>351000</v>
       </c>
-      <c r="F22" s="84" t="n">
+      <c r="F22" s="90" t="n">
         <v>0.4</v>
       </c>
       <c r="G22" s="10" t="n">
@@ -14316,33 +15232,33 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="86" t="s">
-        <v>250</v>
-      </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="86"/>
+      <c r="A23" s="92" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="B24" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="D24" s="87" t="s">
-        <v>251</v>
-      </c>
-      <c r="E24" s="88" t="n">
+      <c r="A24" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D24" s="93" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" s="94" t="n">
         <v>941000</v>
       </c>
-      <c r="F24" s="89" t="n">
+      <c r="F24" s="95" t="n">
         <v>0.45</v>
       </c>
       <c r="G24" s="10" t="n">
@@ -14350,9 +15266,53 @@
         <v>423450</v>
       </c>
     </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="93" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" s="94"/>
+      <c r="F25" s="95" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <f aca="false">IF(E25="",0,ROUND(E25*F25,0))</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>252</v>
+      <c r="A26" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="93" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" s="94"/>
+      <c r="F26" s="95" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <f aca="false">IF(E26="",0,ROUND(E26*F26,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="173">
   <si>
     <r>
       <rPr>
@@ -2584,7 +2584,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">※ 매입가는 현재 할인율 기준</t>
+      <t xml:space="preserve">※ 매입가는 현재 할인율</t>
     </r>
     <r>
       <rPr>
@@ -2594,7 +2594,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. MCC CPU(TM241CE40T)</t>
+      <t xml:space="preserve">(CPU 0.45 · </t>
     </r>
     <r>
       <rPr>
@@ -2603,7 +2603,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 견적에 없어 추정 단가 — 실단가를 </t>
+      <t xml:space="preserve">모듈 </t>
     </r>
     <r>
       <rPr>
@@ -2613,7 +2613,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">0.40) </t>
     </r>
     <r>
       <rPr>
@@ -2622,7 +2622,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">단가표</t>
+      <t xml:space="preserve">기준</t>
     </r>
     <r>
       <rPr>
@@ -2632,7 +2632,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">. MCC</t>
     </r>
     <r>
       <rPr>
@@ -2641,7 +2641,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에 넣으면 자동 반영됩니다</t>
+      <t xml:space="preserve">는 버스 확장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM3XTRA1/XREC1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">까지 포함된 가격입니다</t>
     </r>
     <r>
       <rPr>
@@ -3759,7 +3778,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3768,7 +3787,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3778,7 +3797,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3787,7 +3806,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3797,7 +3816,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3806,7 +3825,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3816,7 +3835,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3825,7 +3844,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3835,7 +3854,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3844,17 +3863,17 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.  ※ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3863,7 +3882,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3873,7 +3892,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3882,7 +3901,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF375623"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3892,49 +3911,21 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가격 미정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.  TM241CE40T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 추정 단가</t>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF375623"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -4379,27 +4370,6 @@
     <t xml:space="preserve">TSU, ANU-S</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MCC  ※ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추정 단가</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">MCC×5</t>
   </si>
   <si>
@@ -4409,185 +4379,97 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MCC  ※ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가격 미정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ TM241CE40T</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 단가는 </t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 추정 단가</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, TM3XTRA1/XREC1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가표</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 가격 미정</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(0</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매입 단가 </t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM241CE40T · TM3XTRA1 · TM3XREC1</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 </t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가격을 </t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-06 </t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추가 견적</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단가표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노란 칸에 넣으면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BOM·MCC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마진이 모두 자동 반영됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
     </r>
   </si>
   <si>
@@ -4780,6 +4662,1103 @@
     <t xml:space="preserve">ANU (DC24V)</t>
   </si>
   <si>
+    <t xml:space="preserve">AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSU + ANU-S (AC220V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANU (AC220V)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC24V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 살 때 연간 절감 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM241C24T + C40T + CE40T)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC220V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 살 때 연간 절감 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM241C24R + C40R + MCC CE40T)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 확장 모듈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 할인율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 그대로 두고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, CPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 계산했습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가표 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받은 견적 그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매입 단가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리스트가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">할인율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DF)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">No.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">할인율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DF)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM241CE24T</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이더넷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 + TR 4)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 + TR 4)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디지털 입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DI8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디지털 입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DQ16R</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트랜지스터 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DQ16U</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트랜지스터 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Sink)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DQ8R</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">릴레이 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트랜지스터 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3DQ8U</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트랜지스터 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Sink)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3AI2H</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2CH</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3AI4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4CH</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TM3AI8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8CH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2CH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아날로그 출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4CH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPU + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이더넷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 송신</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TM3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스 확장 수신</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="8"/>
@@ -4788,7 +5767,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MCC (</t>
+      <t xml:space="preserve">※ 1~18</t>
     </r>
     <r>
       <rPr>
@@ -4797,7 +5776,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추정 단가</t>
+      <t xml:space="preserve">번 기존 견적</t>
     </r>
     <r>
       <rPr>
@@ -4807,1294 +5786,83 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">AC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSU + ANU-S (AC220V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANU (AC220V)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC24V</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 살 때 연간 절감 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TM241C24T + C40T + CE40T)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AC220V</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 살 때 연간 절감 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TM241C24R + C40R + MCC CE40T)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 확장 모듈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TM3)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 할인율 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 그대로 두고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, CPU</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 계산했습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단가표 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받은 견적 그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">매입 단가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리스트가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">할인율</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(DF)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">No.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">할인율 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(DF)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM241CE24T</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이더넷 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 + TR 4)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16 = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 + TR 4)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디지털 입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DI8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디지털 입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DQ16R</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트랜지스터 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DQ16U</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트랜지스터 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Sink)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DQ8R</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">릴레이 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트랜지스터 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3DQ8U</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트랜지스터 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Sink)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3AI2H</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2CH</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3AI4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4CH</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TM3AI8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8CH</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2CH</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아날로그 출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4CH</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견적에 없는 품목 — 가격을 받으면 노란 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리스트가</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 입력하세요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이더넷 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24 / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16) — MCC, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견적에 없어 추정가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TM3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">버스 확장 송신 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(MCC)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TM3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">버스 확장 수신 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(MCC)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">, 19~21</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ TM241CE40T </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리스트가는 추정값</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TM241CE40T · TM3XTRA1 · TM3XREC1)</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: TM241C40T </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정가 </t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-06 </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">928,000 + (CE24T − C24T </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추가 견적</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정가 차이 </t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.  </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13,000). </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참고 </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실단가를 받으면 리스트가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">할인율을 덮어쓰세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NP: 579,600 / 98,280 / 116,550</t>
     </r>
   </si>
 </sst>
@@ -6111,7 +5879,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6311,12 +6079,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1F3864"/>
@@ -6433,23 +6195,8 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6478,12 +6225,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7F7F7F"/>
-        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
@@ -6549,7 +6290,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6646,19 +6387,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6666,11 +6403,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6698,11 +6435,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6710,7 +6447,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6726,11 +6463,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6742,11 +6479,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6774,19 +6511,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6794,19 +6531,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6828,22 +6565,6 @@
     </xf>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7281,18 +7002,18 @@
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F47</f>
-        <v>1268650</v>
+        <v>1395600</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">C9*D9</f>
-        <v>126865000</v>
+        <v>139560000</v>
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">F9</f>
-        <v>126865000</v>
+        <v>139560000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7308,11 +7029,11 @@
       <c r="E10" s="15"/>
       <c r="F10" s="16" t="n">
         <f aca="false">SUM(F6:F9)</f>
-        <v>357277500</v>
+        <v>369972500</v>
       </c>
       <c r="G10" s="16" t="n">
         <f aca="false">SUM(G6:G9)</f>
-        <v>351877500</v>
+        <v>364572500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7418,7 +7139,7 @@
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="str">
         <f aca="false">"① 연간 구매금액: DC24V 기준 약 "&amp;TEXT(F10/100000000,"0.00")&amp;"억 원,  AC220V 기준 약 "&amp;TEXT(G10/100000000,"0.00")&amp;"억 원"</f>
-        <v>① 연간 구매금액: DC24V 기준 약 3.57억 원,  AC220V 기준 약 3.52억 원</v>
+        <v>① 연간 구매금액: DC24V 기준 약 3.70억 원,  AC220V 기준 약 3.65억 원</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -7450,16 +7171,16 @@
       <c r="G23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="str">
-        <f aca="false">IF(VLOOKUP("TM3XTRA1",단가표!$B$5:$G$26,6,FALSE())+VLOOKUP("TM3XREC1",단가표!$B$5:$G$26,6,FALSE())=0,"④ 가격 미확정: TM241CE40T(추정 단가), TM3XTRA1 / TM3XREC1(가격 미정, 현재 0원) → Schneider에 요청 후 '단가표' 노란 칸에 입력","④ 가격 확인 필요: TM241CE40T 단가가 추정값이면 실단가로 바꿔 입력")</f>
-        <v>④ 가격 미확정: TM241CE40T(추정 단가), TM3XTRA1 / TM3XREC1(가격 미정, 현재 0원) → Schneider에 요청 후 '단가표' 노란 칸에 입력</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="A24" s="22" t="str">
+        <f aca="false">"④ MCC 가격 확정: TM241CE40T · TM3XTRA1 · TM3XREC1 견적 반영 (2026-10-06) → MCC 1대 "&amp;TEXT(D9,"#,##0")&amp;"원, 연간 "&amp;TEXT(F9,"#,##0")&amp;"원"</f>
+        <v>④ MCC 가격 확정: TM241CE40T · TM3XTRA1 · TM3XREC1 견적 반영 (2026-10-06) → MCC 1대 1,395,600원, 연간 139,560,000원</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
@@ -7475,7 +7196,7 @@
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="str">
         <f aca="false">"⑥ CPU 할인율을 "&amp;TEXT('CPU 할인 효과'!B3,"0.00")&amp;" → "&amp;TEXT('CPU 할인 효과'!B4,"0.00")&amp;"으로 받으면 연간 약 "&amp;TEXT('CPU 할인 효과'!H13/10000,"#,##0")&amp;"만 원 절감 (DC24V 기준)"</f>
-        <v>⑥ CPU 할인율을 0.45 → 0.40으로 받으면 연간 약 2,954만 원 절감 (DC24V 기준)</v>
+        <v>⑥ CPU 할인율을 0.45 → 0.40으로 받으면 연간 약 2,943만 원 절감 (DC24V 기준)</v>
       </c>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -7485,27 +7206,27 @@
       <c r="G26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="str">
+      <c r="A28" s="25" t="str">
         <f aca="false">"⑧ LS 타겟 기준 연간 마진 (DC24V): "&amp;IF(ISNUMBER('마진 계산'!E30),TEXT('마진 계산'!E30,"#,##0")&amp;"원 (마진율 "&amp;TEXT('마진 계산'!F30,"0.0%")&amp;")  /  희망 마진("&amp;TEXT('마진 계산'!B4,"0%")&amp;")까지 연간 추가 특가 "&amp;TEXT('마진 계산'!G30,"#,##0")&amp;"원 필요","LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
         <v>⑧ LS 타겟 기준 연간 마진 (DC24V): LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -7564,7 +7285,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7574,10 +7295,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="28" t="n">
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -7585,7 +7306,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>47</v>
       </c>
     </row>
@@ -7622,23 +7343,23 @@
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="31" t="n">
         <f aca="false">요약!C6</f>
         <v>200</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F9</f>
         <v>392850</v>
       </c>
-      <c r="F8" s="34" t="str">
+      <c r="F8" s="33" t="str">
         <f aca="false">IF(D8="","",D8-E8)</f>
         <v/>
       </c>
-      <c r="G8" s="35" t="str">
+      <c r="G8" s="34" t="str">
         <f aca="false">IF(OR(D8="",D8=0),"",F8/D8)</f>
         <v/>
       </c>
@@ -7646,11 +7367,11 @@
         <f aca="false">IF(D8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="I8" s="34" t="str">
+      <c r="I8" s="33" t="str">
         <f aca="false">IF(D8="","",C8*F8)</f>
         <v/>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="35" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7658,23 +7379,23 @@
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="31" t="n">
         <f aca="false">요약!C6</f>
         <v>200</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F11</f>
         <v>384750</v>
       </c>
-      <c r="F9" s="34" t="str">
+      <c r="F9" s="33" t="str">
         <f aca="false">IF(D9="","",D9-E9)</f>
         <v/>
       </c>
-      <c r="G9" s="35" t="str">
+      <c r="G9" s="34" t="str">
         <f aca="false">IF(OR(D9="",D9=0),"",F9/D9)</f>
         <v/>
       </c>
@@ -7682,7 +7403,7 @@
         <f aca="false">IF(D9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="I9" s="34" t="str">
+      <c r="I9" s="33" t="str">
         <f aca="false">IF(D9="","",C9*F9)</f>
         <v/>
       </c>
@@ -7691,23 +7412,23 @@
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="31" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F19</f>
         <v>417600</v>
       </c>
-      <c r="F10" s="34" t="str">
+      <c r="F10" s="33" t="str">
         <f aca="false">IF(D10="","",D10-E10)</f>
         <v/>
       </c>
-      <c r="G10" s="35" t="str">
+      <c r="G10" s="34" t="str">
         <f aca="false">IF(OR(D10="",D10=0),"",F10/D10)</f>
         <v/>
       </c>
@@ -7715,7 +7436,7 @@
         <f aca="false">IF(D10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="I10" s="34" t="str">
+      <c r="I10" s="33" t="str">
         <f aca="false">IF(D10="","",C10*F10)</f>
         <v/>
       </c>
@@ -7724,23 +7445,23 @@
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="31" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="32"/>
       <c r="E11" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F21</f>
         <v>406350</v>
       </c>
-      <c r="F11" s="34" t="str">
+      <c r="F11" s="33" t="str">
         <f aca="false">IF(D11="","",D11-E11)</f>
         <v/>
       </c>
-      <c r="G11" s="35" t="str">
+      <c r="G11" s="34" t="str">
         <f aca="false">IF(OR(D11="",D11=0),"",F11/D11)</f>
         <v/>
       </c>
@@ -7748,7 +7469,7 @@
         <f aca="false">IF(D11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="I11" s="34" t="str">
+      <c r="I11" s="33" t="str">
         <f aca="false">IF(D11="","",C11*F11)</f>
         <v/>
       </c>
@@ -7757,23 +7478,23 @@
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="31" t="n">
         <f aca="false">요약!C8</f>
         <v>50</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F30</f>
         <v>531250</v>
       </c>
-      <c r="F12" s="34" t="str">
+      <c r="F12" s="33" t="str">
         <f aca="false">IF(D12="","",D12-E12)</f>
         <v/>
       </c>
-      <c r="G12" s="35" t="str">
+      <c r="G12" s="34" t="str">
         <f aca="false">IF(OR(D12="",D12=0),"",F12/D12)</f>
         <v/>
       </c>
@@ -7781,7 +7502,7 @@
         <f aca="false">IF(D12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="I12" s="34" t="str">
+      <c r="I12" s="33" t="str">
         <f aca="false">IF(D12="","",C12*F12)</f>
         <v/>
       </c>
@@ -7790,23 +7511,23 @@
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="31" t="n">
         <f aca="false">요약!C8</f>
         <v>50</v>
       </c>
-      <c r="D13" s="33"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F33</f>
         <v>523150</v>
       </c>
-      <c r="F13" s="34" t="str">
+      <c r="F13" s="33" t="str">
         <f aca="false">IF(D13="","",D13-E13)</f>
         <v/>
       </c>
-      <c r="G13" s="35" t="str">
+      <c r="G13" s="34" t="str">
         <f aca="false">IF(OR(D13="",D13=0),"",F13/D13)</f>
         <v/>
       </c>
@@ -7814,7 +7535,7 @@
         <f aca="false">IF(D13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="I13" s="34" t="str">
+      <c r="I13" s="33" t="str">
         <f aca="false">IF(D13="","",C13*F13)</f>
         <v/>
       </c>
@@ -7823,23 +7544,23 @@
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="31" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="9" t="n">
         <f aca="false">'프로젝트별 구성'!F47</f>
-        <v>1268650</v>
-      </c>
-      <c r="F14" s="34" t="str">
+        <v>1395600</v>
+      </c>
+      <c r="F14" s="33" t="str">
         <f aca="false">IF(D14="","",D14-E14)</f>
         <v/>
       </c>
-      <c r="G14" s="35" t="str">
+      <c r="G14" s="34" t="str">
         <f aca="false">IF(OR(D14="",D14=0),"",F14/D14)</f>
         <v/>
       </c>
@@ -7847,13 +7568,13 @@
         <f aca="false">IF(D14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="I14" s="34" t="str">
+      <c r="I14" s="33" t="str">
         <f aca="false">IF(D14="","",C14*F14)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="29" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7893,7 +7614,7 @@
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="30" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="9" t="str">
@@ -7904,19 +7625,19 @@
         <f aca="false">E8</f>
         <v>392850</v>
       </c>
-      <c r="E19" s="37" t="str">
+      <c r="E19" s="36" t="str">
         <f aca="false">IF(C19="","",MAX(D19-C19,0))</f>
         <v/>
       </c>
-      <c r="F19" s="38" t="str">
+      <c r="F19" s="37" t="str">
         <f aca="false">IF(C19="","",E19/D19)</f>
         <v/>
       </c>
-      <c r="G19" s="39" t="n">
+      <c r="G19" s="38" t="n">
         <f aca="false">IFERROR(D19/'프로젝트별 구성'!G9,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H19" s="40" t="str">
+      <c r="H19" s="39" t="str">
         <f aca="false">IF(C19="","",IFERROR(MIN(C19,D19)/'프로젝트별 구성'!G9,""))</f>
         <v/>
       </c>
@@ -7924,7 +7645,7 @@
         <f aca="false">IF(C19="","",E19*C8)</f>
         <v/>
       </c>
-      <c r="J19" s="41" t="str">
+      <c r="J19" s="40" t="str">
         <f aca="false">IF(C19="","타겟 입력 전",IF(E19=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -7933,7 +7654,7 @@
       <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="30" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="9" t="str">
@@ -7944,19 +7665,19 @@
         <f aca="false">E9</f>
         <v>384750</v>
       </c>
-      <c r="E20" s="37" t="str">
+      <c r="E20" s="36" t="str">
         <f aca="false">IF(C20="","",MAX(D20-C20,0))</f>
         <v/>
       </c>
-      <c r="F20" s="38" t="str">
+      <c r="F20" s="37" t="str">
         <f aca="false">IF(C20="","",E20/D20)</f>
         <v/>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="38" t="n">
         <f aca="false">IFERROR(D20/'프로젝트별 구성'!G11,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H20" s="40" t="str">
+      <c r="H20" s="39" t="str">
         <f aca="false">IF(C20="","",IFERROR(MIN(C20,D20)/'프로젝트별 구성'!G11,""))</f>
         <v/>
       </c>
@@ -7964,7 +7685,7 @@
         <f aca="false">IF(C20="","",E20*C9)</f>
         <v/>
       </c>
-      <c r="J20" s="41" t="str">
+      <c r="J20" s="40" t="str">
         <f aca="false">IF(C20="","타겟 입력 전",IF(E20=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -7973,7 +7694,7 @@
       <c r="A21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="30" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="9" t="str">
@@ -7984,19 +7705,19 @@
         <f aca="false">E10</f>
         <v>417600</v>
       </c>
-      <c r="E21" s="37" t="str">
+      <c r="E21" s="36" t="str">
         <f aca="false">IF(C21="","",MAX(D21-C21,0))</f>
         <v/>
       </c>
-      <c r="F21" s="38" t="str">
+      <c r="F21" s="37" t="str">
         <f aca="false">IF(C21="","",E21/D21)</f>
         <v/>
       </c>
-      <c r="G21" s="39" t="n">
+      <c r="G21" s="38" t="n">
         <f aca="false">IFERROR(D21/'프로젝트별 구성'!G19,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H21" s="40" t="str">
+      <c r="H21" s="39" t="str">
         <f aca="false">IF(C21="","",IFERROR(MIN(C21,D21)/'프로젝트별 구성'!G19,""))</f>
         <v/>
       </c>
@@ -8004,7 +7725,7 @@
         <f aca="false">IF(C21="","",E21*C10)</f>
         <v/>
       </c>
-      <c r="J21" s="41" t="str">
+      <c r="J21" s="40" t="str">
         <f aca="false">IF(C21="","타겟 입력 전",IF(E21=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -8013,7 +7734,7 @@
       <c r="A22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="30" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="9" t="str">
@@ -8024,19 +7745,19 @@
         <f aca="false">E11</f>
         <v>406350</v>
       </c>
-      <c r="E22" s="37" t="str">
+      <c r="E22" s="36" t="str">
         <f aca="false">IF(C22="","",MAX(D22-C22,0))</f>
         <v/>
       </c>
-      <c r="F22" s="38" t="str">
+      <c r="F22" s="37" t="str">
         <f aca="false">IF(C22="","",E22/D22)</f>
         <v/>
       </c>
-      <c r="G22" s="39" t="n">
+      <c r="G22" s="38" t="n">
         <f aca="false">IFERROR(D22/'프로젝트별 구성'!G21,"")</f>
         <v>0.45</v>
       </c>
-      <c r="H22" s="40" t="str">
+      <c r="H22" s="39" t="str">
         <f aca="false">IF(C22="","",IFERROR(MIN(C22,D22)/'프로젝트별 구성'!G21,""))</f>
         <v/>
       </c>
@@ -8044,7 +7765,7 @@
         <f aca="false">IF(C22="","",E22*C11)</f>
         <v/>
       </c>
-      <c r="J22" s="41" t="str">
+      <c r="J22" s="40" t="str">
         <f aca="false">IF(C22="","타겟 입력 전",IF(E22=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -8053,7 +7774,7 @@
       <c r="A23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="30" t="s">
         <v>56</v>
       </c>
       <c r="C23" s="9" t="str">
@@ -8064,19 +7785,19 @@
         <f aca="false">E12</f>
         <v>531250</v>
       </c>
-      <c r="E23" s="37" t="str">
+      <c r="E23" s="36" t="str">
         <f aca="false">IF(C23="","",MAX(D23-C23,0))</f>
         <v/>
       </c>
-      <c r="F23" s="38" t="str">
+      <c r="F23" s="37" t="str">
         <f aca="false">IF(C23="","",E23/D23)</f>
         <v/>
       </c>
-      <c r="G23" s="39" t="n">
+      <c r="G23" s="38" t="n">
         <f aca="false">IFERROR(D23/'프로젝트별 구성'!G30,"")</f>
         <v>0.435808039376538</v>
       </c>
-      <c r="H23" s="40" t="str">
+      <c r="H23" s="39" t="str">
         <f aca="false">IF(C23="","",IFERROR(MIN(C23,D23)/'프로젝트별 구성'!G30,""))</f>
         <v/>
       </c>
@@ -8084,7 +7805,7 @@
         <f aca="false">IF(C23="","",E23*C12)</f>
         <v/>
       </c>
-      <c r="J23" s="41" t="str">
+      <c r="J23" s="40" t="str">
         <f aca="false">IF(C23="","타겟 입력 전",IF(E23=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -8093,7 +7814,7 @@
       <c r="A24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="30" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="9" t="str">
@@ -8104,19 +7825,19 @@
         <f aca="false">E13</f>
         <v>523150</v>
       </c>
-      <c r="E24" s="37" t="str">
+      <c r="E24" s="36" t="str">
         <f aca="false">IF(C24="","",MAX(D24-C24,0))</f>
         <v/>
       </c>
-      <c r="F24" s="38" t="str">
+      <c r="F24" s="37" t="str">
         <f aca="false">IF(C24="","",E24/D24)</f>
         <v/>
       </c>
-      <c r="G24" s="39" t="n">
+      <c r="G24" s="38" t="n">
         <f aca="false">IFERROR(D24/'프로젝트별 구성'!G33,"")</f>
         <v>0.435595337218984</v>
       </c>
-      <c r="H24" s="40" t="str">
+      <c r="H24" s="39" t="str">
         <f aca="false">IF(C24="","",IFERROR(MIN(C24,D24)/'프로젝트별 구성'!G33,""))</f>
         <v/>
       </c>
@@ -8124,7 +7845,7 @@
         <f aca="false">IF(C24="","",E24*C13)</f>
         <v/>
       </c>
-      <c r="J24" s="41" t="str">
+      <c r="J24" s="40" t="str">
         <f aca="false">IF(C24="","타겟 입력 전",IF(E24=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
@@ -8133,7 +7854,7 @@
       <c r="A25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="30" t="s">
         <v>56</v>
       </c>
       <c r="C25" s="9" t="str">
@@ -8142,21 +7863,21 @@
       </c>
       <c r="D25" s="9" t="n">
         <f aca="false">E14</f>
-        <v>1268650</v>
-      </c>
-      <c r="E25" s="37" t="str">
+        <v>1395600</v>
+      </c>
+      <c r="E25" s="36" t="str">
         <f aca="false">IF(C25="","",MAX(D25-C25,0))</f>
         <v/>
       </c>
-      <c r="F25" s="38" t="str">
+      <c r="F25" s="37" t="str">
         <f aca="false">IF(C25="","",E25/D25)</f>
         <v/>
       </c>
-      <c r="G25" s="39" t="n">
+      <c r="G25" s="38" t="n">
         <f aca="false">IFERROR(D25/'프로젝트별 구성'!G47,"")</f>
-        <v>0.415406024885396</v>
-      </c>
-      <c r="H25" s="40" t="str">
+        <v>0.413633669235329</v>
+      </c>
+      <c r="H25" s="39" t="str">
         <f aca="false">IF(C25="","",IFERROR(MIN(C25,D25)/'프로젝트별 구성'!G47,""))</f>
         <v/>
       </c>
@@ -8164,18 +7885,18 @@
         <f aca="false">IF(C25="","",E25*C14)</f>
         <v/>
       </c>
-      <c r="J25" s="41" t="str">
+      <c r="J25" s="40" t="str">
         <f aca="false">IF(C25="","타겟 입력 전",IF(E25=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
         <v>타겟 입력 전</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="35" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="29" t="s">
         <v>67</v>
       </c>
     </row>
@@ -8201,64 +7922,64 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="42"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="9" t="n">
         <f aca="false">C8*E8+C10*E10+C12*E12+C14*E14</f>
-        <v>357277500</v>
+        <v>369972500</v>
       </c>
       <c r="D30" s="9" t="str">
         <f aca="false">IF((D8="")+(D10="")+(D12="")+(D14="")&gt;0,"타겟 "&amp;((D8="")+(D10="")+(D12="")+(D14=""))&amp;"건 미입력",H8+H10+H12+H14)</f>
         <v>타겟 4건 미입력</v>
       </c>
-      <c r="E30" s="43" t="str">
+      <c r="E30" s="42" t="str">
         <f aca="false">IF(ISNUMBER(D30),D30-C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="44" t="str">
+      <c r="F30" s="43" t="str">
         <f aca="false">IF(ISNUMBER(D30),E30/D30,"")</f>
         <v/>
       </c>
-      <c r="G30" s="45" t="str">
+      <c r="G30" s="44" t="str">
         <f aca="false">IF(ISNUMBER(D30),I19+I21+I23+I25,"")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="42"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="9" t="n">
         <f aca="false">C9*E9+C11*E11+C13*E13+C14*E14</f>
-        <v>351877500</v>
+        <v>364572500</v>
       </c>
       <c r="D31" s="9" t="str">
         <f aca="false">IF((D9="")+(D11="")+(D13="")+(D14="")&gt;0,"타겟 "&amp;((D9="")+(D11="")+(D13="")+(D14=""))&amp;"건 미입력",H9+H11+H13+H14)</f>
         <v>타겟 4건 미입력</v>
       </c>
-      <c r="E31" s="43" t="str">
+      <c r="E31" s="42" t="str">
         <f aca="false">IF(ISNUMBER(D31),D31-C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="44" t="str">
+      <c r="F31" s="43" t="str">
         <f aca="false">IF(ISNUMBER(D31),E31/D31,"")</f>
         <v/>
       </c>
-      <c r="G31" s="45" t="str">
+      <c r="G31" s="44" t="str">
         <f aca="false">IF(ISNUMBER(D31),I20+I22+I24+I25,"")</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="45" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
+      <c r="A34" s="46" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8313,7 +8034,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>75</v>
       </c>
     </row>
@@ -8323,41 +8044,41 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -8383,140 +8104,140 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="53" t="str">
-        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C8" s="52" t="str">
+        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B8,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>392850</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">D8*E8</f>
         <v>392850</v>
       </c>
-      <c r="G8" s="54" t="n">
-        <f aca="false">D8*VLOOKUP(B8,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G8" s="53" t="n">
+        <f aca="false">D8*VLOOKUP(B8,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>873000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56" t="n">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="55" t="n">
         <f aca="false">SUM(F8:F8)</f>
         <v>392850</v>
       </c>
-      <c r="G9" s="57" t="n">
+      <c r="G9" s="56" t="n">
         <f aca="false">SUM(G8:G8)</f>
         <v>873000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="53" t="str">
-        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C10" s="52" t="str">
+        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B10,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>384750</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">D10*E10</f>
         <v>384750</v>
       </c>
-      <c r="G10" s="54" t="n">
-        <f aca="false">D10*VLOOKUP(B10,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G10" s="53" t="n">
+        <f aca="false">D10*VLOOKUP(B10,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>855000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="56" t="n">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="55" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>384750</v>
       </c>
-      <c r="G11" s="57" t="n">
+      <c r="G11" s="56" t="n">
         <f aca="false">SUM(G10:G10)</f>
         <v>855000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -8542,140 +8263,140 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="53" t="str">
-        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C18" s="52" t="str">
+        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B18,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>417600</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">D18*E18</f>
         <v>417600</v>
       </c>
-      <c r="G18" s="54" t="n">
-        <f aca="false">D18*VLOOKUP(B18,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G18" s="53" t="n">
+        <f aca="false">D18*VLOOKUP(B18,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>928000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56" t="n">
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="55" t="n">
         <f aca="false">SUM(F18:F18)</f>
         <v>417600</v>
       </c>
-      <c r="G19" s="57" t="n">
+      <c r="G19" s="56" t="n">
         <f aca="false">SUM(G18:G18)</f>
         <v>928000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="53" t="str">
-        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C20" s="52" t="str">
+        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B20,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>406350</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">D20*E20</f>
         <v>406350</v>
       </c>
-      <c r="G20" s="54" t="n">
-        <f aca="false">D20*VLOOKUP(B20,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G20" s="53" t="n">
+        <f aca="false">D20*VLOOKUP(B20,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>903000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="56" t="n">
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="55" t="n">
         <f aca="false">SUM(F20:F20)</f>
         <v>406350</v>
       </c>
-      <c r="G21" s="57" t="n">
+      <c r="G21" s="56" t="n">
         <f aca="false">SUM(G20:G20)</f>
         <v>903000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
@@ -8701,190 +8422,190 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="53" t="str">
-        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C28" s="52" t="str">
+        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="9" t="n">
-        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B28,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>392850</v>
       </c>
       <c r="F28" s="9" t="n">
         <f aca="false">D28*E28</f>
         <v>392850</v>
       </c>
-      <c r="G28" s="54" t="n">
-        <f aca="false">D28*VLOOKUP(B28,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G28" s="53" t="n">
+        <f aca="false">D28*VLOOKUP(B28,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>873000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31"/>
-      <c r="B29" s="52" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="53" t="str">
-        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C29" s="52" t="str">
+        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="9" t="n">
-        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B29,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>138400</v>
       </c>
       <c r="F29" s="9" t="n">
         <f aca="false">D29*E29</f>
         <v>138400</v>
       </c>
-      <c r="G29" s="54" t="n">
-        <f aca="false">D29*VLOOKUP(B29,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G29" s="53" t="n">
+        <f aca="false">D29*VLOOKUP(B29,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56" t="n">
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="55" t="n">
         <f aca="false">SUM(F28:F29)</f>
         <v>531250</v>
       </c>
-      <c r="G30" s="57" t="n">
+      <c r="G30" s="56" t="n">
         <f aca="false">SUM(G28:G29)</f>
         <v>1219000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B31" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="53" t="str">
-        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C31" s="52" t="str">
+        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="9" t="n">
-        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B31,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>384750</v>
       </c>
       <c r="F31" s="9" t="n">
         <f aca="false">D31*E31</f>
         <v>384750</v>
       </c>
-      <c r="G31" s="54" t="n">
-        <f aca="false">D31*VLOOKUP(B31,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G31" s="53" t="n">
+        <f aca="false">D31*VLOOKUP(B31,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>855000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31"/>
-      <c r="B32" s="52" t="s">
+      <c r="A32" s="30"/>
+      <c r="B32" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="53" t="str">
-        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C32" s="52" t="str">
+        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
-      <c r="D32" s="31" t="n">
+      <c r="D32" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="9" t="n">
-        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B32,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>138400</v>
       </c>
       <c r="F32" s="9" t="n">
         <f aca="false">D32*E32</f>
         <v>138400</v>
       </c>
-      <c r="G32" s="54" t="n">
-        <f aca="false">D32*VLOOKUP(B32,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G32" s="53" t="n">
+        <f aca="false">D32*VLOOKUP(B32,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>346000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="56" t="n">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="55" t="n">
         <f aca="false">SUM(F31:F32)</f>
         <v>523150</v>
       </c>
-      <c r="G33" s="57" t="n">
+      <c r="G33" s="56" t="n">
         <f aca="false">SUM(G31:G32)</f>
         <v>1201000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="58" t="s">
+      <c r="A34" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
@@ -8909,210 +8630,210 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="31" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="53" t="str">
-        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$26,3,FALSE())</f>
-        <v>CPU + 이더넷 (입력 24 / 출력 16) — MCC, 견적에 없어 추정가</v>
-      </c>
-      <c r="D40" s="31" t="n">
+      <c r="C40" s="52" t="str">
+        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$25,3,FALSE())</f>
+        <v>CPU + 이더넷 (입력 24 / 출력 16)</v>
+      </c>
+      <c r="D40" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="9" t="n">
-        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$26,6,FALSE())</f>
-        <v>423450</v>
+        <f aca="false">VLOOKUP(B40,단가표!$B$5:$G$25,6,FALSE())</f>
+        <v>414000</v>
       </c>
       <c r="F40" s="9" t="n">
         <f aca="false">D40*E40</f>
-        <v>423450</v>
-      </c>
-      <c r="G40" s="54" t="n">
-        <f aca="false">D40*VLOOKUP(B40,단가표!$B$5:$G$26,4,FALSE())</f>
-        <v>941000</v>
+        <v>414000</v>
+      </c>
+      <c r="G40" s="53" t="n">
+        <f aca="false">D40*VLOOKUP(B40,단가표!$B$5:$G$25,4,FALSE())</f>
+        <v>920000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="31"/>
-      <c r="B41" s="52" t="s">
+      <c r="A41" s="30"/>
+      <c r="B41" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="53" t="str">
-        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C41" s="52" t="str">
+        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
-      <c r="D41" s="31" t="n">
+      <c r="D41" s="30" t="n">
         <v>5</v>
       </c>
       <c r="E41" s="9" t="n">
-        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B41,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>91200</v>
       </c>
       <c r="F41" s="9" t="n">
         <f aca="false">D41*E41</f>
         <v>456000</v>
       </c>
-      <c r="G41" s="54" t="n">
-        <f aca="false">D41*VLOOKUP(B41,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G41" s="53" t="n">
+        <f aca="false">D41*VLOOKUP(B41,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>1140000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="31"/>
-      <c r="B42" s="52" t="s">
+      <c r="A42" s="30"/>
+      <c r="B42" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="53" t="str">
-        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C42" s="52" t="str">
+        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>트랜지스터 출력 16점</v>
       </c>
-      <c r="D42" s="31" t="n">
+      <c r="D42" s="30" t="n">
         <v>2</v>
       </c>
       <c r="E42" s="9" t="n">
-        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B42,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>90800</v>
       </c>
       <c r="F42" s="9" t="n">
         <f aca="false">D42*E42</f>
         <v>181600</v>
       </c>
-      <c r="G42" s="54" t="n">
-        <f aca="false">D42*VLOOKUP(B42,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G42" s="53" t="n">
+        <f aca="false">D42*VLOOKUP(B42,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>454000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="31"/>
-      <c r="B43" s="52" t="s">
+      <c r="A43" s="30"/>
+      <c r="B43" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="53" t="str">
-        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C43" s="52" t="str">
+        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>트랜지스터 출력 8점</v>
       </c>
-      <c r="D43" s="31" t="n">
+      <c r="D43" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="9" t="n">
-        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B43,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>67200</v>
       </c>
       <c r="F43" s="9" t="n">
         <f aca="false">D43*E43</f>
         <v>67200</v>
       </c>
-      <c r="G43" s="54" t="n">
-        <f aca="false">D43*VLOOKUP(B43,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G43" s="53" t="n">
+        <f aca="false">D43*VLOOKUP(B43,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>168000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="31"/>
-      <c r="B44" s="52" t="s">
+      <c r="A44" s="30"/>
+      <c r="B44" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="53" t="str">
-        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$26,3,FALSE())</f>
+      <c r="C44" s="52" t="str">
+        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>아날로그 출력 4CH</v>
       </c>
-      <c r="D44" s="31" t="n">
+      <c r="D44" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="9" t="n">
-        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(B44,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>140400</v>
       </c>
       <c r="F44" s="9" t="n">
         <f aca="false">D44*E44</f>
         <v>140400</v>
       </c>
-      <c r="G44" s="54" t="n">
-        <f aca="false">D44*VLOOKUP(B44,단가표!$B$5:$G$26,4,FALSE())</f>
+      <c r="G44" s="53" t="n">
+        <f aca="false">D44*VLOOKUP(B44,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>351000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="31"/>
-      <c r="B45" s="52" t="s">
+      <c r="A45" s="30"/>
+      <c r="B45" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="53" t="str">
-        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$26,3,FALSE())</f>
-        <v>TM3 버스 확장 송신 (MCC)</v>
-      </c>
-      <c r="D45" s="31" t="n">
+      <c r="C45" s="52" t="str">
+        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$25,3,FALSE())</f>
+        <v>TM3 버스 확장 송신</v>
+      </c>
+      <c r="D45" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="9" t="n">
-        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$26,6,FALSE())</f>
-        <v>0</v>
+        <f aca="false">VLOOKUP(B45,단가표!$B$5:$G$25,6,FALSE())</f>
+        <v>62400</v>
       </c>
       <c r="F45" s="9" t="n">
         <f aca="false">D45*E45</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="54" t="n">
-        <f aca="false">D45*VLOOKUP(B45,단가표!$B$5:$G$26,4,FALSE())</f>
-        <v>0</v>
+        <v>62400</v>
+      </c>
+      <c r="G45" s="53" t="n">
+        <f aca="false">D45*VLOOKUP(B45,단가표!$B$5:$G$25,4,FALSE())</f>
+        <v>156000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="31"/>
-      <c r="B46" s="52" t="s">
+      <c r="A46" s="30"/>
+      <c r="B46" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="53" t="str">
-        <f aca="false">VLOOKUP(B46,단가표!$B$5:$G$26,3,FALSE())</f>
-        <v>TM3 버스 확장 수신 (MCC)</v>
-      </c>
-      <c r="D46" s="31" t="n">
+      <c r="C46" s="52" t="str">
+        <f aca="false">VLOOKUP(B46,단가표!$B$5:$G$25,3,FALSE())</f>
+        <v>TM3 버스 확장 수신</v>
+      </c>
+      <c r="D46" s="30" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="9" t="n">
-        <f aca="false">VLOOKUP(B46,단가표!$B$5:$G$26,6,FALSE())</f>
-        <v>0</v>
+        <f aca="false">VLOOKUP(B46,단가표!$B$5:$G$25,6,FALSE())</f>
+        <v>74000</v>
       </c>
       <c r="F46" s="9" t="n">
         <f aca="false">D46*E46</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="54" t="n">
-        <f aca="false">D46*VLOOKUP(B46,단가표!$B$5:$G$26,4,FALSE())</f>
-        <v>0</v>
+        <v>74000</v>
+      </c>
+      <c r="G46" s="53" t="n">
+        <f aca="false">D46*VLOOKUP(B46,단가표!$B$5:$G$25,4,FALSE())</f>
+        <v>185000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="55" t="s">
+      <c r="A47" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="55"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="56" t="n">
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="55" t="n">
         <f aca="false">SUM(F40:F46)</f>
-        <v>1268650</v>
-      </c>
-      <c r="G47" s="57" t="n">
+        <v>1395600</v>
+      </c>
+      <c r="G47" s="56" t="n">
         <f aca="false">SUM(G40:G46)</f>
-        <v>3054000</v>
+        <v>3374000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="59" t="s">
+      <c r="A48" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="59"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -9172,7 +8893,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>105</v>
       </c>
     </row>
@@ -9208,18 +8929,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="51" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="7" t="str">
-        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10)</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A5,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>392850</v>
       </c>
-      <c r="D5" s="60" t="n">
+      <c r="D5" s="59" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -9227,37 +8948,37 @@
         <f aca="false">C5*D5</f>
         <v>98212500</v>
       </c>
-      <c r="F5" s="60" t="n">
+      <c r="F5" s="59" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">C5*F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="60" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="51" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="7" t="str">
-        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 14 / 출력 10 = 릴레이 6 + TR 4)</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A6,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>384750</v>
       </c>
-      <c r="D6" s="60" t="n">
+      <c r="D6" s="59" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">C6*D6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="60" t="n">
+      <c r="F6" s="59" t="n">
         <f aca="false">1*요약!$C$6+1*요약!$C$8</f>
         <v>250</v>
       </c>
@@ -9265,23 +8986,23 @@
         <f aca="false">C6*F6</f>
         <v>96187500</v>
       </c>
-      <c r="H6" s="61" t="s">
+      <c r="H6" s="60" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="7" t="str">
-        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16)</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>417600</v>
       </c>
-      <c r="D7" s="60" t="n">
+      <c r="D7" s="59" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -9289,37 +9010,37 @@
         <f aca="false">C7*D7</f>
         <v>125280000</v>
       </c>
-      <c r="F7" s="60" t="n">
+      <c r="F7" s="59" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">C7*F7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="61" t="s">
+      <c r="H7" s="60" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="51" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="7" t="str">
-        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>CPU (입력 24 / 출력 16 = 릴레이 12 + TR 4)</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>406350</v>
       </c>
-      <c r="D8" s="60" t="n">
+      <c r="D8" s="59" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">C8*D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="60" t="n">
+      <c r="F8" s="59" t="n">
         <f aca="false">1*요약!$C$7</f>
         <v>300</v>
       </c>
@@ -9327,55 +9048,55 @@
         <f aca="false">C8*F8</f>
         <v>121905000</v>
       </c>
-      <c r="H8" s="61" t="s">
+      <c r="H8" s="60" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B9" s="7" t="str">
-        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,3,FALSE())</f>
-        <v>CPU + 이더넷 (입력 24 / 출력 16) — MCC, 견적에 없어 추정가</v>
-      </c>
-      <c r="C9" s="37" t="n">
-        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,6,FALSE())</f>
-        <v>423450</v>
-      </c>
-      <c r="D9" s="60" t="n">
+        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$25,3,FALSE())</f>
+        <v>CPU + 이더넷 (입력 24 / 출력 16)</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$25,6,FALSE())</f>
+        <v>414000</v>
+      </c>
+      <c r="D9" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">C9*D9</f>
-        <v>42345000</v>
-      </c>
-      <c r="F9" s="60" t="n">
+        <v>41400000</v>
+      </c>
+      <c r="F9" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">C9*F9</f>
-        <v>42345000</v>
-      </c>
-      <c r="H9" s="62" t="s">
-        <v>114</v>
+        <v>41400000</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="7" t="str">
-        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>디지털 입력 16점</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>91200</v>
       </c>
-      <c r="D10" s="60" t="n">
+      <c r="D10" s="59" t="n">
         <f aca="false">5*요약!$C$9</f>
         <v>500</v>
       </c>
@@ -9383,7 +9104,7 @@
         <f aca="false">C10*D10</f>
         <v>45600000</v>
       </c>
-      <c r="F10" s="60" t="n">
+      <c r="F10" s="59" t="n">
         <f aca="false">5*요약!$C$9</f>
         <v>500</v>
       </c>
@@ -9391,23 +9112,23 @@
         <f aca="false">C10*F10</f>
         <v>45600000</v>
       </c>
-      <c r="H10" s="61" t="s">
-        <v>115</v>
+      <c r="H10" s="60" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="51" t="s">
         <v>99</v>
       </c>
       <c r="B11" s="7" t="str">
-        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>트랜지스터 출력 16점</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>90800</v>
       </c>
-      <c r="D11" s="60" t="n">
+      <c r="D11" s="59" t="n">
         <f aca="false">2*요약!$C$9</f>
         <v>200</v>
       </c>
@@ -9415,7 +9136,7 @@
         <f aca="false">C11*D11</f>
         <v>18160000</v>
       </c>
-      <c r="F11" s="60" t="n">
+      <c r="F11" s="59" t="n">
         <f aca="false">2*요약!$C$9</f>
         <v>200</v>
       </c>
@@ -9423,23 +9144,23 @@
         <f aca="false">C11*F11</f>
         <v>18160000</v>
       </c>
-      <c r="H11" s="61" t="s">
-        <v>116</v>
+      <c r="H11" s="60" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="51" t="s">
         <v>100</v>
       </c>
       <c r="B12" s="7" t="str">
-        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>트랜지스터 출력 8점</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A12,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>67200</v>
       </c>
-      <c r="D12" s="60" t="n">
+      <c r="D12" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -9447,7 +9168,7 @@
         <f aca="false">C12*D12</f>
         <v>6720000</v>
       </c>
-      <c r="F12" s="60" t="n">
+      <c r="F12" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -9455,23 +9176,23 @@
         <f aca="false">C12*F12</f>
         <v>6720000</v>
       </c>
-      <c r="H12" s="61" t="s">
+      <c r="H12" s="60" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="51" t="s">
         <v>93</v>
       </c>
       <c r="B13" s="7" t="str">
-        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>아날로그 출력 2CH</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A13,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>138400</v>
       </c>
-      <c r="D13" s="60" t="n">
+      <c r="D13" s="59" t="n">
         <f aca="false">1*요약!$C$8</f>
         <v>50</v>
       </c>
@@ -9479,7 +9200,7 @@
         <f aca="false">C13*D13</f>
         <v>6920000</v>
       </c>
-      <c r="F13" s="60" t="n">
+      <c r="F13" s="59" t="n">
         <f aca="false">1*요약!$C$8</f>
         <v>50</v>
       </c>
@@ -9487,23 +9208,23 @@
         <f aca="false">C13*F13</f>
         <v>6920000</v>
       </c>
-      <c r="H13" s="61" t="s">
+      <c r="H13" s="60" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="51" t="s">
         <v>101</v>
       </c>
       <c r="B14" s="7" t="str">
-        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$26,3,FALSE())</f>
+        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$25,3,FALSE())</f>
         <v>아날로그 출력 4CH</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$26,6,FALSE())</f>
+        <f aca="false">VLOOKUP(A14,단가표!$B$5:$G$25,6,FALSE())</f>
         <v>140400</v>
       </c>
-      <c r="D14" s="60" t="n">
+      <c r="D14" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -9511,7 +9232,7 @@
         <f aca="false">C14*D14</f>
         <v>14040000</v>
       </c>
-      <c r="F14" s="60" t="n">
+      <c r="F14" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
@@ -9519,72 +9240,72 @@
         <f aca="false">C14*F14</f>
         <v>14040000</v>
       </c>
-      <c r="H14" s="61" t="s">
+      <c r="H14" s="60" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="51" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="7" t="str">
-        <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$26,3,FALSE())</f>
-        <v>TM3 버스 확장 송신 (MCC)</v>
+        <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$25,3,FALSE())</f>
+        <v>TM3 버스 확장 송신</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$26,6,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="60" t="n">
+        <f aca="false">VLOOKUP(A15,단가표!$B$5:$G$25,6,FALSE())</f>
+        <v>62400</v>
+      </c>
+      <c r="D15" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">C15*D15</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="60" t="n">
+        <v>6240000</v>
+      </c>
+      <c r="F15" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">C15*F15</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="62" t="s">
-        <v>117</v>
+        <v>6240000</v>
+      </c>
+      <c r="H15" s="60" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="51" t="s">
         <v>103</v>
       </c>
       <c r="B16" s="7" t="str">
-        <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$26,3,FALSE())</f>
-        <v>TM3 버스 확장 수신 (MCC)</v>
+        <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$25,3,FALSE())</f>
+        <v>TM3 버스 확장 수신</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$26,6,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="60" t="n">
+        <f aca="false">VLOOKUP(A16,단가표!$B$5:$G$25,6,FALSE())</f>
+        <v>74000</v>
+      </c>
+      <c r="D16" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">C16*D16</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="60" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="F16" s="59" t="n">
         <f aca="false">1*요약!$C$9</f>
         <v>100</v>
       </c>
       <c r="G16" s="9" t="n">
         <f aca="false">C16*F16</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="62" t="s">
-        <v>117</v>
+        <v>7400000</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9593,32 +9314,32 @@
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="63" t="n">
+      <c r="D17" s="61" t="n">
         <f aca="false">SUM(D5:D16)</f>
         <v>1800</v>
       </c>
-      <c r="E17" s="56" t="n">
+      <c r="E17" s="55" t="n">
         <f aca="false">SUM(E5:E16)</f>
-        <v>357277500</v>
-      </c>
-      <c r="F17" s="63" t="n">
+        <v>369972500</v>
+      </c>
+      <c r="F17" s="61" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>1800</v>
       </c>
-      <c r="G17" s="56" t="n">
+      <c r="G17" s="55" t="n">
         <f aca="false">SUM(G5:G16)</f>
-        <v>351877500</v>
+        <v>364572500</v>
       </c>
       <c r="H17" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="64" t="s">
-        <v>118</v>
+      <c r="A19" s="62" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="64" t="s">
-        <v>119</v>
+      <c r="A20" s="63" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -9654,64 +9375,64 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="64" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
+      <c r="B4" s="64" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B3" s="65" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="65" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>49</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>130</v>
+      <c r="B7" s="30" t="s">
+        <v>128</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$26,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A7,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>873000</v>
       </c>
       <c r="D7" s="9" t="n">
@@ -9722,11 +9443,11 @@
         <f aca="false">ROUND(C7*$B$4,0)</f>
         <v>349200</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="36" t="n">
         <f aca="false">D7-E7</f>
         <v>43650</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="31" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -9734,19 +9455,19 @@
         <f aca="false">F7*G7</f>
         <v>10912500</v>
       </c>
-      <c r="I7" s="66" t="s">
-        <v>131</v>
+      <c r="I7" s="65" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>130</v>
+      <c r="B8" s="30" t="s">
+        <v>128</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$26,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A8,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>928000</v>
       </c>
       <c r="D8" s="9" t="n">
@@ -9757,11 +9478,11 @@
         <f aca="false">ROUND(C8*$B$4,0)</f>
         <v>371200</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="36" t="n">
         <f aca="false">D8-E8</f>
         <v>46400</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="31" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -9769,54 +9490,54 @@
         <f aca="false">F8*G8</f>
         <v>13920000</v>
       </c>
-      <c r="I8" s="66" t="s">
-        <v>132</v>
+      <c r="I8" s="65" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>130</v>
+      <c r="B9" s="30" t="s">
+        <v>128</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$26,4,FALSE())</f>
-        <v>941000</v>
+        <f aca="false">VLOOKUP(A9,단가표!$B$5:$G$25,4,FALSE())</f>
+        <v>920000</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">ROUND(C9*$B$3,0)</f>
-        <v>423450</v>
+        <v>414000</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">ROUND(C9*$B$4,0)</f>
-        <v>376400</v>
-      </c>
-      <c r="F9" s="37" t="n">
+        <v>368000</v>
+      </c>
+      <c r="F9" s="36" t="n">
         <f aca="false">D9-E9</f>
-        <v>47050</v>
-      </c>
-      <c r="G9" s="32" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G9" s="31" t="n">
         <f aca="false">요약!C9</f>
         <v>100</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">F9*G9</f>
-        <v>4705000</v>
-      </c>
-      <c r="I9" s="66" t="s">
-        <v>133</v>
+        <v>4600000</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>134</v>
+      <c r="B10" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$26,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A10,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>855000</v>
       </c>
       <c r="D10" s="9" t="n">
@@ -9827,11 +9548,11 @@
         <f aca="false">ROUND(C10*$B$4,0)</f>
         <v>342000</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="36" t="n">
         <f aca="false">D10-E10</f>
         <v>42750</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="31" t="n">
         <f aca="false">요약!C6+요약!C8</f>
         <v>250</v>
       </c>
@@ -9839,19 +9560,19 @@
         <f aca="false">F10*G10</f>
         <v>10687500</v>
       </c>
-      <c r="I10" s="66" t="s">
-        <v>135</v>
+      <c r="I10" s="65" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>134</v>
+      <c r="B11" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$26,4,FALSE())</f>
+        <f aca="false">VLOOKUP(A11,단가표!$B$5:$G$25,4,FALSE())</f>
         <v>903000</v>
       </c>
       <c r="D11" s="9" t="n">
@@ -9862,11 +9583,11 @@
         <f aca="false">ROUND(C11*$B$4,0)</f>
         <v>361200</v>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="36" t="n">
         <f aca="false">D11-E11</f>
         <v>45150</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="31" t="n">
         <f aca="false">요약!C7</f>
         <v>300</v>
       </c>
@@ -9874,43 +9595,43 @@
         <f aca="false">F11*G11</f>
         <v>13545000</v>
       </c>
-      <c r="I11" s="66" t="s">
-        <v>136</v>
+      <c r="I11" s="65" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
+      <c r="A13" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="16" t="n">
         <f aca="false">H7+H8+H9</f>
-        <v>29537500</v>
+        <v>29432500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
+      <c r="A14" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="16" t="n">
         <f aca="false">H9+H10+H11</f>
-        <v>28937500</v>
+        <v>28832500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
-        <v>139</v>
+      <c r="A16" s="45" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -9933,7 +9654,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -9946,18 +9667,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
-        <v>140</v>
+      <c r="A1" s="47" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>80</v>
@@ -9969,32 +9690,32 @@
         <v>81</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="n">
+      <c r="A5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>145</v>
+      <c r="B5" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>142</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>886000</v>
       </c>
-      <c r="F5" s="68" t="n">
+      <c r="F5" s="67" t="n">
         <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -10003,22 +9724,22 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="n">
+      <c r="A6" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>146</v>
+      <c r="C6" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>143</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>873000</v>
       </c>
-      <c r="F6" s="68" t="n">
+      <c r="F6" s="67" t="n">
         <v>0.45</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -10027,22 +9748,22 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>147</v>
+      <c r="C7" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>855000</v>
       </c>
-      <c r="F7" s="68" t="n">
+      <c r="F7" s="67" t="n">
         <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -10051,22 +9772,22 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>148</v>
+      <c r="C8" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>145</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>928000</v>
       </c>
-      <c r="F8" s="68" t="n">
+      <c r="F8" s="67" t="n">
         <v>0.45</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -10075,22 +9796,22 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="n">
+      <c r="A9" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>149</v>
+      <c r="C9" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>146</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>903000</v>
       </c>
-      <c r="F9" s="68" t="n">
+      <c r="F9" s="67" t="n">
         <v>0.45</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -10099,22 +9820,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31" t="n">
+      <c r="A10" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="69" t="s">
-        <v>151</v>
+      <c r="C10" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>148</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>228000</v>
       </c>
-      <c r="F10" s="68" t="n">
+      <c r="F10" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -10123,22 +9844,22 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="n">
+      <c r="A11" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="68" t="s">
         <v>150</v>
-      </c>
-      <c r="D11" s="69" t="s">
-        <v>153</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>202000</v>
       </c>
-      <c r="F11" s="68" t="n">
+      <c r="F11" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -10147,22 +9868,22 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="n">
+      <c r="A12" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>155</v>
+      <c r="B12" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>152</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F12" s="68" t="n">
+      <c r="F12" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -10171,22 +9892,22 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="31" t="n">
+      <c r="A13" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="69" t="s">
-        <v>156</v>
+      <c r="C13" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>153</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>227000</v>
       </c>
-      <c r="F13" s="68" t="n">
+      <c r="F13" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -10195,22 +9916,22 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="69" t="s">
-        <v>158</v>
+      <c r="B14" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>155</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>213000</v>
       </c>
-      <c r="F14" s="68" t="n">
+      <c r="F14" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -10219,22 +9940,22 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>160</v>
+      <c r="B15" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>161000</v>
       </c>
-      <c r="F15" s="68" t="n">
+      <c r="F15" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -10243,22 +9964,22 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="n">
+      <c r="A16" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="69" t="s">
-        <v>161</v>
+      <c r="C16" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>158</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F16" s="68" t="n">
+      <c r="F16" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -10267,22 +9988,22 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>163</v>
+      <c r="B17" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>160</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>168000</v>
       </c>
-      <c r="F17" s="68" t="n">
+      <c r="F17" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
@@ -10291,22 +10012,22 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>165</v>
+      <c r="B18" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>162</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>311000</v>
       </c>
-      <c r="F18" s="68" t="n">
+      <c r="F18" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -10315,22 +10036,22 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="31" t="n">
+      <c r="A19" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="52" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>167</v>
+      <c r="B19" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>164</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>284000</v>
       </c>
-      <c r="F19" s="68" t="n">
+      <c r="F19" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -10339,22 +10060,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="n">
+      <c r="A20" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>169</v>
+      <c r="B20" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>166</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>331000</v>
       </c>
-      <c r="F20" s="68" t="n">
+      <c r="F20" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -10363,22 +10084,22 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="n">
+      <c r="A21" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="69" t="s">
-        <v>170</v>
+      <c r="C21" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>167</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>346000</v>
       </c>
-      <c r="F21" s="68" t="n">
+      <c r="F21" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -10387,22 +10108,22 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="69" t="s">
-        <v>171</v>
+      <c r="C22" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>168</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>351000</v>
       </c>
-      <c r="F22" s="68" t="n">
+      <c r="F22" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="G22" s="10" t="n">
@@ -10410,94 +10131,84 @@
         <v>140400</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="70" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="66" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>920000</v>
+      </c>
+      <c r="F23" s="67" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <f aca="false">ROUND(E23*F23,0)</f>
+        <v>414000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>156000</v>
+      </c>
+      <c r="F24" s="67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <f aca="false">ROUND(E24*F24,0)</f>
+        <v>62400</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>185000</v>
+      </c>
+      <c r="F25" s="67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <f aca="false">ROUND(E25*F25,0)</f>
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>173</v>
-      </c>
-      <c r="E24" s="72" t="n">
-        <v>941000</v>
-      </c>
-      <c r="F24" s="73" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <f aca="false">IF(E24="",0,ROUND(E24*F24,0))</f>
-        <v>423450</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="71" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <f aca="false">IF(E25="",0,ROUND(E25*F25,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <f aca="false">IF(E26="",0,ROUND(E26*F26,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>176</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A23:G23"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/PLC_견적_요약.xlsx
+++ b/PLC_견적_요약.xlsx
@@ -4065,7 +4065,7 @@
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="str">
         <f aca="false">"⑧ LS 타겟 기준 연간 마진 (DC24V): "&amp;IF(ISNUMBER('마진 계산'!E30),TEXT('마진 계산'!E30,"#,##0")&amp;"원 (마진율 "&amp;TEXT('마진 계산'!F30,"0.0%")&amp;")  /  희망 마진("&amp;TEXT('마진 계산'!B4,"0%")&amp;")까지 연간 추가 특가 "&amp;TEXT('마진 계산'!G30,"#,##0")&amp;"원 (프로젝트별로 각각 맞출 때)  — 묶음 전체로는 "&amp;IF('마진 계산'!F30&gt;='마진 계산'!B4,"추가 특가 없이 달성","추가 특가 필요"),"LS 타겟 프라이스를 '마진 계산' 시트에 넣으면 여기에 표시됩니다")</f>
-        <v>⑧ LS 타겟 기준 연간 마진 (DC24V): 117,495,000원 (마진율 26.4%)  /  희망 마진(20%)까지 연간 추가 특가 26,690,000원 (프로젝트별로 각각 맞출 때)  — 묶음 전체로는 추가 특가 없이 달성</v>
+        <v>⑧ LS 타겟 기준 연간 마진 (DC24V): 114,495,000원 (마진율 25.9%)  /  희망 마진(20%)까지 연간 추가 특가 29,090,000원 (프로젝트별로 각각 맞출 때)  — 묶음 전체로는 추가 특가 없이 달성</v>
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -4077,7 +4077,7 @@
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="str">
         <f aca="false">IF(NOT(ISNUMBER('마진 계산'!F14)),"⑨ MCC 마진: LS 타겟을 넣으면 표시됩니다",IF('마진 계산'!F14&lt;0,"⑨ MCC는 LS 타겟 대비 1대 "&amp;TEXT('마진 계산'!F14,"#,##0")&amp;"원 ("&amp;TEXT('마진 계산'!G14,"0.0%")&amp;"), 연 "&amp;TEXT('마진 계산'!I14,"#,##0")&amp;"원 손실 → 묶음 전체 마진("&amp;TEXT('마진 계산'!F30,"0.0%")&amp;")으로 흡수","⑨ MCC 마진: 1대 "&amp;TEXT('마진 계산'!F14,"#,##0")&amp;"원 ("&amp;TEXT('마진 계산'!G14,"0.0%")&amp;")"))</f>
-        <v>⑨ MCC는 LS 타겟 대비 1대 -26,900원 (-2.2%), 연 -2,690,000원 손실 → 묶음 전체 마진(26.4%)으로 흡수</v>
+        <v>⑨ MCC는 LS 타겟 대비 1대 -56,900원 (-4.9%), 연 -5,690,000원 손실 → 묶음 전체 마진(25.9%)으로 흡수</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -4424,7 +4424,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="35" t="n">
-        <v>1200000</v>
+        <v>1170000</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">'프로젝트별 구성'!F47</f>
@@ -4432,19 +4432,19 @@
       </c>
       <c r="F14" s="36" t="n">
         <f aca="false">IF(D14="","",D14-E14)</f>
-        <v>-26900</v>
+        <v>-56900</v>
       </c>
       <c r="G14" s="37" t="n">
         <f aca="false">IF(OR(D14="",D14=0),"",F14/D14)</f>
-        <v>-0.0224166666666667</v>
+        <v>-0.0486324786324786</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">IF(D14="","",C14*D14)</f>
-        <v>120000000</v>
+        <v>117000000</v>
       </c>
       <c r="I14" s="36" t="n">
         <f aca="false">IF(D14="","",C14*F14)</f>
-        <v>-2690000</v>
+        <v>-5690000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF(D14="","",ROUND(D14*(1-$B$4),0))</f>
-        <v>960000</v>
+        <v>936000</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">E14</f>
@@ -4745,11 +4745,11 @@
       </c>
       <c r="E25" s="42" t="n">
         <f aca="false">IF(C25="","",MAX(D25-C25,0))</f>
-        <v>266900</v>
+        <v>290900</v>
       </c>
       <c r="F25" s="43" t="n">
         <f aca="false">IF(C25="","",E25/D25)</f>
-        <v>0.217540141820849</v>
+        <v>0.237101638275328</v>
       </c>
       <c r="G25" s="44" t="n">
         <f aca="false">IFERROR(D25/'프로젝트별 구성'!G47,"")</f>
@@ -4757,11 +4757,11 @@
       </c>
       <c r="H25" s="45" t="n">
         <f aca="false">IF(C25="","",IFERROR(MIN(C25,D25)/'프로젝트별 구성'!G47,""))</f>
-        <v>0.28452874925904</v>
+        <v>0.277415530527564</v>
       </c>
       <c r="I25" s="11" t="n">
         <f aca="false">IF(C25="","",E25*C14)</f>
-        <v>26690000</v>
+        <v>29090000</v>
       </c>
       <c r="J25" s="46" t="str">
         <f aca="false">IF(C25="","타겟 입력 전",IF(E25=0,"OK — 지금 단가로 희망 마진 확보","추가 특가 필요"))</f>
@@ -4810,19 +4810,19 @@
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">IF((D8="")+(D10="")+(D12="")+(D14="")&gt;0,"타겟 "&amp;((D8="")+(D10="")+(D12="")+(D14=""))&amp;"건 미입력",H8+H10+H12+H14)</f>
-        <v>444900000</v>
+        <v>441900000</v>
       </c>
       <c r="E30" s="49" t="n">
         <f aca="false">IF(ISNUMBER(D30),D30-C30,"")</f>
-        <v>117495000</v>
+        <v>114495000</v>
       </c>
       <c r="F30" s="50" t="n">
         <f aca="false">IF(ISNUMBER(D30),E30/D30,"")</f>
-        <v>0.264093054619016</v>
+        <v>0.259097080787509</v>
       </c>
       <c r="G30" s="51" t="n">
         <f aca="false">IF(ISNUMBER(D30),I19+I21+I23+I25,"")</f>
-        <v>26690000</v>
+        <v>29090000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4836,19 +4836,19 @@
       </c>
       <c r="D31" s="10" t="n">
         <f aca="false">IF((D9="")+(D11="")+(D13="")+(D14="")&gt;0,"타겟 "&amp;((D9="")+(D11="")+(D13="")+(D14=""))&amp;"건 미입력",H9+H11+H13+H14)</f>
-        <v>444900000</v>
+        <v>441900000</v>
       </c>
       <c r="E31" s="49" t="n">
         <f aca="false">IF(ISNUMBER(D31),D31-C31,"")</f>
-        <v>122295000</v>
+        <v>119295000</v>
       </c>
       <c r="F31" s="50" t="n">
         <f aca="false">IF(ISNUMBER(D31),E31/D31,"")</f>
-        <v>0.274881995954147</v>
+        <v>0.269959266802444</v>
       </c>
       <c r="G31" s="51" t="n">
         <f aca="false">IF(ISNUMBER(D31),I20+I22+I24+I25,"")</f>
-        <v>26690000</v>
+        <v>29090000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
